--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -47453,22 +47453,22 @@
         <v>0</v>
       </c>
       <c r="Q99" t="n">
+        <v>6</v>
+      </c>
+      <c r="R99" t="n">
         <v>7</v>
       </c>
-      <c r="R99" t="n">
-        <v>9</v>
-      </c>
       <c r="S99" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T99" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U99" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V99" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="W99" t="n">
         <v>11</v>
@@ -47477,10 +47477,10 @@
         <v>21</v>
       </c>
       <c r="Y99" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Z99" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
@@ -47640,13 +47640,13 @@
         <v>81</v>
       </c>
       <c r="BZ99" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="CA99" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="CB99" t="n">
-        <v>3.63</v>
+        <v>3.85</v>
       </c>
       <c r="CC99" t="n">
         <v>0</v>
@@ -47694,7 +47694,7 @@
         <v>1</v>
       </c>
       <c r="CR99" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CS99" t="n">
         <v>19</v>
@@ -47703,19 +47703,19 @@
         <v>1</v>
       </c>
       <c r="CU99" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CV99" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW99" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX99" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CY99" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CZ99" t="n">
         <v>54</v>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -47931,16 +47931,16 @@
         <v>3</v>
       </c>
       <c r="S100" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U100" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V100" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W100" t="n">
         <v>12</v>
@@ -47949,10 +47949,10 @@
         <v>11</v>
       </c>
       <c r="Y100" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z100" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
@@ -48112,13 +48112,13 @@
         <v>83</v>
       </c>
       <c r="BZ100" t="n">
-        <v>0.6</v>
+        <v>0.97</v>
       </c>
       <c r="CA100" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="CB100" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="CC100" t="n">
         <v>0</v>
@@ -48175,19 +48175,19 @@
         <v>1</v>
       </c>
       <c r="CU100" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CV100" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CW100" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX100" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CY100" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CZ100" t="n">
         <v>20</v>
@@ -48411,16 +48411,16 @@
         <v>3</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T101" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U101" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V101" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W101" t="n">
         <v>23</v>
@@ -48429,10 +48429,10 @@
         <v>15</v>
       </c>
       <c r="Y101" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Z101" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
@@ -48592,13 +48592,13 @@
         <v>75</v>
       </c>
       <c r="BZ101" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="CA101" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="CB101" t="n">
-        <v>2.24</v>
+        <v>2.43</v>
       </c>
       <c r="CC101" t="n">
         <v>0</v>
@@ -48658,16 +48658,16 @@
         <v>15</v>
       </c>
       <c r="CV101" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CW101" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX101" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="CY101" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CZ101" t="n">
         <v>70</v>
@@ -48885,22 +48885,22 @@
         <v>1</v>
       </c>
       <c r="Q102" t="n">
+        <v>4</v>
+      </c>
+      <c r="R102" t="n">
         <v>5</v>
       </c>
-      <c r="R102" t="n">
-        <v>4</v>
-      </c>
       <c r="S102" t="n">
+        <v>13</v>
+      </c>
+      <c r="T102" t="n">
+        <v>1</v>
+      </c>
+      <c r="U102" t="n">
+        <v>17</v>
+      </c>
+      <c r="V102" t="n">
         <v>6</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
-        <v>11</v>
-      </c>
-      <c r="V102" t="n">
-        <v>4</v>
       </c>
       <c r="W102" t="n">
         <v>14</v>
@@ -48909,10 +48909,10 @@
         <v>20</v>
       </c>
       <c r="Y102" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="Z102" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
@@ -49072,13 +49072,13 @@
         <v>53</v>
       </c>
       <c r="BZ102" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="CA102" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="CB102" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="CC102" t="n">
         <v>0</v>
@@ -49135,19 +49135,19 @@
         <v>1</v>
       </c>
       <c r="CU102" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CV102" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CW102" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX102" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CY102" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CZ102" t="n">
         <v>42</v>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP102" headerRowCount="1">
-  <autoFilter ref="A1:EP102"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP104" headerRowCount="1">
+  <autoFilter ref="A1:EP104"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP102"/>
+  <dimension ref="A1:EP104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2757,7 +2757,7 @@
         <v>1</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -4339,164 +4339,164 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
         <v>45879.70833333334</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
       </c>
       <c r="L8" t="n">
+        <v>10</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>13</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>7</v>
       </c>
       <c r="U8" t="n">
         <v>8</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="W8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Z8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Estádio Pina Manique</t>
+          <t>Estádio Dr. Jorge Sampaio</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Rua Monsanto, Lisboa</t>
+          <t>Rua da Paradela, Pedroso, Vila Nova de Gaia</t>
         </is>
       </c>
       <c r="AC8" t="n">
         <v>1</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AH8" t="n">
         <v>1.33</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="AK8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL8" t="n">
         <v>1.82</v>
       </c>
-      <c r="AL8" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AM8" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AO8" t="n">
         <v>2.45</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>4880</v>
+        <v>-1</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
@@ -4520,61 +4520,61 @@
         <v>3</v>
       </c>
       <c r="BJ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM8" t="n">
         <v>6</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>9</v>
       </c>
       <c r="BN8" t="n">
         <v>4</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BU8" t="n">
         <v>1</v>
       </c>
       <c r="BV8" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BW8" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="BX8" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="BY8" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.24</v>
+        <v>0.92</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="CB8" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CC8" t="n">
         <v>0</v>
@@ -4610,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CO8" t="n">
         <v>0</v>
@@ -4622,28 +4622,28 @@
         <v>1</v>
       </c>
       <c r="CR8" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="CS8" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="CT8" t="n">
         <v>1</v>
       </c>
       <c r="CU8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CV8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CW8" t="n">
         <v>1</v>
       </c>
       <c r="CX8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CY8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CZ8" t="n">
         <v>0</v>
@@ -4658,10 +4658,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.33</v>
+        <v>0.5</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4694,105 +4694,89 @@
         <v>11</v>
       </c>
       <c r="DP8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU8" t="b">
         <v>0</v>
       </c>
       <c r="DV8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="DX8" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="DY8" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="DZ8" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="EA8" t="inlineStr">
         <is>
-          <t>3.34</t>
-        </is>
-      </c>
-      <c r="EB8" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EC8" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="ED8" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="EE8" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr"/>
+      <c r="EC8" t="inlineStr"/>
+      <c r="ED8" t="inlineStr"/>
+      <c r="EE8" t="inlineStr"/>
       <c r="EF8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EG8" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="EH8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EI8" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EJ8" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EK8" t="inlineStr"/>
       <c r="EL8" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="EM8" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="EN8" t="inlineStr">
@@ -4802,12 +4786,12 @@
       </c>
       <c r="EO8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EP8" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.27</t>
         </is>
       </c>
     </row>
@@ -4827,40 +4811,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>45879.70833333334</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
         <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -4869,122 +4853,122 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
         <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U9" t="n">
         <v>8</v>
       </c>
       <c r="V9" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="W9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="X9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y9" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="Z9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Estádio Dr. Jorge Sampaio</t>
+          <t>Estádio Pina Manique</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Rua da Paradela, Pedroso, Vila Nova de Gaia</t>
+          <t>Rua Monsanto, Lisboa</t>
         </is>
       </c>
       <c r="AC9" t="n">
         <v>1</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AH9" t="n">
         <v>1.33</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AO9" t="n">
         <v>2.45</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB9" t="n">
-        <v>-1</v>
+        <v>4880</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
@@ -5008,130 +4992,130 @@
         <v>3</v>
       </c>
       <c r="BJ9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BK9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BN9" t="n">
         <v>4</v>
       </c>
       <c r="BO9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BS9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BU9" t="n">
         <v>1</v>
       </c>
       <c r="BV9" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="BW9" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>51</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>5</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS9" t="n">
         <v>23</v>
       </c>
-      <c r="BX9" t="n">
-        <v>73</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>64</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR9" t="n">
+      <c r="CT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU9" t="n">
         <v>17</v>
       </c>
-      <c r="CS9" t="n">
-        <v>30</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>18</v>
-      </c>
       <c r="CV9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CW9" t="n">
         <v>1</v>
       </c>
       <c r="CX9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CY9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CZ9" t="n">
         <v>0</v>
@@ -5146,10 +5130,10 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -5182,89 +5166,105 @@
         <v>11</v>
       </c>
       <c r="DP9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU9" t="b">
         <v>0</v>
       </c>
       <c r="DV9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="DX9" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="DY9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="DZ9" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="EA9" t="inlineStr">
         <is>
-          <t>3.42</t>
-        </is>
-      </c>
-      <c r="EB9" t="inlineStr"/>
-      <c r="EC9" t="inlineStr"/>
-      <c r="ED9" t="inlineStr"/>
-      <c r="EE9" t="inlineStr"/>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EJ9" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EK9" t="inlineStr"/>
       <c r="EL9" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="EM9" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="EN9" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="EO9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EP9" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.09</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE10" t="n">
         <v>2</v>
@@ -7195,161 +7195,161 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
         <v>45885.60416666666</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>15</v>
+      </c>
+      <c r="M14" t="n">
         <v>4</v>
       </c>
-      <c r="K14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
         <v>6</v>
       </c>
       <c r="U14" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="X14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="Z14" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Estádio Municipal do Fontelo</t>
+          <t>Estádio do Lusitânia FC</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Avenida José Relvas, Viseu</t>
+          <t>, Lourosa</t>
         </is>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.7</v>
+        <v>2.16</v>
       </c>
       <c r="AO14" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB14" t="n">
         <v>-1</v>
@@ -7373,133 +7373,133 @@
         <v>1</v>
       </c>
       <c r="BI14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BK14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BL14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BN14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BO14" t="n">
         <v>1</v>
       </c>
       <c r="BP14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BR14" t="n">
         <v>1</v>
       </c>
       <c r="BS14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BU14" t="n">
         <v>1</v>
       </c>
       <c r="BV14" t="n">
+        <v>68</v>
+      </c>
+      <c r="BW14" t="n">
         <v>64</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="BX14" t="n">
+        <v>105</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS14" t="n">
         <v>22</v>
       </c>
-      <c r="BX14" t="n">
-        <v>79</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>67</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>28</v>
-      </c>
-      <c r="CS14" t="n">
-        <v>27</v>
-      </c>
       <c r="CT14" t="n">
         <v>1</v>
       </c>
       <c r="CU14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="CV14" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="CW14" t="n">
         <v>1</v>
       </c>
       <c r="CX14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CY14" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CZ14" t="n">
         <v>0</v>
@@ -7514,10 +7514,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>2</v>
+        <v>0.83</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.5</v>
+        <v>1.67</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7526,10 +7526,10 @@
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DI14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DJ14" t="n">
         <v>0</v>
@@ -7550,16 +7550,16 @@
         <v>11</v>
       </c>
       <c r="DP14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT14" t="b">
         <v>0</v>
@@ -7568,94 +7568,86 @@
         <v>0</v>
       </c>
       <c r="DV14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW14" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="DX14" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="DY14" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="DZ14" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="EA14" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="EB14" t="inlineStr"/>
       <c r="EC14" t="inlineStr"/>
-      <c r="ED14" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EE14" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
+      <c r="ED14" t="inlineStr"/>
+      <c r="EE14" t="inlineStr"/>
       <c r="EF14" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EG14" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="EH14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EI14" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EJ14" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EK14" t="inlineStr"/>
       <c r="EL14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="EM14" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="EN14" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="EO14" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EP14" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.28</t>
         </is>
       </c>
     </row>
@@ -7675,161 +7667,161 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
         <v>45885.60416666666</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>4</v>
       </c>
-      <c r="J15" t="n">
-        <v>8</v>
-      </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="T15" t="n">
         <v>6</v>
       </c>
       <c r="U15" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="X15" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y15" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="Z15" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Estádio do Lusitânia FC</t>
+          <t>Estádio Municipal do Fontelo</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>, Lourosa</t>
+          <t>Avenida José Relvas, Viseu</t>
         </is>
       </c>
       <c r="AC15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AI15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AP15" t="n">
         <v>2.05</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM15" t="n">
+      <c r="AQ15" t="n">
         <v>1.55</v>
       </c>
-      <c r="AN15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AR15" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AU15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
         <v>-1</v>
@@ -7853,133 +7845,133 @@
         <v>1</v>
       </c>
       <c r="BI15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BK15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="BL15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BN15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BO15" t="n">
         <v>1</v>
       </c>
       <c r="BP15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR15" t="n">
         <v>1</v>
       </c>
       <c r="BS15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>64</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>67</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX15" t="n">
         <v>4</v>
       </c>
-      <c r="BU15" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>68</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>64</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>105</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>90</v>
-      </c>
-      <c r="BZ15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CA15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CB15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="CC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI15" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ15" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN15" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ15" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS15" t="n">
-        <v>22</v>
-      </c>
-      <c r="CT15" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU15" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV15" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW15" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX15" t="n">
-        <v>7</v>
-      </c>
       <c r="CY15" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="CZ15" t="n">
         <v>0</v>
@@ -7994,10 +7986,10 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.83</v>
+        <v>2.17</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.67</v>
+        <v>0.5</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -8006,10 +7998,10 @@
         <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ15" t="n">
         <v>0</v>
@@ -8030,16 +8022,16 @@
         <v>11</v>
       </c>
       <c r="DP15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT15" t="b">
         <v>0</v>
@@ -8048,86 +8040,94 @@
         <v>0</v>
       </c>
       <c r="DV15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW15" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="DX15" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="DY15" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="DZ15" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="EA15" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EB15" t="inlineStr"/>
       <c r="EC15" t="inlineStr"/>
-      <c r="ED15" t="inlineStr"/>
-      <c r="EE15" t="inlineStr"/>
+      <c r="ED15" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EE15" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
       <c r="EF15" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EG15" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="EH15" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EI15" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EJ15" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EK15" t="inlineStr"/>
       <c r="EL15" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="EM15" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="EN15" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="EO15" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EP15" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.36</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP18" t="b">
         <v>0</v>
@@ -9917,7 +9917,7 @@
         <v>0.83</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DF19" t="n">
         <v>0</v>
@@ -12338,7 +12338,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE24" t="n">
         <v>1.83</v>
@@ -13285,7 +13285,7 @@
         <v>1.29</v>
       </c>
       <c r="DE26" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -13315,7 +13315,7 @@
         <v>3.03</v>
       </c>
       <c r="DO26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -16165,7 +16165,7 @@
         <v>1.4</v>
       </c>
       <c r="DE32" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DF32" t="n">
         <v>3</v>
@@ -16811,164 +16811,164 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>45900.41666666666</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
+        <v>7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>14</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="n">
         <v>4</v>
       </c>
-      <c r="K34" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" t="n">
-        <v>6</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3</v>
-      </c>
-      <c r="R34" t="n">
-        <v>3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>6</v>
-      </c>
-      <c r="T34" t="n">
-        <v>6</v>
-      </c>
       <c r="U34" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="V34" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W34" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="X34" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y34" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="Z34" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Estádio de São Lúis</t>
+          <t>CGD Stadium Aurélio Pereira</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Rua do Sporting Club Farense, Faro</t>
+          <t>, Alcochete</t>
         </is>
       </c>
       <c r="AC34" t="n">
         <v>3</v>
       </c>
       <c r="AD34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AF34" t="n">
         <v>3</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AJ34" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="AO34" t="n">
-        <v>2.88</v>
+        <v>2.17</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AR34" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AU34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA34" t="n">
         <v>1</v>
       </c>
       <c r="BB34" t="n">
-        <v>177</v>
+        <v>1029</v>
       </c>
       <c r="BC34" t="n">
         <v>0</v>
@@ -16989,64 +16989,64 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL34" t="n">
         <v>1</v>
       </c>
       <c r="BM34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BO34" t="n">
         <v>1</v>
       </c>
       <c r="BP34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ34" t="n">
         <v>2</v>
       </c>
       <c r="BR34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU34" t="n">
         <v>1</v>
       </c>
       <c r="BV34" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="BW34" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BX34" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="BY34" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="BZ34" t="n">
-        <v>1.28</v>
+        <v>3.01</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.14</v>
+        <v>0.51</v>
       </c>
       <c r="CB34" t="n">
-        <v>2.42</v>
+        <v>3.52</v>
       </c>
       <c r="CC34" t="n">
         <v>0</v>
@@ -17076,10 +17076,10 @@
         <v>0</v>
       </c>
       <c r="CL34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
@@ -17094,34 +17094,34 @@
         <v>1</v>
       </c>
       <c r="CR34" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="CS34" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="CT34" t="n">
         <v>1</v>
       </c>
       <c r="CU34" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CV34" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="CW34" t="n">
         <v>1</v>
       </c>
       <c r="CX34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CY34" t="n">
         <v>6</v>
       </c>
       <c r="CZ34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DB34" t="n">
         <v>0</v>
@@ -17130,37 +17130,37 @@
         <v>50</v>
       </c>
       <c r="DD34" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="DE34" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="DF34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DH34" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="DI34" t="n">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="DJ34" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DK34" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DL34" t="n">
-        <v>1.77</v>
+        <v>1.05</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.65</v>
+        <v>0.68</v>
       </c>
       <c r="DN34" t="n">
-        <v>3.42</v>
+        <v>1.73</v>
       </c>
       <c r="DO34" t="n">
         <v>11</v>
@@ -17172,7 +17172,7 @@
         <v>1</v>
       </c>
       <c r="DR34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS34" t="b">
         <v>0</v>
@@ -17190,60 +17190,80 @@
       <c r="DX34" t="inlineStr"/>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="EB34" t="inlineStr"/>
-      <c r="EC34" t="inlineStr"/>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EB34" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EC34" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
       <c r="ED34" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EE34" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EF34" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EG34" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="EH34" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EI34" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EJ34" t="inlineStr">
         <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EK34" t="inlineStr"/>
-      <c r="EL34" t="inlineStr"/>
-      <c r="EM34" t="inlineStr"/>
-      <c r="EN34" t="inlineStr"/>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EK34" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="EL34" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="EM34" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="EN34" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
       <c r="EO34" t="inlineStr"/>
       <c r="EP34" t="inlineStr"/>
     </row>
@@ -17263,40 +17283,40 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
         <v>45900.41666666666</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M35" t="n">
         <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -17305,122 +17325,122 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
+        <v>3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>9</v>
+      </c>
+      <c r="V35" t="n">
+        <v>9</v>
+      </c>
+      <c r="W35" t="n">
+        <v>12</v>
+      </c>
+      <c r="X35" t="n">
         <v>14</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="n">
-        <v>4</v>
-      </c>
-      <c r="U35" t="n">
-        <v>24</v>
-      </c>
-      <c r="V35" t="n">
-        <v>4</v>
-      </c>
-      <c r="W35" t="n">
-        <v>17</v>
-      </c>
-      <c r="X35" t="n">
-        <v>10</v>
-      </c>
       <c r="Y35" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="Z35" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>CGD Stadium Aurélio Pereira</t>
+          <t>Estádio de São Lúis</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>, Alcochete</t>
+          <t>Rua do Sporting Club Farense, Faro</t>
         </is>
       </c>
       <c r="AC35" t="n">
         <v>3</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AF35" t="n">
         <v>3</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AJ35" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AO35" t="n">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR35" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AU35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA35" t="n">
         <v>1</v>
       </c>
       <c r="BB35" t="n">
-        <v>1029</v>
+        <v>177</v>
       </c>
       <c r="BC35" t="n">
         <v>0</v>
@@ -17441,64 +17461,64 @@
         <v>1</v>
       </c>
       <c r="BI35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK35" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN35" t="n">
         <v>4</v>
       </c>
-      <c r="BL35" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM35" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN35" t="n">
-        <v>5</v>
-      </c>
       <c r="BO35" t="n">
         <v>1</v>
       </c>
       <c r="BP35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ35" t="n">
         <v>2</v>
       </c>
       <c r="BR35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU35" t="n">
         <v>1</v>
       </c>
       <c r="BV35" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="BW35" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BX35" t="n">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="BY35" t="n">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="BZ35" t="n">
-        <v>3.01</v>
+        <v>1.28</v>
       </c>
       <c r="CA35" t="n">
-        <v>0.51</v>
+        <v>1.14</v>
       </c>
       <c r="CB35" t="n">
-        <v>3.52</v>
+        <v>2.42</v>
       </c>
       <c r="CC35" t="n">
         <v>0</v>
@@ -17528,10 +17548,10 @@
         <v>0</v>
       </c>
       <c r="CL35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN35" t="n">
         <v>0</v>
@@ -17546,34 +17566,34 @@
         <v>1</v>
       </c>
       <c r="CR35" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="CS35" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="CT35" t="n">
         <v>1</v>
       </c>
       <c r="CU35" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CV35" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="CW35" t="n">
         <v>1</v>
       </c>
       <c r="CX35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CY35" t="n">
         <v>6</v>
       </c>
       <c r="CZ35" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA35" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DB35" t="n">
         <v>0</v>
@@ -17582,37 +17602,37 @@
         <v>50</v>
       </c>
       <c r="DD35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DE35" t="n">
         <v>2.4</v>
       </c>
-      <c r="DE35" t="n">
-        <v>0.5</v>
-      </c>
       <c r="DF35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DG35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DH35" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="DI35" t="n">
-        <v>0.67</v>
+        <v>2</v>
       </c>
       <c r="DJ35" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DK35" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DL35" t="n">
-        <v>1.05</v>
+        <v>1.77</v>
       </c>
       <c r="DM35" t="n">
-        <v>0.68</v>
+        <v>1.65</v>
       </c>
       <c r="DN35" t="n">
-        <v>1.73</v>
+        <v>3.42</v>
       </c>
       <c r="DO35" t="n">
         <v>11</v>
@@ -17624,7 +17644,7 @@
         <v>1</v>
       </c>
       <c r="DR35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS35" t="b">
         <v>0</v>
@@ -17642,80 +17662,60 @@
       <c r="DX35" t="inlineStr"/>
       <c r="DY35" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="DZ35" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EA35" t="inlineStr">
         <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EB35" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EC35" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EB35" t="inlineStr"/>
+      <c r="EC35" t="inlineStr"/>
       <c r="ED35" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EE35" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EF35" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EG35" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="EH35" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EI35" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EJ35" t="inlineStr">
         <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EK35" t="n">
-        <v>22.98</v>
-      </c>
-      <c r="EL35" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="EM35" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="EN35" t="inlineStr">
-        <is>
-          <t>82%</t>
-        </is>
-      </c>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EK35" t="inlineStr"/>
+      <c r="EL35" t="inlineStr"/>
+      <c r="EM35" t="inlineStr"/>
+      <c r="EN35" t="inlineStr"/>
       <c r="EO35" t="inlineStr"/>
       <c r="EP35" t="inlineStr"/>
     </row>
@@ -18054,7 +18054,7 @@
         <v>50</v>
       </c>
       <c r="DD36" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE36" t="n">
         <v>0.8</v>
@@ -19453,7 +19453,7 @@
         <v>0.83</v>
       </c>
       <c r="DE39" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF39" t="n">
         <v>1</v>
@@ -22746,7 +22746,7 @@
         <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE46" t="n">
         <v>1.33</v>
@@ -22779,7 +22779,7 @@
         <v>2.43</v>
       </c>
       <c r="DO46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -23221,7 +23221,7 @@
         <v>2</v>
       </c>
       <c r="DE47" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DF47" t="n">
         <v>3</v>
@@ -23355,37 +23355,37 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
         <v>45927.41666666666</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" t="n">
         <v>6</v>
       </c>
-      <c r="J48" t="n">
-        <v>7</v>
-      </c>
       <c r="K48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L48" t="n">
         <v>12</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
         <v>3</v>
@@ -23397,128 +23397,128 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R48" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U48" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="V48" t="n">
+        <v>12</v>
+      </c>
+      <c r="W48" t="n">
         <v>17</v>
       </c>
-      <c r="W48" t="n">
-        <v>7</v>
-      </c>
       <c r="X48" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Y48" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="Z48" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Caixa Futebol Campus</t>
+          <t>Estádio Municipal 25 de Abril</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>, Seixal</t>
+          <t>Rua Futebol Clube de Penafiel, Penafiel</t>
         </is>
       </c>
       <c r="AC48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD48" t="n">
         <v>3</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="AF48" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.56</v>
+        <v>2.13</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AI48" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AP48" t="n">
         <v>2.1</v>
       </c>
-      <c r="AJ48" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AQ48" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AS48" t="n">
-        <v>2.82</v>
+        <v>2.73</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AU48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV48" t="n">
         <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ48" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>-1</v>
+        <v>182</v>
       </c>
       <c r="BC48" t="n">
         <v>0</v>
       </c>
       <c r="BD48" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="BE48" t="n">
         <v>0</v>
@@ -23533,37 +23533,37 @@
         <v>1</v>
       </c>
       <c r="BI48" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM48" t="n">
         <v>4</v>
       </c>
-      <c r="BJ48" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK48" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL48" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM48" t="n">
-        <v>6</v>
-      </c>
       <c r="BN48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BO48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BT48" t="n">
         <v>3</v>
@@ -23572,25 +23572,25 @@
         <v>1</v>
       </c>
       <c r="BV48" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="BW48" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="BX48" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="BY48" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="BZ48" t="n">
-        <v>2.42</v>
+        <v>1.51</v>
       </c>
       <c r="CA48" t="n">
-        <v>1.99</v>
+        <v>1.64</v>
       </c>
       <c r="CB48" t="n">
-        <v>4.41</v>
+        <v>3.15</v>
       </c>
       <c r="CC48" t="n">
         <v>0</v>
@@ -23626,85 +23626,85 @@
         <v>0</v>
       </c>
       <c r="CN48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ48" t="n">
         <v>1</v>
       </c>
       <c r="CR48" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS48" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU48" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV48" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX48" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY48" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ48" t="n">
         <v>25</v>
-      </c>
-      <c r="CS48" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU48" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV48" t="n">
-        <v>7</v>
-      </c>
-      <c r="CW48" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX48" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY48" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ48" t="n">
-        <v>50</v>
       </c>
       <c r="DA48" t="n">
         <v>75</v>
       </c>
       <c r="DB48" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DC48" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DD48" t="n">
-        <v>0.83</v>
+        <v>1.2</v>
       </c>
       <c r="DE48" t="n">
-        <v>1.67</v>
+        <v>0.4</v>
       </c>
       <c r="DF48" t="n">
         <v>0.5</v>
       </c>
       <c r="DG48" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="DH48" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="DI48" t="n">
         <v>1.4</v>
       </c>
       <c r="DJ48" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DK48" t="n">
         <v>25</v>
       </c>
       <c r="DL48" t="n">
-        <v>2.57</v>
+        <v>1.3</v>
       </c>
       <c r="DM48" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="DN48" t="n">
-        <v>4.03</v>
+        <v>2.69</v>
       </c>
       <c r="DO48" t="n">
         <v>11</v>
@@ -23716,43 +23716,43 @@
         <v>1</v>
       </c>
       <c r="DR48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW48" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DX48" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="DY48" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="DZ48" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EA48" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EB48" t="inlineStr"/>
@@ -23761,38 +23761,38 @@
       <c r="EE48" t="inlineStr"/>
       <c r="EF48" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EG48" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="EH48" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EI48" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EJ48" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EK48" t="n">
-        <v>18.8</v>
+        <v>23.33</v>
       </c>
       <c r="EL48" t="n">
-        <v>12.88</v>
+        <v>4.43</v>
       </c>
       <c r="EM48" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="EN48" t="inlineStr">
@@ -23802,12 +23802,12 @@
       </c>
       <c r="EO48" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EP48" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -23827,37 +23827,37 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
         <v>45927.41666666666</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L49" t="n">
         <v>12</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
         <v>3</v>
@@ -23869,128 +23869,128 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
+        <v>10</v>
+      </c>
+      <c r="R49" t="n">
+        <v>9</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U49" t="n">
+        <v>20</v>
+      </c>
+      <c r="V49" t="n">
+        <v>17</v>
+      </c>
+      <c r="W49" t="n">
+        <v>7</v>
+      </c>
+      <c r="X49" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Caixa Futebol Campus</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>, Seixal</t>
+        </is>
+      </c>
+      <c r="AC49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU49" t="n">
         <v>6</v>
       </c>
-      <c r="R49" t="n">
-        <v>6</v>
-      </c>
-      <c r="S49" t="n">
-        <v>6</v>
-      </c>
-      <c r="T49" t="n">
-        <v>6</v>
-      </c>
-      <c r="U49" t="n">
-        <v>12</v>
-      </c>
-      <c r="V49" t="n">
-        <v>12</v>
-      </c>
-      <c r="W49" t="n">
-        <v>17</v>
-      </c>
-      <c r="X49" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>42</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>Estádio Municipal 25 de Abril</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>Rua Futebol Clube de Penafiel, Penafiel</t>
-        </is>
-      </c>
-      <c r="AC49" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>2</v>
-      </c>
       <c r="AV49" t="n">
         <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB49" t="n">
-        <v>182</v>
+        <v>-1</v>
       </c>
       <c r="BC49" t="n">
         <v>0</v>
       </c>
       <c r="BD49" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="BE49" t="n">
         <v>0</v>
@@ -24005,37 +24005,37 @@
         <v>1</v>
       </c>
       <c r="BI49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BJ49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK49" t="n">
         <v>3</v>
       </c>
       <c r="BL49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BM49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BN49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BO49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BT49" t="n">
         <v>3</v>
@@ -24044,25 +24044,25 @@
         <v>1</v>
       </c>
       <c r="BV49" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="BW49" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="BX49" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="BY49" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="BZ49" t="n">
-        <v>1.51</v>
+        <v>2.42</v>
       </c>
       <c r="CA49" t="n">
-        <v>1.64</v>
+        <v>1.99</v>
       </c>
       <c r="CB49" t="n">
-        <v>3.15</v>
+        <v>4.41</v>
       </c>
       <c r="CC49" t="n">
         <v>0</v>
@@ -24098,85 +24098,85 @@
         <v>0</v>
       </c>
       <c r="CN49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ49" t="n">
         <v>1</v>
       </c>
       <c r="CR49" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="CS49" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="CT49" t="n">
         <v>1</v>
       </c>
       <c r="CU49" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CV49" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="CW49" t="n">
         <v>1</v>
       </c>
       <c r="CX49" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="CY49" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="CZ49" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DA49" t="n">
         <v>75</v>
       </c>
       <c r="DB49" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DC49" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD49" t="n">
-        <v>1.2</v>
+        <v>0.83</v>
       </c>
       <c r="DE49" t="n">
-        <v>0.4</v>
+        <v>1.67</v>
       </c>
       <c r="DF49" t="n">
         <v>0.5</v>
       </c>
       <c r="DG49" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="DH49" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="DI49" t="n">
         <v>1.4</v>
       </c>
       <c r="DJ49" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK49" t="n">
         <v>25</v>
       </c>
       <c r="DL49" t="n">
-        <v>1.3</v>
+        <v>2.57</v>
       </c>
       <c r="DM49" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="DN49" t="n">
-        <v>2.69</v>
+        <v>4.03</v>
       </c>
       <c r="DO49" t="n">
         <v>11</v>
@@ -24188,43 +24188,43 @@
         <v>1</v>
       </c>
       <c r="DR49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW49" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="DX49" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="DY49" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="DZ49" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="EA49" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EB49" t="inlineStr"/>
@@ -24233,38 +24233,38 @@
       <c r="EE49" t="inlineStr"/>
       <c r="EF49" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EG49" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="EH49" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EI49" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EJ49" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EK49" t="n">
-        <v>23.33</v>
+        <v>18.8</v>
       </c>
       <c r="EL49" t="n">
-        <v>4.43</v>
+        <v>12.88</v>
       </c>
       <c r="EM49" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="EN49" t="inlineStr">
@@ -24274,12 +24274,12 @@
       </c>
       <c r="EO49" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EP49" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.13</t>
         </is>
       </c>
     </row>
@@ -25090,7 +25090,7 @@
         <v>75</v>
       </c>
       <c r="DD51" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE51" t="n">
         <v>1.2</v>
@@ -26987,7 +26987,7 @@
         <v>2.97</v>
       </c>
       <c r="DO55" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -29370,7 +29370,7 @@
         <v>67</v>
       </c>
       <c r="DD60" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE60" t="n">
         <v>0.5</v>
@@ -30789,7 +30789,7 @@
         <v>0.83</v>
       </c>
       <c r="DE63" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF63" t="n">
         <v>0.67</v>
@@ -33477,7 +33477,7 @@
         <v>2</v>
       </c>
       <c r="DE69" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DF69" t="n">
         <v>2.33</v>
@@ -34579,143 +34579,143 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
         <v>45955.60416666666</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
+        <v>3</v>
+      </c>
+      <c r="K72" t="n">
+        <v>3</v>
+      </c>
+      <c r="L72" t="n">
         <v>6</v>
-      </c>
-      <c r="K72" t="n">
-        <v>4</v>
-      </c>
-      <c r="L72" t="n">
-        <v>10</v>
       </c>
       <c r="M72" t="n">
         <v>4</v>
       </c>
       <c r="N72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R72" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S72" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T72" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U72" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V72" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="W72" t="n">
         <v>13</v>
       </c>
       <c r="X72" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y72" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="Z72" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Estádio Marcolino de Castro</t>
+          <t>Estádio Municipal do Fontelo</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Avenida 25 de Abril 14, Santa Maria da Feira</t>
+          <t>Avenida José Relvas, Viseu</t>
         </is>
       </c>
       <c r="AC72" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE72" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AF72" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="AG72" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AI72" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AJ72" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AK72" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AL72" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AM72" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AN72" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AO72" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AS72" t="n">
         <v>2.56</v>
       </c>
-      <c r="AP72" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AQ72" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR72" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AS72" t="n">
-        <v>2.85</v>
-      </c>
       <c r="AT72" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AU72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV72" t="n">
         <v>0</v>
@@ -34724,25 +34724,25 @@
         <v>0</v>
       </c>
       <c r="AX72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA72" t="n">
         <v>0</v>
       </c>
       <c r="BB72" t="n">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="BC72" t="n">
         <v>0</v>
       </c>
       <c r="BD72" t="n">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="BE72" t="n">
         <v>0</v>
@@ -34751,28 +34751,28 @@
         <v>-1</v>
       </c>
       <c r="BG72" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH72" t="n">
         <v>1</v>
       </c>
       <c r="BI72" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BJ72" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BK72" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BL72" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BM72" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="BN72" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BO72" t="n">
         <v>1</v>
@@ -34781,40 +34781,40 @@
         <v>2</v>
       </c>
       <c r="BQ72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS72" t="n">
         <v>3</v>
       </c>
       <c r="BT72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BU72" t="n">
         <v>1</v>
       </c>
       <c r="BV72" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="BW72" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="BX72" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="BY72" t="n">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="BZ72" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="CA72" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="CB72" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="CC72" t="n">
         <v>0</v>
@@ -34847,31 +34847,31 @@
         <v>0</v>
       </c>
       <c r="CM72" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="CN72" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ72" t="n">
         <v>1</v>
       </c>
       <c r="CR72" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="CS72" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CT72" t="n">
         <v>1</v>
       </c>
       <c r="CU72" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CV72" t="n">
         <v>13</v>
@@ -34880,64 +34880,64 @@
         <v>1</v>
       </c>
       <c r="CX72" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CY72" t="n">
         <v>12</v>
       </c>
       <c r="CZ72" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="DA72" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="DB72" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC72" t="n">
         <v>67</v>
       </c>
-      <c r="DC72" t="n">
-        <v>84</v>
-      </c>
       <c r="DD72" t="n">
-        <v>1.4</v>
+        <v>2.17</v>
       </c>
       <c r="DE72" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="DF72" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="DG72" t="n">
-        <v>0.67</v>
+        <v>2.33</v>
       </c>
       <c r="DH72" t="n">
-        <v>1.13</v>
+        <v>0.86</v>
       </c>
       <c r="DI72" t="n">
-        <v>0.57</v>
+        <v>1.86</v>
       </c>
       <c r="DJ72" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="DK72" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL72" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="DM72" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="DN72" t="n">
-        <v>3.12</v>
+        <v>3.36</v>
       </c>
       <c r="DO72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
       </c>
       <c r="DQ72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR72" t="b">
         <v>0</v>
@@ -34956,27 +34956,27 @@
       </c>
       <c r="DW72" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="DX72" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="DY72" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="DZ72" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EA72" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="EB72" t="inlineStr"/>
@@ -34985,53 +34985,41 @@
       <c r="EE72" t="inlineStr"/>
       <c r="EF72" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EG72" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="EH72" t="inlineStr">
         <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EI72" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EJ72" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EK72" t="inlineStr"/>
+      <c r="EL72" t="inlineStr"/>
+      <c r="EM72" t="inlineStr"/>
+      <c r="EN72" t="inlineStr"/>
+      <c r="EO72" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="EI72" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EJ72" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="EK72" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="EL72" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="EM72" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="EN72" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="EO72" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
       <c r="EP72" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.23</t>
         </is>
       </c>
     </row>
@@ -35051,143 +35039,143 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
         <v>45955.60416666666</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M73" t="n">
         <v>4</v>
       </c>
       <c r="N73" t="n">
+        <v>3</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>3</v>
+      </c>
+      <c r="R73" t="n">
         <v>5</v>
       </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>7</v>
-      </c>
-      <c r="R73" t="n">
-        <v>2</v>
-      </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U73" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V73" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="W73" t="n">
         <v>13</v>
       </c>
       <c r="X73" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y73" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="Z73" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Estádio Municipal do Fontelo</t>
+          <t>Estádio Marcolino de Castro</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Avenida José Relvas, Viseu</t>
+          <t>Avenida 25 de Abril 14, Santa Maria da Feira</t>
         </is>
       </c>
       <c r="AC73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE73" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AF73" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="AG73" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AI73" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AJ73" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AK73" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AL73" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AM73" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AN73" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AO73" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AR73" t="n">
-        <v>3.28</v>
+        <v>2.65</v>
       </c>
       <c r="AS73" t="n">
-        <v>2.56</v>
+        <v>2.85</v>
       </c>
       <c r="AT73" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AU73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV73" t="n">
         <v>0</v>
@@ -35196,25 +35184,25 @@
         <v>0</v>
       </c>
       <c r="AX73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA73" t="n">
         <v>0</v>
       </c>
       <c r="BB73" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="BC73" t="n">
         <v>0</v>
       </c>
       <c r="BD73" t="n">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="BE73" t="n">
         <v>0</v>
@@ -35223,28 +35211,28 @@
         <v>-1</v>
       </c>
       <c r="BG73" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH73" t="n">
         <v>1</v>
       </c>
       <c r="BI73" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BJ73" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BK73" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BL73" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BM73" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BN73" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BO73" t="n">
         <v>1</v>
@@ -35253,40 +35241,40 @@
         <v>2</v>
       </c>
       <c r="BQ73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS73" t="n">
         <v>3</v>
       </c>
       <c r="BT73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BU73" t="n">
         <v>1</v>
       </c>
       <c r="BV73" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="BW73" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="BX73" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="BY73" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="BZ73" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="CA73" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="CB73" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="CC73" t="n">
         <v>0</v>
@@ -35319,31 +35307,31 @@
         <v>0</v>
       </c>
       <c r="CM73" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN73" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ73" t="n">
         <v>1</v>
       </c>
       <c r="CR73" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="CS73" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="CT73" t="n">
         <v>1</v>
       </c>
       <c r="CU73" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CV73" t="n">
         <v>13</v>
@@ -35352,55 +35340,55 @@
         <v>1</v>
       </c>
       <c r="CX73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CY73" t="n">
         <v>12</v>
       </c>
       <c r="CZ73" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="DA73" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB73" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC73" t="n">
         <v>84</v>
       </c>
-      <c r="DB73" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC73" t="n">
-        <v>67</v>
-      </c>
       <c r="DD73" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="DE73" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DF73" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="DG73" t="n">
-        <v>2.33</v>
+        <v>0.67</v>
       </c>
       <c r="DH73" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DI73" t="n">
-        <v>1.86</v>
+        <v>0.57</v>
       </c>
       <c r="DJ73" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="DK73" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL73" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="DM73" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="DN73" t="n">
-        <v>3.36</v>
+        <v>3.12</v>
       </c>
       <c r="DO73" t="n">
         <v>11</v>
@@ -35409,7 +35397,7 @@
         <v>1</v>
       </c>
       <c r="DQ73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR73" t="b">
         <v>0</v>
@@ -35428,27 +35416,27 @@
       </c>
       <c r="DW73" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DX73" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="DY73" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="DZ73" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EA73" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EB73" t="inlineStr"/>
@@ -35457,41 +35445,53 @@
       <c r="EE73" t="inlineStr"/>
       <c r="EF73" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EG73" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="EH73" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EI73" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EJ73" t="inlineStr">
         <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="EK73" t="inlineStr"/>
-      <c r="EL73" t="inlineStr"/>
-      <c r="EM73" t="inlineStr"/>
-      <c r="EN73" t="inlineStr"/>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EK73" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="EL73" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="EM73" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EN73" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="EO73" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EP73" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -35833,7 +35833,7 @@
         <v>0.8</v>
       </c>
       <c r="DE74" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF74" t="n">
         <v>0</v>
@@ -36786,7 +36786,7 @@
         <v>100</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE76" t="n">
         <v>0.8</v>
@@ -38259,7 +38259,7 @@
         <v>2.83</v>
       </c>
       <c r="DO79" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39645,7 +39645,7 @@
         <v>2</v>
       </c>
       <c r="DE82" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF82" t="n">
         <v>2.5</v>
@@ -40593,7 +40593,7 @@
         <v>1.6</v>
       </c>
       <c r="DE84" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DF84" t="n">
         <v>1.25</v>
@@ -41062,7 +41062,7 @@
         <v>75</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE85" t="n">
         <v>2.4</v>
@@ -41095,7 +41095,7 @@
         <v>2.72</v>
       </c>
       <c r="DO85" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -42510,7 +42510,7 @@
         <v>63</v>
       </c>
       <c r="DD88" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE88" t="n">
         <v>1.2</v>
@@ -47879,44 +47879,44 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
         <v>45984.45833333334</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L100" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -47925,101 +47925,101 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R100" t="n">
         <v>3</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U100" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V100" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W100" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="X100" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Y100" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="Z100" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Estádio Municipal Eng. Manuel Branco Teixeira</t>
+          <t>Estádio Dr. Jorge Sampaio</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>Avenida do Estádio Municipal, Chaves</t>
+          <t>Rua da Paradela, Pedroso, Vila Nova de Gaia</t>
         </is>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE100" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AF100" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ100" t="n">
         <v>3.2</v>
       </c>
-      <c r="AG100" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH100" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI100" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ100" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AK100" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AL100" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AM100" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AN100" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AO100" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AR100" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="AS100" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AU100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV100" t="n">
         <v>0</v>
@@ -48028,25 +48028,25 @@
         <v>0</v>
       </c>
       <c r="AX100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY100" t="n">
         <v>0</v>
       </c>
       <c r="AZ100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA100" t="n">
         <v>0</v>
       </c>
       <c r="BB100" t="n">
-        <v>-1</v>
+        <v>1037</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
@@ -48058,187 +48058,187 @@
         <v>2</v>
       </c>
       <c r="BH100" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM100" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BN100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BO100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BU100" t="n">
         <v>1</v>
       </c>
       <c r="BV100" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW100" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX100" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY100" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ100" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR100" t="n">
+        <v>9</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV100" t="n">
+        <v>23</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY100" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ100" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA100" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB100" t="n">
         <v>55</v>
       </c>
-      <c r="BW100" t="n">
-        <v>47</v>
-      </c>
-      <c r="BX100" t="n">
-        <v>81</v>
-      </c>
-      <c r="BY100" t="n">
-        <v>83</v>
-      </c>
-      <c r="BZ100" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="CA100" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="CB100" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CC100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO100" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CP100" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CQ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR100" t="n">
-        <v>16</v>
-      </c>
-      <c r="CS100" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU100" t="n">
-        <v>12</v>
-      </c>
-      <c r="CV100" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX100" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY100" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ100" t="n">
-        <v>20</v>
-      </c>
-      <c r="DA100" t="n">
-        <v>60</v>
-      </c>
-      <c r="DB100" t="n">
-        <v>20</v>
-      </c>
       <c r="DC100" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="DD100" t="n">
         <v>1.17</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.83</v>
+        <v>1.2</v>
       </c>
       <c r="DF100" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DG100" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH100" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DI100" t="n">
         <v>1.2</v>
       </c>
-      <c r="DG100" t="n">
-        <v>2</v>
-      </c>
-      <c r="DH100" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="DI100" t="n">
-        <v>2.2</v>
-      </c>
       <c r="DJ100" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="DK100" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="DL100" t="n">
-        <v>1.6</v>
+        <v>1.13</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="DN100" t="n">
-        <v>3.07</v>
+        <v>2.33</v>
       </c>
       <c r="DO100" t="n">
         <v>11</v>
       </c>
       <c r="DP100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ100" t="b">
         <v>0</v>
@@ -48260,75 +48260,75 @@
       </c>
       <c r="DW100" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="DX100" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="DZ100" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EA100" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EB100" t="inlineStr"/>
       <c r="EC100" t="inlineStr"/>
       <c r="ED100" t="inlineStr">
         <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EE100" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EF100" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EG100" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EI100" t="inlineStr">
+        <is>
           <t>1.76</t>
         </is>
       </c>
-      <c r="EE100" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EF100" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EG100" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EH100" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EI100" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
       <c r="EJ100" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EK100" t="n">
-        <v>18.1</v>
+        <v>15.5</v>
       </c>
       <c r="EL100" t="n">
-        <v>9.57</v>
+        <v>1.59</v>
       </c>
       <c r="EM100" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="EN100" t="inlineStr">
@@ -48338,12 +48338,12 @@
       </c>
       <c r="EO100" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EP100" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.86</t>
         </is>
       </c>
     </row>
@@ -48359,147 +48359,147 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
         <v>45984.45833333334</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L101" t="n">
+        <v>4</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>3</v>
+      </c>
+      <c r="S101" t="n">
+        <v>9</v>
+      </c>
+      <c r="T101" t="n">
+        <v>7</v>
+      </c>
+      <c r="U101" t="n">
+        <v>9</v>
+      </c>
+      <c r="V101" t="n">
+        <v>10</v>
+      </c>
+      <c r="W101" t="n">
+        <v>12</v>
+      </c>
+      <c r="X101" t="n">
         <v>11</v>
       </c>
-      <c r="M101" t="n">
-        <v>2</v>
-      </c>
-      <c r="N101" t="n">
-        <v>3</v>
-      </c>
-      <c r="O101" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>5</v>
-      </c>
-      <c r="R101" t="n">
-        <v>3</v>
-      </c>
-      <c r="S101" t="n">
-        <v>6</v>
-      </c>
-      <c r="T101" t="n">
-        <v>8</v>
-      </c>
-      <c r="U101" t="n">
-        <v>11</v>
-      </c>
-      <c r="V101" t="n">
-        <v>11</v>
-      </c>
-      <c r="W101" t="n">
-        <v>23</v>
-      </c>
-      <c r="X101" t="n">
-        <v>15</v>
-      </c>
       <c r="Y101" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="Z101" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>Estádio Dr. Jorge Sampaio</t>
+          <t>Estádio Municipal Eng. Manuel Branco Teixeira</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>Rua da Paradela, Pedroso, Vila Nova de Gaia</t>
+          <t>Avenida do Estádio Municipal, Chaves</t>
         </is>
       </c>
       <c r="AC101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AF101" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AG101" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AH101" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI101" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL101" t="n">
         <v>1.85</v>
       </c>
-      <c r="AJ101" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AK101" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL101" t="n">
-        <v>2</v>
-      </c>
       <c r="AM101" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AN101" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AO101" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AR101" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="AS101" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AT101" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV101" t="n">
         <v>0</v>
@@ -48508,25 +48508,25 @@
         <v>0</v>
       </c>
       <c r="AX101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY101" t="n">
         <v>0</v>
       </c>
       <c r="AZ101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA101" t="n">
         <v>0</v>
       </c>
       <c r="BB101" t="n">
-        <v>1037</v>
+        <v>-1</v>
       </c>
       <c r="BC101" t="n">
         <v>0</v>
       </c>
       <c r="BD101" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BE101" t="n">
         <v>0</v>
@@ -48538,67 +48538,67 @@
         <v>2</v>
       </c>
       <c r="BH101" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BI101" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BJ101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM101" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BN101" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BO101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU101" t="n">
         <v>1</v>
       </c>
       <c r="BV101" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BW101" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="BX101" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="BY101" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="BZ101" t="n">
-        <v>1.28</v>
+        <v>0.97</v>
       </c>
       <c r="CA101" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="CB101" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="CC101" t="n">
         <v>0</v>
@@ -48631,94 +48631,94 @@
         <v>0</v>
       </c>
       <c r="CM101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN101" t="n">
         <v>1</v>
       </c>
       <c r="CO101" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP101" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CQ101" t="n">
         <v>1</v>
       </c>
       <c r="CR101" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="CS101" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CT101" t="n">
         <v>1</v>
       </c>
       <c r="CU101" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CV101" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="CW101" t="n">
         <v>1</v>
       </c>
       <c r="CX101" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CY101" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ101" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="DA101" t="n">
+        <v>60</v>
+      </c>
+      <c r="DB101" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC101" t="n">
         <v>80</v>
-      </c>
-      <c r="DB101" t="n">
-        <v>55</v>
-      </c>
-      <c r="DC101" t="n">
-        <v>90</v>
       </c>
       <c r="DD101" t="n">
         <v>1.17</v>
       </c>
       <c r="DE101" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DF101" t="n">
         <v>1.2</v>
       </c>
-      <c r="DF101" t="n">
-        <v>0.8</v>
-      </c>
       <c r="DG101" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DH101" t="n">
-        <v>0.8</v>
+        <v>1.45</v>
       </c>
       <c r="DI101" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="DJ101" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="DK101" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="DL101" t="n">
-        <v>1.13</v>
+        <v>1.6</v>
       </c>
       <c r="DM101" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="DN101" t="n">
-        <v>2.33</v>
+        <v>3.07</v>
       </c>
       <c r="DO101" t="n">
         <v>11</v>
       </c>
       <c r="DP101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ101" t="b">
         <v>0</v>
@@ -48740,75 +48740,75 @@
       </c>
       <c r="DW101" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="DX101" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="DY101" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="DZ101" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EA101" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EB101" t="inlineStr"/>
       <c r="EC101" t="inlineStr"/>
       <c r="ED101" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EE101" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EF101" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EG101" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EH101" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EI101" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EJ101" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EK101" t="n">
-        <v>15.5</v>
+        <v>18.1</v>
       </c>
       <c r="EL101" t="n">
-        <v>1.59</v>
+        <v>9.57</v>
       </c>
       <c r="EM101" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="EN101" t="inlineStr">
@@ -48818,12 +48818,12 @@
       </c>
       <c r="EO101" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EP101" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -49165,7 +49165,7 @@
         <v>1.57</v>
       </c>
       <c r="DE102" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="DF102" t="n">
         <v>1.33</v>
@@ -49306,6 +49306,930 @@
           <t>2.83</t>
         </is>
       </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>LigaPro_Portugal_2a_división_2025-2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>12</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>FC Penafiel</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>45990.45833333334</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>2</v>
+      </c>
+      <c r="J103" t="n">
+        <v>9</v>
+      </c>
+      <c r="K103" t="n">
+        <v>2</v>
+      </c>
+      <c r="L103" t="n">
+        <v>11</v>
+      </c>
+      <c r="M103" t="n">
+        <v>3</v>
+      </c>
+      <c r="N103" t="n">
+        <v>2</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>7</v>
+      </c>
+      <c r="R103" t="n">
+        <v>3</v>
+      </c>
+      <c r="S103" t="n">
+        <v>9</v>
+      </c>
+      <c r="T103" t="n">
+        <v>2</v>
+      </c>
+      <c r="U103" t="n">
+        <v>16</v>
+      </c>
+      <c r="V103" t="n">
+        <v>5</v>
+      </c>
+      <c r="W103" t="n">
+        <v>13</v>
+      </c>
+      <c r="X103" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>Estádio Municipal do Fontelo</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>Avenida José Relvas, Viseu</t>
+        </is>
+      </c>
+      <c r="AC103" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ103" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AQ103" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR103" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS103" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AT103" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ103" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB103" t="n">
+        <v>1032</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>49</v>
+      </c>
+      <c r="BE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ103" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT103" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU103" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV103" t="n">
+        <v>72</v>
+      </c>
+      <c r="BW103" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX103" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY103" t="n">
+        <v>66</v>
+      </c>
+      <c r="BZ103" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CA103" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CB103" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CC103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP103" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR103" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS103" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT103" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU103" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV103" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ103" t="n">
+        <v>49</v>
+      </c>
+      <c r="DA103" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB103" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC103" t="n">
+        <v>52</v>
+      </c>
+      <c r="DD103" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DE103" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF103" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG103" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DH103" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DI103" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DJ103" t="n">
+        <v>52</v>
+      </c>
+      <c r="DK103" t="n">
+        <v>35</v>
+      </c>
+      <c r="DL103" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DM103" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DN103" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="DO103" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ103" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV103" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW103" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="DX103" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="DY103" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DZ103" t="inlineStr">
+        <is>
+          <t>5.18</t>
+        </is>
+      </c>
+      <c r="EA103" t="inlineStr">
+        <is>
+          <t>3.96</t>
+        </is>
+      </c>
+      <c r="EB103" t="inlineStr"/>
+      <c r="EC103" t="inlineStr"/>
+      <c r="ED103" t="inlineStr"/>
+      <c r="EE103" t="inlineStr"/>
+      <c r="EF103" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EG103" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="EH103" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EI103" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EJ103" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EK103" t="inlineStr"/>
+      <c r="EL103" t="inlineStr"/>
+      <c r="EM103" t="inlineStr"/>
+      <c r="EN103" t="inlineStr"/>
+      <c r="EO103" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EP103" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>LigaPro_Portugal_2a_división_2025-2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>12</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Leixões</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>45990.58333333334</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>2</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>2</v>
+      </c>
+      <c r="L104" t="n">
+        <v>2</v>
+      </c>
+      <c r="M104" t="n">
+        <v>2</v>
+      </c>
+      <c r="N104" t="n">
+        <v>5</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>6</v>
+      </c>
+      <c r="R104" t="n">
+        <v>4</v>
+      </c>
+      <c r="S104" t="n">
+        <v>4</v>
+      </c>
+      <c r="T104" t="n">
+        <v>3</v>
+      </c>
+      <c r="U104" t="n">
+        <v>10</v>
+      </c>
+      <c r="V104" t="n">
+        <v>7</v>
+      </c>
+      <c r="W104" t="n">
+        <v>14</v>
+      </c>
+      <c r="X104" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>Estádio de Ribes</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>Rua Associação Desportiva Oliveirense 100, Santa Maria de Oliveira</t>
+        </is>
+      </c>
+      <c r="AC104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB104" t="n">
+        <v>1038</v>
+      </c>
+      <c r="BC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP104" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR104" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS104" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT104" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU104" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV104" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW104" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX104" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY104" t="n">
+        <v>74</v>
+      </c>
+      <c r="BZ104" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CA104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB104" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CC104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR104" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS104" t="n">
+        <v>34</v>
+      </c>
+      <c r="CT104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU104" t="n">
+        <v>25</v>
+      </c>
+      <c r="CV104" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ104" t="n">
+        <v>37</v>
+      </c>
+      <c r="DA104" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB104" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC104" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD104" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DE104" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DF104" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG104" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DH104" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DI104" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DJ104" t="n">
+        <v>64</v>
+      </c>
+      <c r="DK104" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL104" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DM104" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DN104" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DO104" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ104" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV104" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW104" t="inlineStr"/>
+      <c r="DX104" t="inlineStr"/>
+      <c r="DY104" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="DZ104" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EA104" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EB104" t="inlineStr"/>
+      <c r="EC104" t="inlineStr"/>
+      <c r="ED104" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EE104" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EF104" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EG104" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="EH104" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EI104" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EJ104" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EK104" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="EL104" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="EM104" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="EN104" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EO104" t="inlineStr"/>
+      <c r="EP104" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP120" headerRowCount="1">
-  <autoFilter ref="A1:EP120"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP122" headerRowCount="1">
+  <autoFilter ref="A1:EP122"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP120"/>
+  <dimension ref="A1:EP122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2757,7 +2757,7 @@
         <v>0.86</v>
       </c>
       <c r="DE4" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -5146,7 +5146,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE9" t="n">
         <v>0.57</v>
@@ -5618,7 +5618,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE10" t="n">
         <v>1.71</v>
@@ -7517,7 +7517,7 @@
         <v>1.14</v>
       </c>
       <c r="DE14" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -8147,164 +8147,164 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
         <v>45886.41666666666</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>13</v>
+      </c>
+      <c r="U16" t="n">
+        <v>8</v>
+      </c>
+      <c r="V16" t="n">
+        <v>17</v>
+      </c>
+      <c r="W16" t="n">
+        <v>20</v>
+      </c>
+      <c r="X16" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>CGD Stadium Aurélio Pereira</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>, Alcochete</t>
+        </is>
+      </c>
+      <c r="AC16" t="n">
         <v>5</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6</v>
-      </c>
-      <c r="S16" t="n">
-        <v>8</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>13</v>
-      </c>
-      <c r="V16" t="n">
-        <v>9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>10</v>
-      </c>
-      <c r="X16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>64</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Estádio de São Lúis</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Rua do Sporting Club Farense, Faro</t>
-        </is>
-      </c>
-      <c r="AC16" t="n">
-        <v>3</v>
-      </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.94</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.8</v>
+        <v>2.35</v>
       </c>
       <c r="AH16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>1.36</v>
       </c>
-      <c r="AI16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AR16" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AU16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
         <v>1</v>
       </c>
       <c r="BB16" t="n">
-        <v>4835</v>
+        <v>1029</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
@@ -8325,64 +8325,64 @@
         <v>1</v>
       </c>
       <c r="BI16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ16" t="n">
         <v>4</v>
       </c>
-      <c r="BL16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>3</v>
-      </c>
       <c r="BR16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BU16" t="n">
         <v>1</v>
       </c>
       <c r="BV16" t="n">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="BW16" t="n">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="BX16" t="n">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="BY16" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.77</v>
+        <v>1.05</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.23</v>
+        <v>1.78</v>
       </c>
       <c r="CB16" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="CC16" t="n">
         <v>0</v>
@@ -8412,13 +8412,13 @@
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO16" t="n">
         <v>0</v>
@@ -8430,28 +8430,28 @@
         <v>1</v>
       </c>
       <c r="CR16" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="CS16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="CT16" t="n">
         <v>1</v>
       </c>
       <c r="CU16" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="CV16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="CY16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="CZ16" t="n">
         <v>0</v>
@@ -8466,10 +8466,10 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="DE16" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8478,10 +8478,10 @@
         <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DI16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DJ16" t="n">
         <v>0</v>
@@ -8505,10 +8505,10 @@
         <v>1</v>
       </c>
       <c r="DQ16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS16" t="b">
         <v>0</v>
@@ -8524,70 +8524,78 @@
       </c>
       <c r="DW16" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="DX16" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="EA16" t="inlineStr">
         <is>
-          <t>3.46</t>
-        </is>
-      </c>
-      <c r="EB16" t="inlineStr"/>
-      <c r="EC16" t="inlineStr"/>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="EB16" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EC16" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EE16" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EF16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EG16" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EH16" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EI16" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr"/>
       <c r="EL16" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="EM16" t="inlineStr">
@@ -8602,12 +8610,12 @@
       </c>
       <c r="EO16" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EP16" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.12</t>
         </is>
       </c>
     </row>
@@ -8627,164 +8635,164 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
         <v>45886.41666666666</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6</v>
+      </c>
+      <c r="S17" t="n">
+        <v>8</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>13</v>
+      </c>
+      <c r="V17" t="n">
         <v>9</v>
       </c>
-      <c r="L17" t="n">
-        <v>13</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="W17" t="n">
+        <v>10</v>
+      </c>
+      <c r="X17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Estádio de São Lúis</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Rua do Sporting Club Farense, Faro</t>
+        </is>
+      </c>
+      <c r="AC17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD17" t="n">
         <v>5</v>
       </c>
-      <c r="N17" t="n">
-        <v>4</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>13</v>
-      </c>
-      <c r="U17" t="n">
-        <v>8</v>
-      </c>
-      <c r="V17" t="n">
-        <v>17</v>
-      </c>
-      <c r="W17" t="n">
-        <v>20</v>
-      </c>
-      <c r="X17" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>CGD Stadium Aurélio Pereira</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>, Alcochete</t>
-        </is>
-      </c>
-      <c r="AC17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4</v>
-      </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>1.94</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.35</v>
+        <v>3.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AM17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN17" t="n">
         <v>1.65</v>
       </c>
-      <c r="AN17" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AO17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP17" t="n">
         <v>2.1</v>
       </c>
-      <c r="AP17" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA17" t="n">
         <v>1</v>
       </c>
       <c r="BB17" t="n">
-        <v>1029</v>
+        <v>4835</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
@@ -8805,64 +8813,64 @@
         <v>1</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BM17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN17" t="n">
         <v>5</v>
       </c>
-      <c r="BN17" t="n">
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
         <v>8</v>
       </c>
-      <c r="BO17" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>6</v>
-      </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="BW17" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="BX17" t="n">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="BY17" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.05</v>
+        <v>1.77</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.78</v>
+        <v>1.23</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
@@ -8892,13 +8900,13 @@
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO17" t="n">
         <v>0</v>
@@ -8910,28 +8918,28 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="CS17" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="CT17" t="n">
         <v>1</v>
       </c>
       <c r="CU17" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="CV17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="CW17" t="n">
         <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="CY17" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="CZ17" t="n">
         <v>0</v>
@@ -8946,10 +8954,10 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.5</v>
+        <v>1.17</v>
       </c>
       <c r="DE17" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8958,10 +8966,10 @@
         <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DI17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DJ17" t="n">
         <v>0</v>
@@ -8985,10 +8993,10 @@
         <v>1</v>
       </c>
       <c r="DQ17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS17" t="b">
         <v>0</v>
@@ -9004,78 +9012,70 @@
       </c>
       <c r="DW17" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="DX17" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="EA17" t="inlineStr">
         <is>
-          <t>3.24</t>
-        </is>
-      </c>
-      <c r="EB17" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EC17" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="EB17" t="inlineStr"/>
+      <c r="EC17" t="inlineStr"/>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EF17" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EG17" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="EH17" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EI17" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr"/>
       <c r="EL17" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="EM17" t="inlineStr">
@@ -9090,12 +9090,12 @@
       </c>
       <c r="EO17" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EP17" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.31</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP18" t="b">
         <v>0</v>
@@ -12338,7 +12338,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE24" t="n">
         <v>1.71</v>
@@ -12810,7 +12810,7 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE25" t="n">
         <v>2</v>
@@ -13285,7 +13285,7 @@
         <v>1.13</v>
       </c>
       <c r="DE26" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -15205,7 +15205,7 @@
         <v>1.5</v>
       </c>
       <c r="DE30" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF30" t="n">
         <v>1</v>
@@ -15235,7 +15235,7 @@
         <v>2.5</v>
       </c>
       <c r="DO30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -16811,40 +16811,40 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>45900.41666666666</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M34" t="n">
         <v>3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -16853,122 +16853,122 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>9</v>
+      </c>
+      <c r="V34" t="n">
+        <v>9</v>
+      </c>
+      <c r="W34" t="n">
+        <v>12</v>
+      </c>
+      <c r="X34" t="n">
         <v>14</v>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="n">
-        <v>4</v>
-      </c>
-      <c r="U34" t="n">
-        <v>24</v>
-      </c>
-      <c r="V34" t="n">
-        <v>4</v>
-      </c>
-      <c r="W34" t="n">
-        <v>17</v>
-      </c>
-      <c r="X34" t="n">
-        <v>10</v>
-      </c>
       <c r="Y34" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="Z34" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>CGD Stadium Aurélio Pereira</t>
+          <t>Estádio de São Lúis</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>, Alcochete</t>
+          <t>Rua do Sporting Club Farense, Faro</t>
         </is>
       </c>
       <c r="AC34" t="n">
         <v>3</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AF34" t="n">
         <v>3</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AJ34" t="n">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="AO34" t="n">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR34" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AU34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA34" t="n">
         <v>1</v>
       </c>
       <c r="BB34" t="n">
-        <v>1029</v>
+        <v>177</v>
       </c>
       <c r="BC34" t="n">
         <v>0</v>
@@ -16989,64 +16989,64 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN34" t="n">
         <v>4</v>
       </c>
-      <c r="BL34" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM34" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN34" t="n">
-        <v>5</v>
-      </c>
       <c r="BO34" t="n">
         <v>1</v>
       </c>
       <c r="BP34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ34" t="n">
         <v>2</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU34" t="n">
         <v>1</v>
       </c>
       <c r="BV34" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="BW34" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BX34" t="n">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="BY34" t="n">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="BZ34" t="n">
-        <v>3.01</v>
+        <v>1.28</v>
       </c>
       <c r="CA34" t="n">
-        <v>0.51</v>
+        <v>1.14</v>
       </c>
       <c r="CB34" t="n">
-        <v>3.52</v>
+        <v>2.42</v>
       </c>
       <c r="CC34" t="n">
         <v>0</v>
@@ -17076,10 +17076,10 @@
         <v>0</v>
       </c>
       <c r="CL34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
@@ -17094,34 +17094,34 @@
         <v>1</v>
       </c>
       <c r="CR34" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="CS34" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="CT34" t="n">
         <v>1</v>
       </c>
       <c r="CU34" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="CV34" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="CW34" t="n">
         <v>1</v>
       </c>
       <c r="CX34" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CY34" t="n">
         <v>6</v>
       </c>
       <c r="CZ34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DB34" t="n">
         <v>0</v>
@@ -17130,37 +17130,37 @@
         <v>50</v>
       </c>
       <c r="DD34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DE34" t="n">
         <v>2.5</v>
       </c>
-      <c r="DE34" t="n">
-        <v>0.43</v>
-      </c>
       <c r="DF34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DG34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DH34" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="DI34" t="n">
-        <v>0.67</v>
+        <v>2</v>
       </c>
       <c r="DJ34" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DK34" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DL34" t="n">
-        <v>1.05</v>
+        <v>1.77</v>
       </c>
       <c r="DM34" t="n">
-        <v>0.68</v>
+        <v>1.65</v>
       </c>
       <c r="DN34" t="n">
-        <v>1.73</v>
+        <v>3.42</v>
       </c>
       <c r="DO34" t="n">
         <v>13</v>
@@ -17172,7 +17172,7 @@
         <v>1</v>
       </c>
       <c r="DR34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS34" t="b">
         <v>0</v>
@@ -17190,80 +17190,60 @@
       <c r="DX34" t="inlineStr"/>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>3.39</t>
-        </is>
-      </c>
-      <c r="EB34" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EC34" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EB34" t="inlineStr"/>
+      <c r="EC34" t="inlineStr"/>
       <c r="ED34" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EE34" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EF34" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EG34" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="EH34" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EI34" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EJ34" t="inlineStr">
         <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EK34" t="n">
-        <v>22.98</v>
-      </c>
-      <c r="EL34" t="n">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="EM34" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="EN34" t="inlineStr">
-        <is>
-          <t>82%</t>
-        </is>
-      </c>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EK34" t="inlineStr"/>
+      <c r="EL34" t="inlineStr"/>
+      <c r="EM34" t="inlineStr"/>
+      <c r="EN34" t="inlineStr"/>
       <c r="EO34" t="inlineStr"/>
       <c r="EP34" t="inlineStr"/>
     </row>
@@ -17283,164 +17263,164 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
         <v>45900.41666666666</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>8</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>14</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="n">
         <v>4</v>
       </c>
-      <c r="K35" t="n">
-        <v>2</v>
-      </c>
-      <c r="L35" t="n">
-        <v>6</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>6</v>
-      </c>
-      <c r="T35" t="n">
-        <v>6</v>
-      </c>
       <c r="U35" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="V35" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="W35" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="X35" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Y35" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="Z35" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Estádio de São Lúis</t>
+          <t>CGD Stadium Aurélio Pereira</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Rua do Sporting Club Farense, Faro</t>
+          <t>, Alcochete</t>
         </is>
       </c>
       <c r="AC35" t="n">
         <v>3</v>
       </c>
       <c r="AD35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AF35" t="n">
         <v>3</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="AO35" t="n">
-        <v>2.88</v>
+        <v>2.17</v>
       </c>
       <c r="AP35" t="n">
-        <v>2.13</v>
+        <v>1.79</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AR35" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AU35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA35" t="n">
         <v>1</v>
       </c>
       <c r="BB35" t="n">
-        <v>177</v>
+        <v>1029</v>
       </c>
       <c r="BC35" t="n">
         <v>0</v>
@@ -17461,64 +17441,64 @@
         <v>1</v>
       </c>
       <c r="BI35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL35" t="n">
         <v>1</v>
       </c>
       <c r="BM35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BO35" t="n">
         <v>1</v>
       </c>
       <c r="BP35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ35" t="n">
         <v>2</v>
       </c>
       <c r="BR35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU35" t="n">
         <v>1</v>
       </c>
       <c r="BV35" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="BW35" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BX35" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="BY35" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="BZ35" t="n">
-        <v>1.28</v>
+        <v>3.01</v>
       </c>
       <c r="CA35" t="n">
-        <v>1.14</v>
+        <v>0.51</v>
       </c>
       <c r="CB35" t="n">
-        <v>2.42</v>
+        <v>3.52</v>
       </c>
       <c r="CC35" t="n">
         <v>0</v>
@@ -17548,10 +17528,10 @@
         <v>0</v>
       </c>
       <c r="CL35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN35" t="n">
         <v>0</v>
@@ -17566,34 +17546,34 @@
         <v>1</v>
       </c>
       <c r="CR35" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="CS35" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="CT35" t="n">
         <v>1</v>
       </c>
       <c r="CU35" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="CV35" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="CW35" t="n">
         <v>1</v>
       </c>
       <c r="CX35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CY35" t="n">
         <v>6</v>
       </c>
       <c r="CZ35" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA35" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DB35" t="n">
         <v>0</v>
@@ -17602,37 +17582,37 @@
         <v>50</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="DE35" t="n">
-        <v>2.5</v>
+        <v>0.43</v>
       </c>
       <c r="DF35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DH35" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="DI35" t="n">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="DJ35" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DK35" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DL35" t="n">
-        <v>1.77</v>
+        <v>1.05</v>
       </c>
       <c r="DM35" t="n">
-        <v>1.65</v>
+        <v>0.68</v>
       </c>
       <c r="DN35" t="n">
-        <v>3.42</v>
+        <v>1.73</v>
       </c>
       <c r="DO35" t="n">
         <v>13</v>
@@ -17644,7 +17624,7 @@
         <v>1</v>
       </c>
       <c r="DR35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS35" t="b">
         <v>0</v>
@@ -17662,60 +17642,80 @@
       <c r="DX35" t="inlineStr"/>
       <c r="DY35" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="DZ35" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="EA35" t="inlineStr">
         <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="EB35" t="inlineStr"/>
-      <c r="EC35" t="inlineStr"/>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="EB35" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EC35" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
       <c r="ED35" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EE35" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EF35" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EG35" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="EH35" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EI35" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EJ35" t="inlineStr">
         <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EK35" t="inlineStr"/>
-      <c r="EL35" t="inlineStr"/>
-      <c r="EM35" t="inlineStr"/>
-      <c r="EN35" t="inlineStr"/>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EK35" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="EL35" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="EM35" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="EN35" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
       <c r="EO35" t="inlineStr"/>
       <c r="EP35" t="inlineStr"/>
     </row>
@@ -19453,7 +19453,7 @@
         <v>1.14</v>
       </c>
       <c r="DE39" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF39" t="n">
         <v>1</v>
@@ -21802,7 +21802,7 @@
         <v>50</v>
       </c>
       <c r="DD44" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE44" t="n">
         <v>1.29</v>
@@ -22746,7 +22746,7 @@
         <v>100</v>
       </c>
       <c r="DD46" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE46" t="n">
         <v>1.29</v>
@@ -23827,43 +23827,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
         <v>45927.41666666666</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K49" t="n">
         <v>6</v>
       </c>
       <c r="L49" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M49" t="n">
         <v>4</v>
       </c>
       <c r="N49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -23875,95 +23875,95 @@
         <v>6</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T49" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="U49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V49" t="n">
+        <v>12</v>
+      </c>
+      <c r="W49" t="n">
         <v>17</v>
       </c>
-      <c r="W49" t="n">
-        <v>18</v>
-      </c>
       <c r="X49" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y49" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="Z49" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>CGD Stadium Aurélio Pereira</t>
+          <t>Estádio Municipal 25 de Abril</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>, Alcochete</t>
+          <t>Rua Futebol Clube de Penafiel, Penafiel</t>
         </is>
       </c>
       <c r="AC49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AF49" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.79</v>
+        <v>2.13</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AJ49" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AN49" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AO49" t="n">
-        <v>2.51</v>
+        <v>2.78</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="AS49" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AU49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV49" t="n">
         <v>0</v>
@@ -23972,25 +23972,25 @@
         <v>0</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA49" t="n">
         <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="BC49" t="n">
         <v>0</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BE49" t="n">
         <v>0</v>
@@ -24005,76 +24005,76 @@
         <v>1</v>
       </c>
       <c r="BI49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM49" t="n">
         <v>4</v>
       </c>
-      <c r="BK49" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL49" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM49" t="n">
-        <v>6</v>
-      </c>
       <c r="BN49" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS49" t="n">
         <v>4</v>
       </c>
-      <c r="BO49" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP49" t="n">
-        <v>3</v>
-      </c>
-      <c r="BQ49" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR49" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS49" t="n">
-        <v>5</v>
-      </c>
       <c r="BT49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BU49" t="n">
         <v>1</v>
       </c>
       <c r="BV49" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="BW49" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="BX49" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="BY49" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="BZ49" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="CA49" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="CB49" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="CC49" t="n">
         <v>0</v>
       </c>
       <c r="CD49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE49" t="n">
         <v>0</v>
       </c>
       <c r="CF49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG49" t="n">
         <v>0</v>
@@ -24095,7 +24095,7 @@
         <v>0</v>
       </c>
       <c r="CM49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN49" t="n">
         <v>1</v>
@@ -24104,22 +24104,22 @@
         <v>1</v>
       </c>
       <c r="CP49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ49" t="n">
         <v>1</v>
       </c>
       <c r="CR49" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="CS49" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CT49" t="n">
         <v>1</v>
       </c>
       <c r="CU49" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CV49" t="n">
         <v>17</v>
@@ -24128,55 +24128,55 @@
         <v>1</v>
       </c>
       <c r="CX49" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="CY49" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="CZ49" t="n">
         <v>25</v>
       </c>
       <c r="DA49" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DB49" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DC49" t="n">
         <v>75</v>
       </c>
       <c r="DD49" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="DE49" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="DF49" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DG49" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="DH49" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="DI49" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="DJ49" t="n">
         <v>75</v>
       </c>
       <c r="DK49" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DL49" t="n">
-        <v>2.03</v>
+        <v>1.3</v>
       </c>
       <c r="DM49" t="n">
         <v>1.39</v>
       </c>
       <c r="DN49" t="n">
-        <v>3.42</v>
+        <v>2.69</v>
       </c>
       <c r="DO49" t="n">
         <v>13</v>
@@ -24185,7 +24185,7 @@
         <v>1</v>
       </c>
       <c r="DQ49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR49" t="b">
         <v>0</v>
@@ -24204,27 +24204,27 @@
       </c>
       <c r="DW49" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DX49" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="DY49" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="DZ49" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EA49" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="EB49" t="inlineStr"/>
@@ -24233,38 +24233,38 @@
       <c r="EE49" t="inlineStr"/>
       <c r="EF49" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EG49" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="EH49" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EI49" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EJ49" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EK49" t="n">
-        <v>18.89</v>
+        <v>23.33</v>
       </c>
       <c r="EL49" t="n">
-        <v>15.11</v>
+        <v>4.43</v>
       </c>
       <c r="EM49" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="EN49" t="inlineStr">
@@ -24274,12 +24274,12 @@
       </c>
       <c r="EO49" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EP49" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -24299,43 +24299,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
         <v>45927.41666666666</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K50" t="n">
         <v>6</v>
       </c>
       <c r="L50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M50" t="n">
         <v>4</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
@@ -24347,95 +24347,95 @@
         <v>6</v>
       </c>
       <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="n">
+        <v>11</v>
+      </c>
+      <c r="U50" t="n">
+        <v>11</v>
+      </c>
+      <c r="V50" t="n">
+        <v>17</v>
+      </c>
+      <c r="W50" t="n">
+        <v>18</v>
+      </c>
+      <c r="X50" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>CGD Stadium Aurélio Pereira</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>, Alcochete</t>
+        </is>
+      </c>
+      <c r="AC50" t="n">
         <v>6</v>
       </c>
-      <c r="T50" t="n">
-        <v>6</v>
-      </c>
-      <c r="U50" t="n">
-        <v>12</v>
-      </c>
-      <c r="V50" t="n">
-        <v>12</v>
-      </c>
-      <c r="W50" t="n">
-        <v>17</v>
-      </c>
-      <c r="X50" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>42</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>Estádio Municipal 25 de Abril</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>Rua Futebol Clube de Penafiel, Penafiel</t>
-        </is>
-      </c>
-      <c r="AC50" t="n">
-        <v>4</v>
-      </c>
       <c r="AD50" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE50" t="n">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="AF50" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.13</v>
+        <v>2.79</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AI50" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AJ50" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AN50" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AO50" t="n">
-        <v>2.78</v>
+        <v>2.51</v>
       </c>
       <c r="AP50" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="AQ50" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT50" t="n">
         <v>1.4</v>
       </c>
-      <c r="AR50" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AU50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV50" t="n">
         <v>0</v>
@@ -24444,25 +24444,25 @@
         <v>0</v>
       </c>
       <c r="AX50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA50" t="n">
         <v>0</v>
       </c>
       <c r="BB50" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="BC50" t="n">
         <v>0</v>
       </c>
       <c r="BD50" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BE50" t="n">
         <v>0</v>
@@ -24477,76 +24477,76 @@
         <v>1</v>
       </c>
       <c r="BI50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BK50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS50" t="n">
         <v>5</v>
       </c>
-      <c r="BM50" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN50" t="n">
-        <v>8</v>
-      </c>
-      <c r="BO50" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP50" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ50" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR50" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS50" t="n">
-        <v>4</v>
-      </c>
       <c r="BT50" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BU50" t="n">
         <v>1</v>
       </c>
       <c r="BV50" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="BW50" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="BX50" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="BY50" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="BZ50" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="CA50" t="n">
-        <v>1.64</v>
+        <v>1.88</v>
       </c>
       <c r="CB50" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="CC50" t="n">
         <v>0</v>
       </c>
       <c r="CD50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE50" t="n">
         <v>0</v>
       </c>
       <c r="CF50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG50" t="n">
         <v>0</v>
@@ -24567,7 +24567,7 @@
         <v>0</v>
       </c>
       <c r="CM50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN50" t="n">
         <v>1</v>
@@ -24576,22 +24576,22 @@
         <v>1</v>
       </c>
       <c r="CP50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ50" t="n">
         <v>1</v>
       </c>
       <c r="CR50" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="CS50" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CT50" t="n">
         <v>1</v>
       </c>
       <c r="CU50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="CV50" t="n">
         <v>17</v>
@@ -24600,55 +24600,55 @@
         <v>1</v>
       </c>
       <c r="CX50" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="CY50" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="CZ50" t="n">
         <v>25</v>
       </c>
       <c r="DA50" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DB50" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DC50" t="n">
         <v>75</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="DE50" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="DF50" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DG50" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="DH50" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="DI50" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="DJ50" t="n">
         <v>75</v>
       </c>
       <c r="DK50" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DL50" t="n">
-        <v>1.3</v>
+        <v>2.03</v>
       </c>
       <c r="DM50" t="n">
         <v>1.39</v>
       </c>
       <c r="DN50" t="n">
-        <v>2.69</v>
+        <v>3.42</v>
       </c>
       <c r="DO50" t="n">
         <v>13</v>
@@ -24657,7 +24657,7 @@
         <v>1</v>
       </c>
       <c r="DQ50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR50" t="b">
         <v>0</v>
@@ -24676,27 +24676,27 @@
       </c>
       <c r="DW50" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="DX50" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="DY50" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="DZ50" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="EA50" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="EB50" t="inlineStr"/>
@@ -24705,38 +24705,38 @@
       <c r="EE50" t="inlineStr"/>
       <c r="EF50" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EG50" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="EH50" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EI50" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EJ50" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EK50" t="n">
-        <v>23.33</v>
+        <v>18.89</v>
       </c>
       <c r="EL50" t="n">
-        <v>4.43</v>
+        <v>15.11</v>
       </c>
       <c r="EM50" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="EN50" t="inlineStr">
@@ -24746,12 +24746,12 @@
       </c>
       <c r="EO50" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EP50" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.94</t>
         </is>
       </c>
     </row>
@@ -26025,7 +26025,7 @@
         <v>1.17</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF53" t="n">
         <v>0</v>
@@ -28898,7 +28898,7 @@
         <v>67</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE59" t="n">
         <v>0.43</v>
@@ -29370,7 +29370,7 @@
         <v>84</v>
       </c>
       <c r="DD60" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE60" t="n">
         <v>1.43</v>
@@ -30789,7 +30789,7 @@
         <v>1.14</v>
       </c>
       <c r="DE63" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF63" t="n">
         <v>0.67</v>
@@ -31702,7 +31702,7 @@
         <v>54</v>
       </c>
       <c r="DD65" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE65" t="n">
         <v>2.5</v>
@@ -31735,7 +31735,7 @@
         <v>2.72</v>
       </c>
       <c r="DO65" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -33155,170 +33155,170 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
         <v>45955.41666666666</v>
       </c>
       <c r="G69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I69" t="n">
         <v>4</v>
       </c>
       <c r="J69" t="n">
+        <v>10</v>
+      </c>
+      <c r="K69" t="n">
+        <v>2</v>
+      </c>
+      <c r="L69" t="n">
+        <v>12</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1</v>
+      </c>
+      <c r="N69" t="n">
         <v>6</v>
       </c>
-      <c r="K69" t="n">
-        <v>2</v>
-      </c>
-      <c r="L69" t="n">
-        <v>8</v>
-      </c>
-      <c r="M69" t="n">
-        <v>4</v>
-      </c>
-      <c r="N69" t="n">
-        <v>3</v>
-      </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U69" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="V69" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W69" t="n">
         <v>16</v>
       </c>
       <c r="X69" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y69" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="Z69" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>CGD Stadium Aurélio Pereira</t>
+          <t>Estádio Pina Manique</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>, Alcochete</t>
+          <t>Rua Monsanto, Lisboa</t>
         </is>
       </c>
       <c r="AC69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD69" t="n">
         <v>6</v>
       </c>
       <c r="AE69" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AF69" t="n">
         <v>3.1</v>
       </c>
       <c r="AG69" t="n">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="AH69" t="n">
         <v>1.36</v>
       </c>
       <c r="AI69" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AJ69" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AK69" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AL69" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AM69" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AN69" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AO69" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AR69" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AS69" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AT69" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AU69" t="n">
         <v>4</v>
       </c>
       <c r="AV69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB69" t="n">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="BC69" t="n">
         <v>0</v>
       </c>
       <c r="BD69" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="BE69" t="n">
         <v>0</v>
@@ -33327,184 +33327,184 @@
         <v>-1</v>
       </c>
       <c r="BG69" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>7</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR69" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU69" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV69" t="n">
+        <v>74</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>73</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>72</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CB69" t="n">
+        <v>3</v>
+      </c>
+      <c r="CC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR69" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS69" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT69" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU69" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV69" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW69" t="n">
         <v>-1</v>
       </c>
-      <c r="BH69" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI69" t="n">
+      <c r="CX69" t="n">
         <v>-1</v>
       </c>
-      <c r="BJ69" t="n">
+      <c r="CY69" t="n">
         <v>-1</v>
       </c>
-      <c r="BK69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BL69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BM69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BN69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BO69" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP69" t="n">
-        <v>4</v>
-      </c>
-      <c r="BQ69" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR69" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS69" t="n">
-        <v>5</v>
-      </c>
-      <c r="BT69" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU69" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV69" t="n">
-        <v>70</v>
-      </c>
-      <c r="BW69" t="n">
-        <v>25</v>
-      </c>
-      <c r="BX69" t="n">
-        <v>76</v>
-      </c>
-      <c r="BY69" t="n">
-        <v>51</v>
-      </c>
-      <c r="BZ69" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CA69" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="CB69" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="CC69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN69" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP69" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR69" t="n">
+      <c r="CZ69" t="n">
         <v>17</v>
       </c>
-      <c r="CS69" t="n">
-        <v>20</v>
-      </c>
-      <c r="CT69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU69" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV69" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW69" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX69" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY69" t="n">
-        <v>14</v>
-      </c>
-      <c r="CZ69" t="n">
-        <v>50</v>
-      </c>
       <c r="DA69" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="DB69" t="n">
         <v>17</v>
       </c>
       <c r="DC69" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="DD69" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="DE69" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="DF69" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DG69" t="n">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="DH69" t="n">
-        <v>2.14</v>
+        <v>1.71</v>
       </c>
       <c r="DI69" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="DJ69" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="DK69" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="DL69" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="DM69" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="DN69" t="n">
-        <v>3.19</v>
+        <v>2.43</v>
       </c>
       <c r="DO69" t="n">
         <v>13</v>
@@ -33528,26 +33528,26 @@
         <v>0</v>
       </c>
       <c r="DV69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW69" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="DX69" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="DY69" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="DZ69" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="EA69" t="inlineStr">
@@ -33561,53 +33561,53 @@
       <c r="EE69" t="inlineStr"/>
       <c r="EF69" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EG69" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="EH69" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EI69" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EJ69" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EK69" t="n">
-        <v>22.1</v>
+        <v>22.12</v>
       </c>
       <c r="EL69" t="n">
-        <v>5.84</v>
+        <v>4.59</v>
       </c>
       <c r="EM69" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="EN69" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="EO69" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EP69" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.28</t>
         </is>
       </c>
     </row>
@@ -33627,170 +33627,170 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
         <v>45955.41666666666</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
         <v>4</v>
       </c>
       <c r="J70" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K70" t="n">
         <v>2</v>
       </c>
       <c r="L70" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N70" t="n">
+        <v>3</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>9</v>
+      </c>
+      <c r="R70" t="n">
+        <v>2</v>
+      </c>
+      <c r="S70" t="n">
+        <v>11</v>
+      </c>
+      <c r="T70" t="n">
         <v>6</v>
       </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>6</v>
-      </c>
-      <c r="R70" t="n">
-        <v>5</v>
-      </c>
-      <c r="S70" t="n">
-        <v>6</v>
-      </c>
-      <c r="T70" t="n">
-        <v>5</v>
-      </c>
       <c r="U70" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="V70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W70" t="n">
         <v>16</v>
       </c>
       <c r="X70" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y70" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="Z70" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Estádio Pina Manique</t>
+          <t>CGD Stadium Aurélio Pereira</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>Rua Monsanto, Lisboa</t>
+          <t>, Alcochete</t>
         </is>
       </c>
       <c r="AC70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD70" t="n">
         <v>6</v>
       </c>
       <c r="AE70" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="AF70" t="n">
         <v>3.1</v>
       </c>
       <c r="AG70" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="AH70" t="n">
         <v>1.36</v>
       </c>
       <c r="AI70" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AJ70" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AK70" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AL70" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AM70" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AN70" t="n">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AO70" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR70" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AS70" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AT70" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AU70" t="n">
         <v>4</v>
       </c>
       <c r="AV70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB70" t="n">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="BC70" t="n">
         <v>0</v>
       </c>
       <c r="BD70" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BE70" t="n">
         <v>0</v>
@@ -33799,70 +33799,70 @@
         <v>-1</v>
       </c>
       <c r="BG70" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH70" t="n">
         <v>1</v>
       </c>
       <c r="BI70" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="BJ70" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BK70" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BL70" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BM70" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="BN70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ70" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR70" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS70" t="n">
         <v>5</v>
       </c>
-      <c r="BO70" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP70" t="n">
-        <v>3</v>
-      </c>
-      <c r="BQ70" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR70" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS70" t="n">
+      <c r="BT70" t="n">
         <v>4</v>
       </c>
-      <c r="BT70" t="n">
-        <v>3</v>
-      </c>
       <c r="BU70" t="n">
         <v>1</v>
       </c>
       <c r="BV70" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="BW70" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="BX70" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="BY70" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="BZ70" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="CA70" t="n">
-        <v>1.29</v>
+        <v>0.83</v>
       </c>
       <c r="CB70" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="CC70" t="n">
         <v>0</v>
@@ -33895,10 +33895,10 @@
         <v>0</v>
       </c>
       <c r="CM70" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="CN70" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO70" t="n">
         <v>0</v>
@@ -33910,73 +33910,73 @@
         <v>1</v>
       </c>
       <c r="CR70" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CS70" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU70" t="n">
         <v>15</v>
       </c>
-      <c r="CT70" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU70" t="n">
-        <v>13</v>
-      </c>
       <c r="CV70" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="CW70" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX70" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CY70" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="CZ70" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="DA70" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="DB70" t="n">
         <v>17</v>
       </c>
       <c r="DC70" t="n">
+        <v>67</v>
+      </c>
+      <c r="DD70" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DE70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF70" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG70" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH70" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DI70" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DJ70" t="n">
         <v>50</v>
       </c>
-      <c r="DD70" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="DE70" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DF70" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="DG70" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DH70" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DI70" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ70" t="n">
-        <v>84</v>
-      </c>
       <c r="DK70" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="DL70" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DM70" t="n">
         <v>1.39</v>
       </c>
-      <c r="DM70" t="n">
-        <v>1.04</v>
-      </c>
       <c r="DN70" t="n">
-        <v>2.43</v>
+        <v>3.19</v>
       </c>
       <c r="DO70" t="n">
         <v>13</v>
@@ -34000,26 +34000,26 @@
         <v>0</v>
       </c>
       <c r="DV70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW70" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="DX70" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="DY70" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="DZ70" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="EA70" t="inlineStr">
@@ -34033,53 +34033,53 @@
       <c r="EE70" t="inlineStr"/>
       <c r="EF70" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EG70" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="EH70" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EI70" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EJ70" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EK70" t="n">
-        <v>22.12</v>
+        <v>22.1</v>
       </c>
       <c r="EL70" t="n">
-        <v>4.59</v>
+        <v>5.84</v>
       </c>
       <c r="EM70" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="EN70" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="EO70" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EP70" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.21</t>
         </is>
       </c>
     </row>
@@ -34579,143 +34579,143 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
         <v>45955.60416666666</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L72" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M72" t="n">
         <v>4</v>
       </c>
       <c r="N72" t="n">
+        <v>3</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>3</v>
+      </c>
+      <c r="R72" t="n">
         <v>5</v>
       </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>7</v>
-      </c>
-      <c r="R72" t="n">
-        <v>2</v>
-      </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T72" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U72" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V72" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="W72" t="n">
         <v>13</v>
       </c>
       <c r="X72" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y72" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="Z72" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Estádio Municipal do Fontelo</t>
+          <t>Estádio Marcolino de Castro</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Avenida José Relvas, Viseu</t>
+          <t>Avenida 25 de Abril 14, Santa Maria da Feira</t>
         </is>
       </c>
       <c r="AC72" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE72" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AF72" t="n">
-        <v>3.07</v>
+        <v>3.15</v>
       </c>
       <c r="AG72" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AI72" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AJ72" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AK72" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AL72" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AM72" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AN72" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AO72" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AP72" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AR72" t="n">
-        <v>3.28</v>
+        <v>2.65</v>
       </c>
       <c r="AS72" t="n">
-        <v>2.56</v>
+        <v>2.85</v>
       </c>
       <c r="AT72" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AU72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV72" t="n">
         <v>0</v>
@@ -34724,25 +34724,25 @@
         <v>0</v>
       </c>
       <c r="AX72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA72" t="n">
         <v>0</v>
       </c>
       <c r="BB72" t="n">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="BC72" t="n">
         <v>0</v>
       </c>
       <c r="BD72" t="n">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="BE72" t="n">
         <v>0</v>
@@ -34751,28 +34751,28 @@
         <v>-1</v>
       </c>
       <c r="BG72" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH72" t="n">
         <v>1</v>
       </c>
       <c r="BI72" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BJ72" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BK72" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BL72" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BM72" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BN72" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BO72" t="n">
         <v>1</v>
@@ -34781,40 +34781,40 @@
         <v>2</v>
       </c>
       <c r="BQ72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS72" t="n">
         <v>3</v>
       </c>
       <c r="BT72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BU72" t="n">
         <v>1</v>
       </c>
       <c r="BV72" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="BW72" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="BX72" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="BY72" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="BZ72" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="CA72" t="n">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="CB72" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="CC72" t="n">
         <v>0</v>
@@ -34847,31 +34847,31 @@
         <v>0</v>
       </c>
       <c r="CM72" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN72" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ72" t="n">
         <v>1</v>
       </c>
       <c r="CR72" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="CS72" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="CT72" t="n">
         <v>1</v>
       </c>
       <c r="CU72" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CV72" t="n">
         <v>13</v>
@@ -34880,55 +34880,55 @@
         <v>1</v>
       </c>
       <c r="CX72" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CY72" t="n">
         <v>12</v>
       </c>
       <c r="CZ72" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="DA72" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB72" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC72" t="n">
         <v>84</v>
       </c>
-      <c r="DB72" t="n">
-        <v>33</v>
-      </c>
-      <c r="DC72" t="n">
-        <v>67</v>
-      </c>
       <c r="DD72" t="n">
-        <v>2.17</v>
+        <v>1.33</v>
       </c>
       <c r="DE72" t="n">
-        <v>1.86</v>
+        <v>1</v>
       </c>
       <c r="DF72" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="DG72" t="n">
-        <v>2.33</v>
+        <v>0.67</v>
       </c>
       <c r="DH72" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="DI72" t="n">
-        <v>1.86</v>
+        <v>0.57</v>
       </c>
       <c r="DJ72" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="DK72" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL72" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="DM72" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="DN72" t="n">
-        <v>3.36</v>
+        <v>3.12</v>
       </c>
       <c r="DO72" t="n">
         <v>13</v>
@@ -34937,7 +34937,7 @@
         <v>1</v>
       </c>
       <c r="DQ72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR72" t="b">
         <v>0</v>
@@ -34956,27 +34956,27 @@
       </c>
       <c r="DW72" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DX72" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="DY72" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="DZ72" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EA72" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="EB72" t="inlineStr"/>
@@ -34985,41 +34985,53 @@
       <c r="EE72" t="inlineStr"/>
       <c r="EF72" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EG72" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="EH72" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EI72" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EJ72" t="inlineStr">
         <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="EK72" t="inlineStr"/>
-      <c r="EL72" t="inlineStr"/>
-      <c r="EM72" t="inlineStr"/>
-      <c r="EN72" t="inlineStr"/>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EK72" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="EL72" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="EM72" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="EN72" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="EO72" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EP72" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.01</t>
         </is>
       </c>
     </row>
@@ -35039,143 +35051,143 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
         <v>45955.60416666666</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
+        <v>3</v>
+      </c>
+      <c r="K73" t="n">
+        <v>3</v>
+      </c>
+      <c r="L73" t="n">
         <v>6</v>
-      </c>
-      <c r="K73" t="n">
-        <v>4</v>
-      </c>
-      <c r="L73" t="n">
-        <v>10</v>
       </c>
       <c r="M73" t="n">
         <v>4</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U73" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V73" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="W73" t="n">
         <v>13</v>
       </c>
       <c r="X73" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y73" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="Z73" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Estádio Marcolino de Castro</t>
+          <t>Estádio Municipal do Fontelo</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Avenida 25 de Abril 14, Santa Maria da Feira</t>
+          <t>Avenida José Relvas, Viseu</t>
         </is>
       </c>
       <c r="AC73" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AD73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE73" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AF73" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="AG73" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AI73" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AJ73" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AK73" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AL73" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AM73" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AN73" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AO73" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AS73" t="n">
         <v>2.56</v>
       </c>
-      <c r="AP73" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AQ73" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR73" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AS73" t="n">
-        <v>2.85</v>
-      </c>
       <c r="AT73" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AU73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV73" t="n">
         <v>0</v>
@@ -35184,25 +35196,25 @@
         <v>0</v>
       </c>
       <c r="AX73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA73" t="n">
         <v>0</v>
       </c>
       <c r="BB73" t="n">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="BC73" t="n">
         <v>0</v>
       </c>
       <c r="BD73" t="n">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="BE73" t="n">
         <v>0</v>
@@ -35211,28 +35223,28 @@
         <v>-1</v>
       </c>
       <c r="BG73" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH73" t="n">
         <v>1</v>
       </c>
       <c r="BI73" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BJ73" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BK73" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BL73" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BM73" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="BN73" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BO73" t="n">
         <v>1</v>
@@ -35241,40 +35253,40 @@
         <v>2</v>
       </c>
       <c r="BQ73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BR73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS73" t="n">
         <v>3</v>
       </c>
       <c r="BT73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BU73" t="n">
         <v>1</v>
       </c>
       <c r="BV73" t="n">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="BW73" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="BX73" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="BY73" t="n">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="BZ73" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="CA73" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="CB73" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="CC73" t="n">
         <v>0</v>
@@ -35307,31 +35319,31 @@
         <v>0</v>
       </c>
       <c r="CM73" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="CN73" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ73" t="n">
         <v>1</v>
       </c>
       <c r="CR73" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="CS73" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CT73" t="n">
         <v>1</v>
       </c>
       <c r="CU73" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CV73" t="n">
         <v>13</v>
@@ -35340,55 +35352,55 @@
         <v>1</v>
       </c>
       <c r="CX73" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CY73" t="n">
         <v>12</v>
       </c>
       <c r="CZ73" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="DA73" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="DB73" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC73" t="n">
         <v>67</v>
       </c>
-      <c r="DC73" t="n">
-        <v>84</v>
-      </c>
       <c r="DD73" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DE73" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF73" t="n">
         <v>1.33</v>
       </c>
-      <c r="DE73" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF73" t="n">
-        <v>2</v>
-      </c>
       <c r="DG73" t="n">
-        <v>0.67</v>
+        <v>2.33</v>
       </c>
       <c r="DH73" t="n">
-        <v>1.13</v>
+        <v>0.86</v>
       </c>
       <c r="DI73" t="n">
-        <v>0.57</v>
+        <v>1.86</v>
       </c>
       <c r="DJ73" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="DK73" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL73" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="DM73" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="DN73" t="n">
-        <v>3.12</v>
+        <v>3.36</v>
       </c>
       <c r="DO73" t="n">
         <v>13</v>
@@ -35397,7 +35409,7 @@
         <v>1</v>
       </c>
       <c r="DQ73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR73" t="b">
         <v>0</v>
@@ -35416,27 +35428,27 @@
       </c>
       <c r="DW73" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="DX73" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="DY73" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="DZ73" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EA73" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="EB73" t="inlineStr"/>
@@ -35445,53 +35457,41 @@
       <c r="EE73" t="inlineStr"/>
       <c r="EF73" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EG73" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="EH73" t="inlineStr">
         <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EI73" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EJ73" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EK73" t="inlineStr"/>
+      <c r="EL73" t="inlineStr"/>
+      <c r="EM73" t="inlineStr"/>
+      <c r="EN73" t="inlineStr"/>
+      <c r="EO73" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="EI73" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EJ73" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="EK73" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="EL73" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="EM73" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="EN73" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="EO73" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
       <c r="EP73" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>3.23</t>
         </is>
       </c>
     </row>
@@ -35833,7 +35833,7 @@
         <v>1.17</v>
       </c>
       <c r="DE74" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF74" t="n">
         <v>0</v>
@@ -36786,7 +36786,7 @@
         <v>100</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE76" t="n">
         <v>1.17</v>
@@ -36819,7 +36819,7 @@
         <v>2.67</v>
       </c>
       <c r="DO76" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP76" t="b">
         <v>1</v>
@@ -37907,12 +37907,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
@@ -37922,155 +37922,155 @@
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J79" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K79" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L79" t="n">
+        <v>10</v>
+      </c>
+      <c r="M79" t="n">
+        <v>2</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1</v>
+      </c>
+      <c r="R79" t="n">
+        <v>11</v>
+      </c>
+      <c r="S79" t="n">
+        <v>7</v>
+      </c>
+      <c r="T79" t="n">
+        <v>10</v>
+      </c>
+      <c r="U79" t="n">
         <v>8</v>
       </c>
-      <c r="M79" t="n">
-        <v>3</v>
-      </c>
-      <c r="N79" t="n">
-        <v>3</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>5</v>
-      </c>
-      <c r="R79" t="n">
-        <v>6</v>
-      </c>
-      <c r="S79" t="n">
-        <v>11</v>
-      </c>
-      <c r="T79" t="n">
-        <v>1</v>
-      </c>
-      <c r="U79" t="n">
+      <c r="V79" t="n">
+        <v>21</v>
+      </c>
+      <c r="W79" t="n">
         <v>16</v>
-      </c>
-      <c r="V79" t="n">
-        <v>7</v>
-      </c>
-      <c r="W79" t="n">
-        <v>17</v>
       </c>
       <c r="X79" t="n">
         <v>14</v>
       </c>
       <c r="Y79" t="n">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="Z79" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Campo da Imaculada Conceição</t>
+          <t>Estádio do Mar</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>, Ilha da Madeira</t>
+          <t>Lugar da Cruz de Pau, Matosinhos</t>
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="AF79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR79" t="n">
         <v>3.1</v>
       </c>
-      <c r="AG79" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AK79" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL79" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM79" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN79" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO79" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AP79" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AQ79" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR79" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AS79" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AU79" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ79" t="n">
         <v>4</v>
       </c>
-      <c r="AV79" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY79" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ79" t="n">
-        <v>3</v>
-      </c>
       <c r="BA79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB79" t="n">
-        <v>4880</v>
+        <v>1032</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -38085,64 +38085,64 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL79" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BM79" t="n">
         <v>4</v>
       </c>
       <c r="BN79" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BO79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS79" t="n">
         <v>2</v>
       </c>
       <c r="BT79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="BW79" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="BX79" t="n">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="BY79" t="n">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="BZ79" t="n">
-        <v>1.82</v>
+        <v>0.9</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.21</v>
+        <v>2.52</v>
       </c>
       <c r="CB79" t="n">
-        <v>3.02</v>
+        <v>3.42</v>
       </c>
       <c r="CC79" t="n">
         <v>0</v>
@@ -38172,7 +38172,7 @@
         <v>0</v>
       </c>
       <c r="CL79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM79" t="n">
         <v>0</v>
@@ -38190,10 +38190,10 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS79" t="n">
         <v>14</v>
-      </c>
-      <c r="CS79" t="n">
-        <v>30</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
@@ -38202,61 +38202,61 @@
         <v>14</v>
       </c>
       <c r="CV79" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CW79" t="n">
         <v>1</v>
       </c>
       <c r="CX79" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CY79" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CZ79" t="n">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="DA79" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB79" t="n">
         <v>50</v>
       </c>
-      <c r="DB79" t="n">
-        <v>13</v>
-      </c>
       <c r="DC79" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="DE79" t="n">
         <v>1.29</v>
       </c>
       <c r="DF79" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH79" t="n">
         <v>1.25</v>
       </c>
-      <c r="DG79" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DH79" t="n">
-        <v>1.75</v>
-      </c>
       <c r="DI79" t="n">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="DJ79" t="n">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="DK79" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="DN79" t="n">
-        <v>3.07</v>
+        <v>2.83</v>
       </c>
       <c r="DO79" t="n">
         <v>13</v>
@@ -38274,94 +38274,102 @@
         <v>1</v>
       </c>
       <c r="DT79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV79" t="b">
         <v>1</v>
       </c>
       <c r="DW79" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="DX79" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>3.38</t>
-        </is>
-      </c>
-      <c r="EB79" t="inlineStr"/>
-      <c r="EC79" t="inlineStr"/>
-      <c r="ED79" t="inlineStr"/>
-      <c r="EE79" t="inlineStr"/>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="EB79" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EC79" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="ED79" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
       <c r="EF79" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EG79" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="EH79" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EI79" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EK79" t="n">
-        <v>20.23</v>
+        <v>18.51</v>
       </c>
       <c r="EL79" t="n">
-        <v>6.75</v>
+        <v>5.45</v>
       </c>
       <c r="EM79" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="EN79" t="inlineStr">
         <is>
-          <t>22%</t>
-        </is>
-      </c>
-      <c r="EO79" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EP79" t="inlineStr">
-        <is>
-          <t>3.02</t>
-        </is>
-      </c>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="EO79" t="inlineStr"/>
+      <c r="EP79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -38379,12 +38387,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
@@ -38394,155 +38402,155 @@
         <v>1</v>
       </c>
       <c r="H80" t="n">
+        <v>3</v>
+      </c>
+      <c r="I80" t="n">
+        <v>4</v>
+      </c>
+      <c r="J80" t="n">
+        <v>6</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2</v>
+      </c>
+      <c r="L80" t="n">
+        <v>8</v>
+      </c>
+      <c r="M80" t="n">
+        <v>3</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
         <v>5</v>
       </c>
-      <c r="I80" t="n">
+      <c r="R80" t="n">
         <v>6</v>
       </c>
-      <c r="J80" t="n">
-        <v>3</v>
-      </c>
-      <c r="K80" t="n">
+      <c r="S80" t="n">
+        <v>11</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>16</v>
+      </c>
+      <c r="V80" t="n">
         <v>7</v>
       </c>
-      <c r="L80" t="n">
-        <v>10</v>
-      </c>
-      <c r="M80" t="n">
-        <v>2</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>1</v>
-      </c>
-      <c r="R80" t="n">
-        <v>11</v>
-      </c>
-      <c r="S80" t="n">
-        <v>7</v>
-      </c>
-      <c r="T80" t="n">
-        <v>10</v>
-      </c>
-      <c r="U80" t="n">
-        <v>8</v>
-      </c>
-      <c r="V80" t="n">
-        <v>21</v>
-      </c>
       <c r="W80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X80" t="n">
         <v>14</v>
       </c>
       <c r="Y80" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="Z80" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Estádio do Mar</t>
+          <t>Campo da Imaculada Conceição</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>Lugar da Cruz de Pau, Matosinhos</t>
+          <t>, Ilha da Madeira</t>
         </is>
       </c>
       <c r="AC80" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU80" t="n">
         <v>4</v>
       </c>
-      <c r="AD80" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF80" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG80" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AH80" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI80" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ80" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AK80" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AL80" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM80" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN80" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AO80" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AP80" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AQ80" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR80" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AS80" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT80" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU80" t="n">
-        <v>6</v>
-      </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY80" t="n">
         <v>3</v>
       </c>
       <c r="AZ80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>1032</v>
+        <v>4880</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -38557,64 +38565,64 @@
         <v>1</v>
       </c>
       <c r="BI80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BM80" t="n">
         <v>4</v>
       </c>
       <c r="BN80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BO80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS80" t="n">
         <v>2</v>
       </c>
       <c r="BT80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BU80" t="n">
         <v>1</v>
       </c>
       <c r="BV80" t="n">
+        <v>63</v>
+      </c>
+      <c r="BW80" t="n">
         <v>45</v>
       </c>
-      <c r="BW80" t="n">
-        <v>59</v>
-      </c>
       <c r="BX80" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="BY80" t="n">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="BZ80" t="n">
-        <v>0.9</v>
+        <v>1.82</v>
       </c>
       <c r="CA80" t="n">
-        <v>2.52</v>
+        <v>1.21</v>
       </c>
       <c r="CB80" t="n">
-        <v>3.42</v>
+        <v>3.02</v>
       </c>
       <c r="CC80" t="n">
         <v>0</v>
@@ -38644,7 +38652,7 @@
         <v>0</v>
       </c>
       <c r="CL80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM80" t="n">
         <v>0</v>
@@ -38662,10 +38670,10 @@
         <v>1</v>
       </c>
       <c r="CR80" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="CS80" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="CT80" t="n">
         <v>1</v>
@@ -38674,61 +38682,61 @@
         <v>14</v>
       </c>
       <c r="CV80" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CW80" t="n">
         <v>1</v>
       </c>
       <c r="CX80" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="CY80" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CZ80" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="DA80" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB80" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="DC80" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="DE80" t="n">
         <v>1.29</v>
       </c>
       <c r="DF80" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DI80" t="n">
         <v>1.5</v>
       </c>
-      <c r="DG80" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DH80" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DI80" t="n">
-        <v>1.13</v>
-      </c>
       <c r="DJ80" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="DK80" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL80" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="DM80" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="DN80" t="n">
-        <v>2.83</v>
+        <v>3.07</v>
       </c>
       <c r="DO80" t="n">
         <v>13</v>
@@ -38746,102 +38754,94 @@
         <v>1</v>
       </c>
       <c r="DT80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV80" t="b">
         <v>1</v>
       </c>
       <c r="DW80" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DX80" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="DY80" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="DZ80" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>2.94</t>
-        </is>
-      </c>
-      <c r="EB80" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EC80" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="ED80" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EE80" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EB80" t="inlineStr"/>
+      <c r="EC80" t="inlineStr"/>
+      <c r="ED80" t="inlineStr"/>
+      <c r="EE80" t="inlineStr"/>
       <c r="EF80" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EG80" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="EH80" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EI80" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EJ80" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EK80" t="n">
-        <v>18.51</v>
+        <v>20.23</v>
       </c>
       <c r="EL80" t="n">
-        <v>5.45</v>
+        <v>6.75</v>
       </c>
       <c r="EM80" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="EN80" t="inlineStr">
         <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="EO80" t="inlineStr"/>
-      <c r="EP80" t="inlineStr"/>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="EO80" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EP80" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -39645,7 +39645,7 @@
         <v>1.83</v>
       </c>
       <c r="DE82" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF82" t="n">
         <v>2.5</v>
@@ -41062,7 +41062,7 @@
         <v>75</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE85" t="n">
         <v>2.5</v>
@@ -41095,7 +41095,7 @@
         <v>2.72</v>
       </c>
       <c r="DO85" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41537,7 +41537,7 @@
         <v>1.83</v>
       </c>
       <c r="DE86" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF86" t="n">
         <v>1.75</v>
@@ -44443,7 +44443,7 @@
         <v>3.05</v>
       </c>
       <c r="DO92" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -47733,7 +47733,7 @@
         <v>1.13</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF99" t="n">
         <v>1.5</v>
@@ -48202,7 +48202,7 @@
         <v>90</v>
       </c>
       <c r="DD100" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE100" t="n">
         <v>1</v>
@@ -49165,7 +49165,7 @@
         <v>1.75</v>
       </c>
       <c r="DE102" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF102" t="n">
         <v>1.33</v>
@@ -49645,7 +49645,7 @@
         <v>2.17</v>
       </c>
       <c r="DE103" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="DF103" t="n">
         <v>2</v>
@@ -50110,7 +50110,7 @@
         <v>80</v>
       </c>
       <c r="DD104" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="DE104" t="n">
         <v>0.67</v>
@@ -50143,7 +50143,7 @@
         <v>2.37</v>
       </c>
       <c r="DO104" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -50582,7 +50582,7 @@
         <v>74</v>
       </c>
       <c r="DD105" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DE105" t="n">
         <v>1.5</v>
@@ -51057,7 +51057,7 @@
         <v>1.67</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DF106" t="n">
         <v>2</v>
@@ -55855,7 +55855,7 @@
         <v>2.82</v>
       </c>
       <c r="DO116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -56489,22 +56489,22 @@
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R118" t="n">
         <v>3</v>
       </c>
       <c r="S118" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T118" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U118" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V118" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="W118" t="n">
         <v>9</v>
@@ -56513,10 +56513,10 @@
         <v>13</v>
       </c>
       <c r="Y118" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="Z118" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
@@ -56676,13 +56676,13 @@
         <v>73</v>
       </c>
       <c r="BZ118" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="CA118" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="CB118" t="n">
-        <v>2.88</v>
+        <v>3.38</v>
       </c>
       <c r="CC118" t="n">
         <v>0</v>
@@ -56730,28 +56730,28 @@
         <v>1</v>
       </c>
       <c r="CR118" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="CS118" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CT118" t="n">
         <v>1</v>
       </c>
       <c r="CU118" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CV118" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="CW118" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX118" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CY118" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CZ118" t="n">
         <v>70</v>
@@ -57832,6 +57832,958 @@
       <c r="EP120" t="inlineStr">
         <is>
           <t>3.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>LigaPro_Portugal_2a_división_2025-2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>14</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Porto II</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>FC Penafiel</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>46003.75</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" t="n">
+        <v>6</v>
+      </c>
+      <c r="K121" t="n">
+        <v>6</v>
+      </c>
+      <c r="L121" t="n">
+        <v>12</v>
+      </c>
+      <c r="M121" t="n">
+        <v>4</v>
+      </c>
+      <c r="N121" t="n">
+        <v>2</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>4</v>
+      </c>
+      <c r="R121" t="n">
+        <v>1</v>
+      </c>
+      <c r="S121" t="n">
+        <v>3</v>
+      </c>
+      <c r="T121" t="n">
+        <v>11</v>
+      </c>
+      <c r="U121" t="n">
+        <v>7</v>
+      </c>
+      <c r="V121" t="n">
+        <v>12</v>
+      </c>
+      <c r="W121" t="n">
+        <v>12</v>
+      </c>
+      <c r="X121" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>Estádio Dr. Jorge Sampaio</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>Rua da Paradela, Pedroso, Vila Nova de Gaia</t>
+        </is>
+      </c>
+      <c r="AC121" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>1037</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>59</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>65</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>91</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU121" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV121" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ121" t="n">
+        <v>47</v>
+      </c>
+      <c r="DA121" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB121" t="n">
+        <v>41</v>
+      </c>
+      <c r="DC121" t="n">
+        <v>48</v>
+      </c>
+      <c r="DD121" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DE121" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="DF121" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG121" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH121" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DI121" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DJ121" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK121" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL121" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DM121" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DN121" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DO121" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW121" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="DX121" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="DY121" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="DZ121" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="EA121" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EB121" t="inlineStr"/>
+      <c r="EC121" t="inlineStr"/>
+      <c r="ED121" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EE121" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EF121" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EG121" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="EH121" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EI121" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EJ121" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EK121" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="EL121" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="EM121" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="EN121" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EO121" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EP121" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>LigaPro_Portugal_2a_división_2025-2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>14</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>GD Chaves</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>46003.75</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2</v>
+      </c>
+      <c r="H122" t="n">
+        <v>3</v>
+      </c>
+      <c r="I122" t="n">
+        <v>5</v>
+      </c>
+      <c r="J122" t="n">
+        <v>6</v>
+      </c>
+      <c r="K122" t="n">
+        <v>5</v>
+      </c>
+      <c r="L122" t="n">
+        <v>11</v>
+      </c>
+      <c r="M122" t="n">
+        <v>3</v>
+      </c>
+      <c r="N122" t="n">
+        <v>4</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>4</v>
+      </c>
+      <c r="R122" t="n">
+        <v>9</v>
+      </c>
+      <c r="S122" t="n">
+        <v>8</v>
+      </c>
+      <c r="T122" t="n">
+        <v>2</v>
+      </c>
+      <c r="U122" t="n">
+        <v>12</v>
+      </c>
+      <c r="V122" t="n">
+        <v>11</v>
+      </c>
+      <c r="W122" t="n">
+        <v>14</v>
+      </c>
+      <c r="X122" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>Estádio de Ribes</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>Rua Associação Desportiva Oliveirense 100, Santa Maria de Oliveira</t>
+        </is>
+      </c>
+      <c r="AC122" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>165</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>51</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>86</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>73</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU122" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV122" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ122" t="n">
+        <v>29</v>
+      </c>
+      <c r="DA122" t="n">
+        <v>71</v>
+      </c>
+      <c r="DB122" t="n">
+        <v>7</v>
+      </c>
+      <c r="DC122" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD122" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE122" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF122" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DG122" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DH122" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DI122" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DJ122" t="n">
+        <v>71</v>
+      </c>
+      <c r="DK122" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL122" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DM122" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN122" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DO122" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU122" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV122" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW122" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="DX122" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="DY122" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="DZ122" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EA122" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EB122" t="inlineStr"/>
+      <c r="EC122" t="inlineStr"/>
+      <c r="ED122" t="inlineStr"/>
+      <c r="EE122" t="inlineStr"/>
+      <c r="EF122" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EG122" t="inlineStr">
+        <is>
+          <t>3.91</t>
+        </is>
+      </c>
+      <c r="EH122" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EI122" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EJ122" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EK122" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="EL122" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="EM122" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="EN122" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="EO122" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EP122" t="inlineStr">
+        <is>
+          <t>3.23</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP128" headerRowCount="1">
-  <autoFilter ref="A1:EP128"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP129" headerRowCount="1">
+  <autoFilter ref="A1:EP129"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP128"/>
+  <dimension ref="A1:EP129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3698,7 +3698,7 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE6" t="n">
         <v>1.71</v>
@@ -9947,7 +9947,7 @@
         <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -13762,7 +13762,7 @@
         <v>0</v>
       </c>
       <c r="DD27" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE27" t="n">
         <v>0.88</v>
@@ -14283,7 +14283,7 @@
         <v>2.36</v>
       </c>
       <c r="DO28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -16683,7 +16683,7 @@
         <v>2.19</v>
       </c>
       <c r="DO33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -19011,7 +19011,7 @@
         <v>2.27</v>
       </c>
       <c r="DO38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -20866,7 +20866,7 @@
         <v>75</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE42" t="n">
         <v>1.5</v>
@@ -24651,7 +24651,7 @@
         <v>4.03</v>
       </c>
       <c r="DO50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -26954,7 +26954,7 @@
         <v>84</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE55" t="n">
         <v>1.29</v>
@@ -30819,7 +30819,7 @@
         <v>3.76</v>
       </c>
       <c r="DO63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -34931,7 +34931,7 @@
         <v>3.12</v>
       </c>
       <c r="DO72" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -37779,7 +37779,7 @@
         <v>3.35</v>
       </c>
       <c r="DO78" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38706,7 +38706,7 @@
         <v>63</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE80" t="n">
         <v>1.29</v>
@@ -40147,7 +40147,7 @@
         <v>2.74</v>
       </c>
       <c r="DO83" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP83" t="b">
         <v>1</v>
@@ -44091,52 +44091,52 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
         <v>45969.75</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K92" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L92" t="n">
         <v>17</v>
       </c>
       <c r="M92" t="n">
+        <v>3</v>
+      </c>
+      <c r="N92" t="n">
+        <v>6</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
         <v>5</v>
       </c>
-      <c r="N92" t="n">
-        <v>4</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>3</v>
-      </c>
       <c r="R92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S92" t="n">
         <v>11</v>
@@ -44145,92 +44145,92 @@
         <v>6</v>
       </c>
       <c r="U92" t="n">
+        <v>16</v>
+      </c>
+      <c r="V92" t="n">
+        <v>11</v>
+      </c>
+      <c r="W92" t="n">
         <v>14</v>
       </c>
-      <c r="V92" t="n">
-        <v>9</v>
-      </c>
-      <c r="W92" t="n">
-        <v>16</v>
-      </c>
       <c r="X92" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Y92" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="Z92" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>Estádio Municipal Eng. Manuel Branco Teixeira</t>
+          <t>Caixa Futebol Campus</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>Avenida do Estádio Municipal, Chaves</t>
+          <t>, Seixal</t>
         </is>
       </c>
       <c r="AC92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD92" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE92" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN92" t="n">
         <v>1.66</v>
       </c>
-      <c r="AF92" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG92" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AH92" t="n">
+      <c r="AO92" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ92" t="n">
         <v>1.35</v>
       </c>
-      <c r="AI92" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AJ92" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AK92" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL92" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM92" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN92" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO92" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AP92" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ92" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AR92" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AS92" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="AT92" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AU92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW92" t="n">
         <v>1</v>
@@ -44239,22 +44239,22 @@
         <v>0</v>
       </c>
       <c r="AY92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB92" t="n">
-        <v>1037</v>
+        <v>4841</v>
       </c>
       <c r="BC92" t="n">
         <v>0</v>
       </c>
       <c r="BD92" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="BE92" t="n">
         <v>0</v>
@@ -44263,184 +44263,184 @@
         <v>-1</v>
       </c>
       <c r="BG92" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH92" t="n">
         <v>1</v>
       </c>
       <c r="BI92" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BJ92" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BK92" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BL92" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BM92" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="BN92" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="BO92" t="n">
         <v>1</v>
       </c>
       <c r="BP92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BR92" t="n">
         <v>4</v>
       </c>
       <c r="BS92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BT92" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV92" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW92" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX92" t="n">
+        <v>111</v>
+      </c>
+      <c r="BY92" t="n">
+        <v>81</v>
+      </c>
+      <c r="BZ92" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CA92" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CB92" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="CC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR92" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS92" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU92" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV92" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX92" t="n">
         <v>8</v>
       </c>
-      <c r="BU92" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV92" t="n">
-        <v>61</v>
-      </c>
-      <c r="BW92" t="n">
-        <v>31</v>
-      </c>
-      <c r="BX92" t="n">
-        <v>77</v>
-      </c>
-      <c r="BY92" t="n">
-        <v>58</v>
-      </c>
-      <c r="BZ92" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CA92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CB92" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="CC92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN92" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR92" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS92" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU92" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV92" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX92" t="n">
-        <v>3</v>
-      </c>
       <c r="CY92" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ92" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA92" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB92" t="n">
         <v>10</v>
       </c>
-      <c r="CZ92" t="n">
-        <v>25</v>
-      </c>
-      <c r="DA92" t="n">
-        <v>75</v>
-      </c>
-      <c r="DB92" t="n">
-        <v>38</v>
-      </c>
       <c r="DC92" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="DE92" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="DF92" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DG92" t="n">
-        <v>0.25</v>
+        <v>1.2</v>
       </c>
       <c r="DH92" t="n">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="DI92" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="DJ92" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="DK92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="DL92" t="n">
-        <v>1.62</v>
+        <v>2.22</v>
       </c>
       <c r="DM92" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="DN92" t="n">
-        <v>3.05</v>
+        <v>3.69</v>
       </c>
       <c r="DO92" t="n">
         <v>14</v>
@@ -44449,10 +44449,10 @@
         <v>1</v>
       </c>
       <c r="DQ92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS92" t="b">
         <v>0</v>
@@ -44464,94 +44464,86 @@
         <v>0</v>
       </c>
       <c r="DV92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW92" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="DX92" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="DY92" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="DZ92" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EA92" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="EB92" t="inlineStr"/>
       <c r="EC92" t="inlineStr"/>
-      <c r="ED92" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EE92" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
+      <c r="ED92" t="inlineStr"/>
+      <c r="EE92" t="inlineStr"/>
       <c r="EF92" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EG92" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EH92" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="EI92" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EJ92" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EK92" t="n">
-        <v>15.18</v>
+        <v>18.59</v>
       </c>
       <c r="EL92" t="n">
-        <v>3.98</v>
+        <v>3.85</v>
       </c>
       <c r="EM92" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="EN92" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="EO92" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EP92" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.77</t>
         </is>
       </c>
     </row>
@@ -44571,40 +44563,40 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
         <v>45969.75</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K93" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L93" t="n">
         <v>17</v>
       </c>
       <c r="M93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -44613,10 +44605,10 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S93" t="n">
         <v>11</v>
@@ -44625,92 +44617,92 @@
         <v>6</v>
       </c>
       <c r="U93" t="n">
+        <v>14</v>
+      </c>
+      <c r="V93" t="n">
+        <v>9</v>
+      </c>
+      <c r="W93" t="n">
         <v>16</v>
       </c>
-      <c r="V93" t="n">
-        <v>11</v>
-      </c>
-      <c r="W93" t="n">
-        <v>14</v>
-      </c>
       <c r="X93" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Y93" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="Z93" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Caixa Futebol Campus</t>
+          <t>Estádio Municipal Eng. Manuel Branco Teixeira</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>, Seixal</t>
+          <t>Avenida do Estádio Municipal, Chaves</t>
         </is>
       </c>
       <c r="AC93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE93" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR93" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF93" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AG93" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH93" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI93" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AJ93" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AK93" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL93" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AM93" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN93" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AO93" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AP93" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AQ93" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR93" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AS93" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AT93" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AU93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW93" t="n">
         <v>1</v>
@@ -44719,22 +44711,22 @@
         <v>0</v>
       </c>
       <c r="AY93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB93" t="n">
-        <v>4841</v>
+        <v>1037</v>
       </c>
       <c r="BC93" t="n">
         <v>0</v>
       </c>
       <c r="BD93" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="BE93" t="n">
         <v>0</v>
@@ -44743,82 +44735,82 @@
         <v>-1</v>
       </c>
       <c r="BG93" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH93" t="n">
         <v>1</v>
       </c>
       <c r="BI93" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BJ93" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BK93" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BL93" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BM93" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="BN93" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BO93" t="n">
         <v>1</v>
       </c>
       <c r="BP93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR93" t="n">
         <v>4</v>
       </c>
       <c r="BS93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT93" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BU93" t="n">
         <v>1</v>
       </c>
       <c r="BV93" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="BW93" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="BX93" t="n">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="BY93" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="BZ93" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="CA93" t="n">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="CB93" t="n">
-        <v>3.34</v>
+        <v>2.53</v>
       </c>
       <c r="CC93" t="n">
         <v>0</v>
       </c>
       <c r="CD93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE93" t="n">
         <v>0</v>
       </c>
       <c r="CF93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG93" t="n">
         <v>0</v>
@@ -44839,10 +44831,10 @@
         <v>0</v>
       </c>
       <c r="CM93" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN93" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CO93" t="n">
         <v>0</v>
@@ -44854,85 +44846,85 @@
         <v>1</v>
       </c>
       <c r="CR93" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="CS93" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="CT93" t="n">
         <v>1</v>
       </c>
       <c r="CU93" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV93" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX93" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY93" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ93" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA93" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB93" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC93" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD93" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DE93" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DF93" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG93" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DH93" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DI93" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="DJ93" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK93" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL93" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DM93" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN93" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="DO93" t="n">
         <v>14</v>
       </c>
-      <c r="CV93" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX93" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY93" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ93" t="n">
-        <v>40</v>
-      </c>
-      <c r="DA93" t="n">
-        <v>90</v>
-      </c>
-      <c r="DB93" t="n">
-        <v>10</v>
-      </c>
-      <c r="DC93" t="n">
-        <v>80</v>
-      </c>
-      <c r="DD93" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="DE93" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DF93" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG93" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DH93" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI93" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DJ93" t="n">
-        <v>60</v>
-      </c>
-      <c r="DK93" t="n">
-        <v>10</v>
-      </c>
-      <c r="DL93" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="DM93" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="DN93" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="DO93" t="n">
-        <v>13</v>
-      </c>
       <c r="DP93" t="b">
         <v>1</v>
       </c>
       <c r="DQ93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS93" t="b">
         <v>0</v>
@@ -44944,86 +44936,94 @@
         <v>0</v>
       </c>
       <c r="DV93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW93" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="DX93" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="DY93" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="DZ93" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="EA93" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EB93" t="inlineStr"/>
       <c r="EC93" t="inlineStr"/>
-      <c r="ED93" t="inlineStr"/>
-      <c r="EE93" t="inlineStr"/>
+      <c r="ED93" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EE93" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
       <c r="EF93" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EG93" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="EH93" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EI93" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EJ93" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EK93" t="n">
-        <v>18.59</v>
+        <v>15.18</v>
       </c>
       <c r="EL93" t="n">
-        <v>3.85</v>
+        <v>3.98</v>
       </c>
       <c r="EM93" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EN93" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="EO93" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EP93" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -46314,7 +46314,7 @@
         <v>60</v>
       </c>
       <c r="DD96" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE96" t="n">
         <v>0.43</v>
@@ -49162,7 +49162,7 @@
         <v>50</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE102" t="n">
         <v>0.89</v>
@@ -49195,7 +49195,7 @@
         <v>3.13</v>
       </c>
       <c r="DO102" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -51687,149 +51687,149 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
         <v>45991.64583333334</v>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I108" t="n">
         <v>4</v>
       </c>
       <c r="J108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K108" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L108" t="n">
         <v>10</v>
       </c>
       <c r="M108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R108" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S108" t="n">
         <v>8</v>
       </c>
       <c r="T108" t="n">
+        <v>13</v>
+      </c>
+      <c r="U108" t="n">
+        <v>11</v>
+      </c>
+      <c r="V108" t="n">
+        <v>19</v>
+      </c>
+      <c r="W108" t="n">
+        <v>7</v>
+      </c>
+      <c r="X108" t="n">
         <v>12</v>
       </c>
-      <c r="U108" t="n">
-        <v>15</v>
-      </c>
-      <c r="V108" t="n">
-        <v>16</v>
-      </c>
-      <c r="W108" t="n">
-        <v>18</v>
-      </c>
-      <c r="X108" t="n">
-        <v>11</v>
-      </c>
       <c r="Y108" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="Z108" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Estádio Pina Manique</t>
+          <t>CGD Stadium Aurélio Pereira</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>Rua Monsanto, Lisboa</t>
+          <t>, Alcochete</t>
         </is>
       </c>
       <c r="AC108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
         <v>3</v>
       </c>
       <c r="AE108" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="AF108" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AG108" t="n">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="AH108" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AI108" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="AJ108" t="n">
-        <v>3.14</v>
+        <v>3.65</v>
       </c>
       <c r="AK108" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AL108" t="n">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AM108" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AN108" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AO108" t="n">
-        <v>2.87</v>
+        <v>2.42</v>
       </c>
       <c r="AP108" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AR108" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AS108" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AT108" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AU108" t="n">
         <v>4</v>
       </c>
       <c r="AV108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX108" t="n">
         <v>1</v>
@@ -51844,13 +51844,13 @@
         <v>2</v>
       </c>
       <c r="BB108" t="n">
-        <v>-1</v>
+        <v>1029</v>
       </c>
       <c r="BC108" t="n">
         <v>0</v>
       </c>
       <c r="BD108" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="BE108" t="n">
         <v>0</v>
@@ -51868,179 +51868,179 @@
         <v>1</v>
       </c>
       <c r="BJ108" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BK108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BL108" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BM108" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BN108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT108" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV108" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW108" t="n">
+        <v>81</v>
+      </c>
+      <c r="BX108" t="n">
+        <v>77</v>
+      </c>
+      <c r="BY108" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ108" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CA108" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CB108" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="CC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN108" t="n">
+        <v>3</v>
+      </c>
+      <c r="CO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR108" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS108" t="n">
+        <v>33</v>
+      </c>
+      <c r="CT108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU108" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV108" t="n">
         <v>7</v>
       </c>
-      <c r="BO108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR108" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT108" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU108" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV108" t="n">
-        <v>31</v>
-      </c>
-      <c r="BW108" t="n">
+      <c r="CW108" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX108" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY108" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ108" t="n">
         <v>39</v>
       </c>
-      <c r="BX108" t="n">
-        <v>63</v>
-      </c>
-      <c r="BY108" t="n">
+      <c r="DA108" t="n">
+        <v>72</v>
+      </c>
+      <c r="DB108" t="n">
+        <v>37</v>
+      </c>
+      <c r="DC108" t="n">
+        <v>65</v>
+      </c>
+      <c r="DD108" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DE108" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF108" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DG108" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH108" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DI108" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DJ108" t="n">
         <v>62</v>
       </c>
-      <c r="BZ108" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CA108" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CB108" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="CC108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP108" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR108" t="n">
+      <c r="DK108" t="n">
+        <v>29</v>
+      </c>
+      <c r="DL108" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="DM108" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DN108" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="DO108" t="n">
         <v>14</v>
       </c>
-      <c r="CS108" t="n">
-        <v>24</v>
-      </c>
-      <c r="CT108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU108" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV108" t="n">
-        <v>18</v>
-      </c>
-      <c r="CW108" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX108" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY108" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ108" t="n">
-        <v>50</v>
-      </c>
-      <c r="DA108" t="n">
-        <v>80</v>
-      </c>
-      <c r="DB108" t="n">
-        <v>50</v>
-      </c>
-      <c r="DC108" t="n">
-        <v>80</v>
-      </c>
-      <c r="DD108" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DE108" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF108" t="n">
-        <v>2</v>
-      </c>
-      <c r="DG108" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH108" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="DI108" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="DJ108" t="n">
-        <v>50</v>
-      </c>
-      <c r="DK108" t="n">
-        <v>20</v>
-      </c>
-      <c r="DL108" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="DM108" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DN108" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="DO108" t="n">
-        <v>13</v>
-      </c>
       <c r="DP108" t="b">
         <v>1</v>
       </c>
@@ -52064,90 +52064,98 @@
       </c>
       <c r="DW108" t="inlineStr">
         <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="DX108" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="DY108" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="DZ108" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="EA108" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EB108" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="EC108" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="ED108" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EE108" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF108" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EG108" t="inlineStr">
+        <is>
+          <t>3.83</t>
+        </is>
+      </c>
+      <c r="EH108" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EI108" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EJ108" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EK108" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="EL108" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="EM108" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="EN108" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="EO108" t="inlineStr">
+        <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="DX108" t="inlineStr">
+      <c r="EP108" t="inlineStr">
         <is>
           <t>3.14</t>
-        </is>
-      </c>
-      <c r="DY108" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="DZ108" t="inlineStr">
-        <is>
-          <t>3.16</t>
-        </is>
-      </c>
-      <c r="EA108" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
-      <c r="EB108" t="inlineStr"/>
-      <c r="EC108" t="inlineStr"/>
-      <c r="ED108" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EE108" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
-      <c r="EF108" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="EG108" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="EH108" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="EI108" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="EJ108" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EK108" t="n">
-        <v>14.24</v>
-      </c>
-      <c r="EL108" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="EM108" t="inlineStr">
-        <is>
-          <t>46%</t>
-        </is>
-      </c>
-      <c r="EN108" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="EO108" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EP108" t="inlineStr">
-        <is>
-          <t>2.79</t>
         </is>
       </c>
     </row>
@@ -52167,149 +52175,149 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
         <v>45991.64583333334</v>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I109" t="n">
         <v>4</v>
       </c>
       <c r="J109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K109" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L109" t="n">
         <v>10</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q109" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R109" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S109" t="n">
         <v>8</v>
       </c>
       <c r="T109" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U109" t="n">
+        <v>15</v>
+      </c>
+      <c r="V109" t="n">
+        <v>16</v>
+      </c>
+      <c r="W109" t="n">
+        <v>18</v>
+      </c>
+      <c r="X109" t="n">
         <v>11</v>
       </c>
-      <c r="V109" t="n">
-        <v>19</v>
-      </c>
-      <c r="W109" t="n">
-        <v>7</v>
-      </c>
-      <c r="X109" t="n">
-        <v>12</v>
-      </c>
       <c r="Y109" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="Z109" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>CGD Stadium Aurélio Pereira</t>
+          <t>Estádio Pina Manique</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>, Alcochete</t>
+          <t>Rua Monsanto, Lisboa</t>
         </is>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD109" t="n">
         <v>3</v>
       </c>
       <c r="AE109" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="AF109" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AG109" t="n">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="AH109" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AI109" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AJ109" t="n">
-        <v>3.65</v>
+        <v>3.14</v>
       </c>
       <c r="AK109" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AL109" t="n">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="AM109" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AN109" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AO109" t="n">
-        <v>2.42</v>
+        <v>2.87</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AR109" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="AS109" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AT109" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AU109" t="n">
         <v>4</v>
       </c>
       <c r="AV109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX109" t="n">
         <v>1</v>
@@ -52324,13 +52332,13 @@
         <v>2</v>
       </c>
       <c r="BB109" t="n">
-        <v>1029</v>
+        <v>-1</v>
       </c>
       <c r="BC109" t="n">
         <v>0</v>
       </c>
       <c r="BD109" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="BE109" t="n">
         <v>0</v>
@@ -52348,28 +52356,28 @@
         <v>1</v>
       </c>
       <c r="BJ109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK109" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL109" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM109" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN109" t="n">
         <v>7</v>
       </c>
-      <c r="BK109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL109" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM109" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN109" t="n">
-        <v>2</v>
-      </c>
       <c r="BO109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR109" t="n">
         <v>2</v>
@@ -52378,31 +52386,31 @@
         <v>1</v>
       </c>
       <c r="BT109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU109" t="n">
         <v>1</v>
       </c>
       <c r="BV109" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="BW109" t="n">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="BX109" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="BY109" t="n">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="BZ109" t="n">
-        <v>1.18</v>
+        <v>1.66</v>
       </c>
       <c r="CA109" t="n">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="CB109" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="CC109" t="n">
         <v>0</v>
@@ -52438,7 +52446,7 @@
         <v>0</v>
       </c>
       <c r="CN109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CO109" t="n">
         <v>0</v>
@@ -52450,73 +52458,73 @@
         <v>1</v>
       </c>
       <c r="CR109" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="CS109" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="CT109" t="n">
         <v>1</v>
       </c>
       <c r="CU109" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CV109" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW109" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX109" t="n">
         <v>7</v>
       </c>
-      <c r="CW109" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX109" t="n">
-        <v>9</v>
-      </c>
       <c r="CY109" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CZ109" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="DA109" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="DB109" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="DC109" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="DD109" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="DE109" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DF109" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="DG109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DH109" t="n">
-        <v>2.09</v>
+        <v>1.73</v>
       </c>
       <c r="DI109" t="n">
-        <v>1.45</v>
+        <v>0.91</v>
       </c>
       <c r="DJ109" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="DK109" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="DL109" t="n">
-        <v>2.04</v>
+        <v>1.49</v>
       </c>
       <c r="DM109" t="n">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="DN109" t="n">
-        <v>3.55</v>
+        <v>2.69</v>
       </c>
       <c r="DO109" t="n">
         <v>14</v>
@@ -52544,98 +52552,90 @@
       </c>
       <c r="DW109" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="DX109" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="DY109" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="DZ109" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="EA109" t="inlineStr">
         <is>
-          <t>3.28</t>
-        </is>
-      </c>
-      <c r="EB109" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="EC109" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EB109" t="inlineStr"/>
+      <c r="EC109" t="inlineStr"/>
       <c r="ED109" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EE109" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EF109" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EG109" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="EH109" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="EI109" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EJ109" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EK109" t="n">
-        <v>14.07</v>
+        <v>14.24</v>
       </c>
       <c r="EL109" t="n">
-        <v>10.39</v>
+        <v>7.36</v>
       </c>
       <c r="EM109" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="EN109" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="EO109" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EP109" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.79</t>
         </is>
       </c>
     </row>
@@ -54854,7 +54854,7 @@
         <v>69</v>
       </c>
       <c r="DD114" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE114" t="n">
         <v>1.43</v>
@@ -55023,12 +55023,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
@@ -55038,22 +55038,22 @@
         <v>2</v>
       </c>
       <c r="H115" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L115" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M115" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
         <v>2</v>
@@ -55065,128 +55065,128 @@
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S115" t="n">
         <v>17</v>
       </c>
       <c r="T115" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U115" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V115" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W115" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X115" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y115" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="Z115" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>Estádio do Mar</t>
+          <t>Caixa Futebol Campus</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>Lugar da Cruz de Pau, Matosinhos</t>
+          <t>, Seixal</t>
         </is>
       </c>
       <c r="AC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG115" t="n">
         <v>5</v>
       </c>
-      <c r="AD115" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE115" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF115" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG115" t="n">
-        <v>3</v>
-      </c>
       <c r="AH115" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AI115" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AJ115" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="AK115" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AL115" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN115" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.63</v>
+        <v>3.17</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AR115" t="n">
-        <v>3.23</v>
+        <v>2.55</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AU115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV115" t="n">
         <v>1</v>
       </c>
       <c r="AW115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX115" t="n">
         <v>1</v>
       </c>
       <c r="AY115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB115" t="n">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="BC115" t="n">
         <v>0</v>
       </c>
       <c r="BD115" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="BE115" t="n">
         <v>0</v>
@@ -55195,184 +55195,184 @@
         <v>-1</v>
       </c>
       <c r="BG115" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH115" t="n">
         <v>1</v>
       </c>
       <c r="BI115" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BJ115" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BK115" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BL115" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BM115" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="BN115" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BO115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BP115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT115" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BU115" t="n">
         <v>1</v>
       </c>
       <c r="BV115" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="BW115" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="BX115" t="n">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="BY115" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="BZ115" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="CA115" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CB115" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="CC115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP115" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR115" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS115" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU115" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV115" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW115" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX115" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY115" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ115" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA115" t="n">
+        <v>70</v>
+      </c>
+      <c r="DB115" t="n">
+        <v>17</v>
+      </c>
+      <c r="DC115" t="n">
+        <v>62</v>
+      </c>
+      <c r="DD115" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DE115" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF115" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DG115" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DH115" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DI115" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ115" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK115" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL115" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DM115" t="n">
         <v>1.17</v>
       </c>
-      <c r="CB115" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="CC115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP115" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR115" t="n">
-        <v>20</v>
-      </c>
-      <c r="CS115" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU115" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV115" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW115" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX115" t="n">
-        <v>4</v>
-      </c>
-      <c r="CY115" t="n">
-        <v>14</v>
-      </c>
-      <c r="CZ115" t="n">
-        <v>49</v>
-      </c>
-      <c r="DA115" t="n">
-        <v>66</v>
-      </c>
-      <c r="DB115" t="n">
-        <v>49</v>
-      </c>
-      <c r="DC115" t="n">
-        <v>86</v>
-      </c>
-      <c r="DD115" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DE115" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DF115" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="DG115" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="DH115" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI115" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DJ115" t="n">
-        <v>52</v>
-      </c>
-      <c r="DK115" t="n">
-        <v>35</v>
-      </c>
-      <c r="DL115" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="DM115" t="n">
-        <v>1.34</v>
-      </c>
       <c r="DN115" t="n">
-        <v>2.82</v>
+        <v>3.35</v>
       </c>
       <c r="DO115" t="n">
         <v>14</v>
@@ -55384,83 +55384,91 @@
         <v>1</v>
       </c>
       <c r="DR115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV115" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW115" t="inlineStr"/>
-      <c r="DX115" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DW115" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="DX115" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
       <c r="DY115" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="DZ115" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="EA115" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="EB115" t="inlineStr"/>
       <c r="EC115" t="inlineStr"/>
       <c r="ED115" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EE115" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EF115" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EG115" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="EH115" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="EI115" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EJ115" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EK115" t="n">
-        <v>15.66</v>
+        <v>18.3</v>
       </c>
       <c r="EL115" t="n">
-        <v>8.699999999999999</v>
+        <v>3.67</v>
       </c>
       <c r="EM115" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="EN115" t="inlineStr">
@@ -55468,8 +55476,16 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="EO115" t="inlineStr"/>
-      <c r="EP115" t="inlineStr"/>
+      <c r="EO115" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EP115" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -55487,12 +55503,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
@@ -55502,22 +55518,22 @@
         <v>2</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J116" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K116" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N116" t="n">
         <v>2</v>
@@ -55529,128 +55545,128 @@
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S116" t="n">
         <v>17</v>
       </c>
       <c r="T116" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U116" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V116" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W116" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y116" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="Z116" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>Caixa Futebol Campus</t>
+          <t>Estádio do Mar</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>, Seixal</t>
+          <t>Lugar da Cruz de Pau, Matosinhos</t>
         </is>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD116" t="n">
         <v>2</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.63</v>
+        <v>2.04</v>
       </c>
       <c r="AF116" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AG116" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AI116" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AJ116" t="n">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="AK116" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AL116" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AM116" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AN116" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AO116" t="n">
-        <v>3.17</v>
+        <v>2.63</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AR116" t="n">
-        <v>2.55</v>
+        <v>3.23</v>
       </c>
       <c r="AS116" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="AT116" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AU116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV116" t="n">
         <v>1</v>
       </c>
       <c r="AW116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX116" t="n">
         <v>1</v>
       </c>
       <c r="AY116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB116" t="n">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
       </c>
       <c r="BD116" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="BE116" t="n">
         <v>0</v>
@@ -55659,82 +55675,82 @@
         <v>-1</v>
       </c>
       <c r="BG116" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH116" t="n">
         <v>1</v>
       </c>
       <c r="BI116" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BJ116" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BK116" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BL116" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BM116" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BN116" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BO116" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BP116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BT116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BU116" t="n">
         <v>1</v>
       </c>
       <c r="BV116" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="BW116" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="BX116" t="n">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="BY116" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="BZ116" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="CA116" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="CB116" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="CC116" t="n">
         <v>0</v>
       </c>
       <c r="CD116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE116" t="n">
         <v>0</v>
       </c>
       <c r="CF116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG116" t="n">
         <v>0</v>
@@ -55755,10 +55771,10 @@
         <v>0</v>
       </c>
       <c r="CM116" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN116" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO116" t="n">
         <v>0</v>
@@ -55770,76 +55786,76 @@
         <v>1</v>
       </c>
       <c r="CR116" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CS116" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CT116" t="n">
         <v>1</v>
       </c>
       <c r="CU116" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CV116" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CW116" t="n">
         <v>1</v>
       </c>
       <c r="CX116" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CY116" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CZ116" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="DA116" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="DB116" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="DC116" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DE116" t="n">
-        <v>0.5</v>
+        <v>1.17</v>
       </c>
       <c r="DF116" t="n">
-        <v>0.83</v>
+        <v>1.29</v>
       </c>
       <c r="DG116" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="DH116" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI116" t="n">
         <v>0.92</v>
       </c>
-      <c r="DI116" t="n">
-        <v>1.25</v>
-      </c>
       <c r="DJ116" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="DK116" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="DL116" t="n">
-        <v>2.18</v>
+        <v>1.48</v>
       </c>
       <c r="DM116" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="DN116" t="n">
-        <v>3.35</v>
+        <v>2.82</v>
       </c>
       <c r="DO116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -55848,91 +55864,83 @@
         <v>1</v>
       </c>
       <c r="DR116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV116" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW116" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="DX116" t="inlineStr">
-        <is>
-          <t>3.08</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="DW116" t="inlineStr"/>
+      <c r="DX116" t="inlineStr"/>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="EA116" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="EB116" t="inlineStr"/>
       <c r="EC116" t="inlineStr"/>
       <c r="ED116" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EE116" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF116" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EG116" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="EH116" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EI116" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EJ116" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EK116" t="n">
-        <v>18.3</v>
+        <v>15.66</v>
       </c>
       <c r="EL116" t="n">
-        <v>3.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="EM116" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="EN116" t="inlineStr">
@@ -55940,16 +55948,8 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="EO116" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EP116" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
+      <c r="EO116" t="inlineStr"/>
+      <c r="EP116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -57899,16 +57899,16 @@
         <v>1</v>
       </c>
       <c r="S121" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T121" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V121" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W121" t="n">
         <v>13</v>
@@ -57917,10 +57917,10 @@
         <v>16</v>
       </c>
       <c r="Y121" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="Z121" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
@@ -58080,13 +58080,13 @@
         <v>91</v>
       </c>
       <c r="BZ121" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="CA121" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="CB121" t="n">
-        <v>2.51</v>
+        <v>2.64</v>
       </c>
       <c r="CC121" t="n">
         <v>0</v>
@@ -58143,19 +58143,19 @@
         <v>1</v>
       </c>
       <c r="CU121" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV121" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CW121" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX121" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CY121" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CZ121" t="n">
         <v>47</v>
@@ -58373,19 +58373,19 @@
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R122" t="n">
+        <v>8</v>
+      </c>
+      <c r="S122" t="n">
         <v>9</v>
       </c>
-      <c r="S122" t="n">
-        <v>8</v>
-      </c>
       <c r="T122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U122" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V122" t="n">
         <v>11</v>
@@ -58397,10 +58397,10 @@
         <v>17</v>
       </c>
       <c r="Y122" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z122" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
@@ -58560,13 +58560,13 @@
         <v>73</v>
       </c>
       <c r="BZ122" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="CA122" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="CB122" t="n">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="CC122" t="n">
         <v>0</v>
@@ -58617,25 +58617,25 @@
         <v>18</v>
       </c>
       <c r="CS122" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU122" t="n">
         <v>18</v>
       </c>
-      <c r="CT122" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU122" t="n">
-        <v>20</v>
-      </c>
       <c r="CV122" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CW122" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX122" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CY122" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CZ122" t="n">
         <v>29</v>
@@ -58845,19 +58845,19 @@
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R123" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
       </c>
       <c r="T123" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U123" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V123" t="n">
         <v>21</v>
@@ -59032,13 +59032,13 @@
         <v>69</v>
       </c>
       <c r="BZ123" t="n">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="CA123" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="CB123" t="n">
-        <v>4</v>
+        <v>3.59</v>
       </c>
       <c r="CC123" t="n">
         <v>0</v>
@@ -59095,19 +59095,19 @@
         <v>1</v>
       </c>
       <c r="CU123" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CV123" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CW123" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX123" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CY123" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CZ123" t="n">
         <v>24</v>
@@ -59325,22 +59325,22 @@
         <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R124" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T124" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U124" t="n">
         <v>11</v>
       </c>
       <c r="V124" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="W124" t="n">
         <v>18</v>
@@ -59349,10 +59349,10 @@
         <v>11</v>
       </c>
       <c r="Y124" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="Z124" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
@@ -59512,13 +59512,13 @@
         <v>86</v>
       </c>
       <c r="BZ124" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="CA124" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="CB124" t="n">
-        <v>3.11</v>
+        <v>3.28</v>
       </c>
       <c r="CC124" t="n">
         <v>0</v>
@@ -59578,16 +59578,16 @@
         <v>11</v>
       </c>
       <c r="CV124" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="CW124" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX124" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CY124" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CZ124" t="n">
         <v>50</v>
@@ -59797,7 +59797,7 @@
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R125" t="n">
         <v>2</v>
@@ -59806,13 +59806,13 @@
         <v>7</v>
       </c>
       <c r="T125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U125" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V125" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W125" t="n">
         <v>10</v>
@@ -59821,10 +59821,10 @@
         <v>7</v>
       </c>
       <c r="Y125" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Z125" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
@@ -59984,13 +59984,13 @@
         <v>108</v>
       </c>
       <c r="BZ125" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="CA125" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="CB125" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="CC125" t="n">
         <v>0</v>
@@ -60047,19 +60047,19 @@
         <v>1</v>
       </c>
       <c r="CU125" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="CV125" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="CW125" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX125" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CY125" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CZ125" t="n">
         <v>31</v>
@@ -60265,22 +60265,22 @@
         <v>1</v>
       </c>
       <c r="Q126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R126" t="n">
         <v>7</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U126" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="V126" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W126" t="n">
         <v>14</v>
@@ -60289,10 +60289,10 @@
         <v>15</v>
       </c>
       <c r="Y126" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Z126" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
@@ -60395,28 +60395,28 @@
         <v>-1</v>
       </c>
       <c r="BG126" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH126" t="n">
         <v>1</v>
       </c>
       <c r="BI126" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BJ126" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK126" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BL126" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BM126" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BN126" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BO126" t="n">
         <v>3</v>
@@ -60452,13 +60452,13 @@
         <v>58</v>
       </c>
       <c r="BZ126" t="n">
-        <v>1.49</v>
+        <v>1.98</v>
       </c>
       <c r="CA126" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="CB126" t="n">
-        <v>2.72</v>
+        <v>3.33</v>
       </c>
       <c r="CC126" t="n">
         <v>0</v>
@@ -60491,10 +60491,10 @@
         <v>0</v>
       </c>
       <c r="CM126" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CN126" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO126" t="n">
         <v>0</v>
@@ -60515,19 +60515,19 @@
         <v>1</v>
       </c>
       <c r="CU126" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CV126" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="CW126" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX126" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CY126" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CZ126" t="n">
         <v>31</v>
@@ -61209,22 +61209,22 @@
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R128" t="n">
         <v>7</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T128" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U128" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="V128" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W128" t="n">
         <v>20</v>
@@ -61396,13 +61396,13 @@
         <v>72</v>
       </c>
       <c r="BZ128" t="n">
-        <v>1.66</v>
+        <v>1.48</v>
       </c>
       <c r="CA128" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="CB128" t="n">
-        <v>3.29</v>
+        <v>2.98</v>
       </c>
       <c r="CC128" t="n">
         <v>0</v>
@@ -61544,42 +61544,42 @@
       </c>
       <c r="DW128" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="DX128" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="DY128" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="DZ128" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="EA128" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="EB128" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EC128" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="ED128" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EE128" t="inlineStr">
@@ -61589,27 +61589,27 @@
       </c>
       <c r="EF128" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EG128" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="EH128" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EI128" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EJ128" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EK128" t="n">
@@ -61635,7 +61635,487 @@
       </c>
       <c r="EP128" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>LigaPro_Portugal_2a_división_2025-2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>14</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>CS Marítimo</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Benfica II</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>46007.70833333334</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" t="n">
+        <v>2</v>
+      </c>
+      <c r="J129" t="n">
+        <v>4</v>
+      </c>
+      <c r="K129" t="n">
+        <v>5</v>
+      </c>
+      <c r="L129" t="n">
+        <v>9</v>
+      </c>
+      <c r="M129" t="n">
+        <v>2</v>
+      </c>
+      <c r="N129" t="n">
+        <v>5</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>4</v>
+      </c>
+      <c r="R129" t="n">
+        <v>4</v>
+      </c>
+      <c r="S129" t="n">
+        <v>4</v>
+      </c>
+      <c r="T129" t="n">
+        <v>4</v>
+      </c>
+      <c r="U129" t="n">
+        <v>8</v>
+      </c>
+      <c r="V129" t="n">
+        <v>8</v>
+      </c>
+      <c r="W129" t="n">
+        <v>19</v>
+      </c>
+      <c r="X129" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>Campo da Imaculada Conceição</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>, Ilha da Madeira</t>
+        </is>
+      </c>
+      <c r="AC129" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>47</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>43</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>77</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>72</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>25</v>
+      </c>
+      <c r="CT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU129" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV129" t="n">
+        <v>23</v>
+      </c>
+      <c r="CW129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ129" t="n">
+        <v>44</v>
+      </c>
+      <c r="DA129" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB129" t="n">
+        <v>54</v>
+      </c>
+      <c r="DC129" t="n">
+        <v>79</v>
+      </c>
+      <c r="DD129" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE129" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF129" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG129" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH129" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DI129" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DJ129" t="n">
+        <v>57</v>
+      </c>
+      <c r="DK129" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL129" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DM129" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DN129" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="DO129" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU129" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV129" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW129" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="DX129" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
+      <c r="DY129" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="DZ129" t="inlineStr">
+        <is>
+          <t>5.05</t>
+        </is>
+      </c>
+      <c r="EA129" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="EB129" t="inlineStr"/>
+      <c r="EC129" t="inlineStr"/>
+      <c r="ED129" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EE129" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EF129" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EG129" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="EH129" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EI129" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EJ129" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EK129" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="EL129" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="EM129" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="EN129" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="EO129" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EP129" t="inlineStr">
+        <is>
+          <t>2.70</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -61215,16 +61215,16 @@
         <v>7</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T128" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U128" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="V128" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="W128" t="n">
         <v>20</v>
@@ -61233,10 +61233,10 @@
         <v>16</v>
       </c>
       <c r="Y128" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Z128" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
@@ -61396,13 +61396,13 @@
         <v>72</v>
       </c>
       <c r="BZ128" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="CA128" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="CB128" t="n">
-        <v>2.98</v>
+        <v>3.29</v>
       </c>
       <c r="CC128" t="n">
         <v>0</v>
@@ -61459,19 +61459,19 @@
         <v>1</v>
       </c>
       <c r="CU128" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CV128" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="CW128" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX128" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CY128" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CZ128" t="n">
         <v>75</v>
@@ -61697,22 +61697,22 @@
         <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R129" t="n">
         <v>4</v>
       </c>
       <c r="S129" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T129" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U129" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V129" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W129" t="n">
         <v>19</v>
@@ -61721,10 +61721,10 @@
         <v>17</v>
       </c>
       <c r="Y129" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Z129" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
@@ -61884,13 +61884,13 @@
         <v>72</v>
       </c>
       <c r="BZ129" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="CA129" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="CB129" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="CC129" t="n">
         <v>0</v>
@@ -61950,16 +61950,16 @@
         <v>17</v>
       </c>
       <c r="CV129" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CW129" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX129" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY129" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CZ129" t="n">
         <v>44</v>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -63601,22 +63601,22 @@
         <v>1</v>
       </c>
       <c r="Q133" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S133" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="T133" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U133" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="V133" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="W133" t="n">
         <v>10</v>
@@ -63625,10 +63625,10 @@
         <v>14</v>
       </c>
       <c r="Y133" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="Z133" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
@@ -63788,13 +63788,13 @@
         <v>45</v>
       </c>
       <c r="BZ133" t="n">
-        <v>1.75</v>
+        <v>2.18</v>
       </c>
       <c r="CA133" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="CB133" t="n">
-        <v>2.87</v>
+        <v>3.68</v>
       </c>
       <c r="CC133" t="n">
         <v>0</v>
@@ -63854,16 +63854,16 @@
         <v>14</v>
       </c>
       <c r="CV133" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CW133" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX133" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CY133" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CZ133" t="n">
         <v>47</v>
@@ -64076,13 +64076,13 @@
         <v>6</v>
       </c>
       <c r="R134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S134" t="n">
         <v>4</v>
       </c>
       <c r="T134" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U134" t="n">
         <v>10</v>
@@ -64097,10 +64097,10 @@
         <v>19</v>
       </c>
       <c r="Y134" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="Z134" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
@@ -64263,10 +64263,10 @@
         <v>1.39</v>
       </c>
       <c r="CA134" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="CB134" t="n">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="CC134" t="n">
         <v>0</v>
@@ -64323,19 +64323,19 @@
         <v>1</v>
       </c>
       <c r="CU134" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CV134" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CW134" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX134" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CY134" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CZ134" t="n">
         <v>32</v>
@@ -64561,22 +64561,22 @@
         <v>0</v>
       </c>
       <c r="Q135" t="n">
+        <v>6</v>
+      </c>
+      <c r="R135" t="n">
         <v>5</v>
       </c>
-      <c r="R135" t="n">
-        <v>8</v>
-      </c>
       <c r="S135" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T135" t="n">
         <v>7</v>
       </c>
       <c r="U135" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V135" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W135" t="n">
         <v>10</v>
@@ -64585,10 +64585,10 @@
         <v>22</v>
       </c>
       <c r="Y135" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z135" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
@@ -64748,13 +64748,13 @@
         <v>70</v>
       </c>
       <c r="BZ135" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="CA135" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="CB135" t="n">
-        <v>3.47</v>
+        <v>3.27</v>
       </c>
       <c r="CC135" t="n">
         <v>0</v>
@@ -64811,19 +64811,19 @@
         <v>1</v>
       </c>
       <c r="CU135" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="CV135" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CW135" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX135" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CY135" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CZ135" t="n">
         <v>31</v>
@@ -65020,19 +65020,19 @@
         <v>5</v>
       </c>
       <c r="R136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S136" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T136" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U136" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V136" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W136" t="n">
         <v>16</v>
@@ -65041,10 +65041,10 @@
         <v>17</v>
       </c>
       <c r="Y136" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="Z136" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
@@ -65204,13 +65204,13 @@
         <v>77</v>
       </c>
       <c r="BZ136" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="CA136" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="CB136" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="CC136" t="n">
         <v>0</v>
@@ -65270,16 +65270,16 @@
         <v>17</v>
       </c>
       <c r="CV136" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CW136" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX136" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CY136" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CZ136" t="n">
         <v>22</v>
@@ -65497,22 +65497,22 @@
         <v>2</v>
       </c>
       <c r="Q137" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R137" t="n">
         <v>4</v>
       </c>
       <c r="S137" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T137" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U137" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="V137" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W137" t="n">
         <v>9</v>
@@ -65521,10 +65521,10 @@
         <v>24</v>
       </c>
       <c r="Y137" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z137" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
@@ -65684,13 +65684,13 @@
         <v>52</v>
       </c>
       <c r="BZ137" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="CA137" t="n">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
       <c r="CB137" t="n">
-        <v>2.43</v>
+        <v>3.18</v>
       </c>
       <c r="CC137" t="n">
         <v>1</v>
@@ -65741,7 +65741,7 @@
         <v>23</v>
       </c>
       <c r="CS137" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="CT137" t="n">
         <v>1</v>
@@ -65753,13 +65753,13 @@
         <v>9</v>
       </c>
       <c r="CW137" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX137" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CY137" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CZ137" t="n">
         <v>43</v>
@@ -65940,13 +65940,13 @@
         <v>1</v>
       </c>
       <c r="J138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K138" t="n">
         <v>3</v>
       </c>
       <c r="L138" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M138" t="n">
         <v>0</v>
@@ -65961,22 +65961,22 @@
         <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R138" t="n">
+        <v>7</v>
+      </c>
+      <c r="S138" t="n">
         <v>8</v>
       </c>
-      <c r="S138" t="n">
-        <v>6</v>
-      </c>
       <c r="T138" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="U138" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V138" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="W138" t="n">
         <v>12</v>
@@ -65985,10 +65985,10 @@
         <v>16</v>
       </c>
       <c r="Y138" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="Z138" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
@@ -66148,13 +66148,13 @@
         <v>174</v>
       </c>
       <c r="BZ138" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="CA138" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="CB138" t="n">
-        <v>3.39</v>
+        <v>3.82</v>
       </c>
       <c r="CC138" t="n">
         <v>0</v>
@@ -66202,28 +66202,28 @@
         <v>1</v>
       </c>
       <c r="CR138" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS138" t="n">
         <v>16</v>
       </c>
-      <c r="CS138" t="n">
-        <v>14</v>
-      </c>
       <c r="CT138" t="n">
         <v>1</v>
       </c>
       <c r="CU138" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CV138" t="n">
         <v>13</v>
       </c>
       <c r="CW138" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX138" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CY138" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CZ138" t="n">
         <v>30</v>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -65964,13 +65964,13 @@
         <v>2</v>
       </c>
       <c r="R138" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S138" t="n">
         <v>8</v>
       </c>
       <c r="T138" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U138" t="n">
         <v>10</v>
@@ -65985,10 +65985,10 @@
         <v>16</v>
       </c>
       <c r="Y138" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Z138" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
@@ -66151,10 +66151,10 @@
         <v>1.12</v>
       </c>
       <c r="CA138" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="CB138" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="CC138" t="n">
         <v>0</v>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -70169,10 +70169,10 @@
         <v>10</v>
       </c>
       <c r="M147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N147" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -70221,10 +70221,10 @@
         </is>
       </c>
       <c r="AC147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD147" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE147" t="n">
         <v>1.8</v>
@@ -70341,16 +70341,16 @@
         <v>2</v>
       </c>
       <c r="BQ147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS147" t="n">
         <v>3</v>
       </c>
       <c r="BT147" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BU147" t="n">
         <v>1</v>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP148" headerRowCount="1">
-  <autoFilter ref="A1:EP148"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP149" headerRowCount="1">
+  <autoFilter ref="A1:EP149"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP148"/>
+  <dimension ref="A1:EP149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -9947,7 +9947,7 @@
         <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -13315,7 +13315,7 @@
         <v>3.03</v>
       </c>
       <c r="DO26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -14283,7 +14283,7 @@
         <v>2.36</v>
       </c>
       <c r="DO28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -19483,7 +19483,7 @@
         <v>3.2</v>
       </c>
       <c r="DO39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP39" t="b">
         <v>0</v>
@@ -19955,7 +19955,7 @@
         <v>3.34</v>
       </c>
       <c r="DO40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -27475,7 +27475,7 @@
         <v>3.65</v>
       </c>
       <c r="DO56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP56" t="b">
         <v>1</v>
@@ -36947,146 +36947,146 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
         <v>45960.75</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H77" t="n">
         <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L77" t="n">
+        <v>15</v>
+      </c>
+      <c r="M77" t="n">
+        <v>3</v>
+      </c>
+      <c r="N77" t="n">
+        <v>2</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
         <v>6</v>
       </c>
-      <c r="M77" t="n">
-        <v>2</v>
-      </c>
-      <c r="N77" t="n">
-        <v>1</v>
-      </c>
-      <c r="O77" t="n">
-        <v>1</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="n">
+        <v>10</v>
+      </c>
+      <c r="U77" t="n">
+        <v>16</v>
+      </c>
+      <c r="V77" t="n">
+        <v>11</v>
+      </c>
+      <c r="W77" t="n">
+        <v>17</v>
+      </c>
+      <c r="X77" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Caixa Futebol Campus</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>, Seixal</t>
+        </is>
+      </c>
+      <c r="AC77" t="n">
         <v>3</v>
       </c>
-      <c r="R77" t="n">
-        <v>3</v>
-      </c>
-      <c r="S77" t="n">
-        <v>4</v>
-      </c>
-      <c r="T77" t="n">
-        <v>9</v>
-      </c>
-      <c r="U77" t="n">
-        <v>7</v>
-      </c>
-      <c r="V77" t="n">
-        <v>12</v>
-      </c>
-      <c r="W77" t="n">
-        <v>14</v>
-      </c>
-      <c r="X77" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>Estádio Municipal de Portimão</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>Avenida Zeca Afonso Portimão, Portimão</t>
-        </is>
-      </c>
-      <c r="AC77" t="n">
-        <v>4</v>
-      </c>
       <c r="AD77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE77" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF77" t="n">
         <v>3.3</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.33</v>
+        <v>4.09</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AI77" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AJ77" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU77" t="n">
         <v>3</v>
       </c>
-      <c r="AK77" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL77" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AM77" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN77" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AO77" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AP77" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AQ77" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR77" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AS77" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT77" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AU77" t="n">
-        <v>1</v>
-      </c>
       <c r="AV77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW77" t="n">
         <v>0</v>
@@ -37101,16 +37101,16 @@
         <v>1</v>
       </c>
       <c r="BA77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB77" t="n">
-        <v>4835</v>
+        <v>1031</v>
       </c>
       <c r="BC77" t="n">
         <v>0</v>
       </c>
       <c r="BD77" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="BE77" t="n">
         <v>0</v>
@@ -37125,37 +37125,37 @@
         <v>1</v>
       </c>
       <c r="BI77" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BJ77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BK77" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM77" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BN77" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BO77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP77" t="n">
         <v>0</v>
       </c>
       <c r="BQ77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT77" t="n">
         <v>4</v>
@@ -37164,151 +37164,151 @@
         <v>1</v>
       </c>
       <c r="BV77" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW77" t="n">
+        <v>39</v>
+      </c>
+      <c r="BX77" t="n">
+        <v>117</v>
+      </c>
+      <c r="BY77" t="n">
+        <v>89</v>
+      </c>
+      <c r="BZ77" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CA77" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CB77" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR77" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS77" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU77" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV77" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX77" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY77" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ77" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA77" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC77" t="n">
+        <v>63</v>
+      </c>
+      <c r="DD77" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE77" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG77" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH77" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DI77" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ77" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK77" t="n">
         <v>25</v>
       </c>
-      <c r="BW77" t="n">
-        <v>50</v>
-      </c>
-      <c r="BX77" t="n">
-        <v>67</v>
-      </c>
-      <c r="BY77" t="n">
-        <v>69</v>
-      </c>
-      <c r="BZ77" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="CA77" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="CB77" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CC77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR77" t="n">
-        <v>34</v>
-      </c>
-      <c r="CS77" t="n">
-        <v>29</v>
-      </c>
-      <c r="CT77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU77" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV77" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX77" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY77" t="n">
-        <v>5</v>
-      </c>
-      <c r="CZ77" t="n">
-        <v>63</v>
-      </c>
-      <c r="DA77" t="n">
-        <v>88</v>
-      </c>
-      <c r="DB77" t="n">
-        <v>25</v>
-      </c>
-      <c r="DC77" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD77" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DE77" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DF77" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DG77" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DH77" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DI77" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DJ77" t="n">
-        <v>38</v>
-      </c>
-      <c r="DK77" t="n">
-        <v>13</v>
-      </c>
       <c r="DL77" t="n">
-        <v>2.07</v>
+        <v>2.31</v>
       </c>
       <c r="DM77" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="DN77" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="DO77" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP77" t="b">
         <v>1</v>
       </c>
       <c r="DQ77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS77" t="b">
         <v>0</v>
@@ -37320,94 +37320,94 @@
         <v>0</v>
       </c>
       <c r="DV77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW77" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="DX77" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="DY77" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="DZ77" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="EA77" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="EB77" t="inlineStr"/>
       <c r="EC77" t="inlineStr"/>
       <c r="ED77" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EE77" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EF77" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EG77" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EH77" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EI77" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EJ77" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EK77" t="n">
-        <v>20.83</v>
+        <v>20.84</v>
       </c>
       <c r="EL77" t="n">
-        <v>6.52</v>
+        <v>2.97</v>
       </c>
       <c r="EM77" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="EN77" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EO77" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EP77" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
@@ -37427,146 +37427,146 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
         <v>45960.75</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
       </c>
       <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>5</v>
+      </c>
+      <c r="L78" t="n">
+        <v>6</v>
+      </c>
+      <c r="M78" t="n">
+        <v>2</v>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
         <v>3</v>
       </c>
-      <c r="J78" t="n">
-        <v>11</v>
-      </c>
-      <c r="K78" t="n">
+      <c r="R78" t="n">
+        <v>3</v>
+      </c>
+      <c r="S78" t="n">
         <v>4</v>
       </c>
-      <c r="L78" t="n">
-        <v>15</v>
-      </c>
-      <c r="M78" t="n">
-        <v>3</v>
-      </c>
-      <c r="N78" t="n">
-        <v>2</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>6</v>
-      </c>
-      <c r="R78" t="n">
-        <v>1</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
       <c r="T78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U78" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="V78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W78" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X78" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y78" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Z78" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Caixa Futebol Campus</t>
+          <t>Estádio Municipal de Portimão</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>, Seixal</t>
+          <t>Avenida Zeca Afonso Portimão, Portimão</t>
         </is>
       </c>
       <c r="AC78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="AF78" t="n">
         <v>3.3</v>
       </c>
       <c r="AG78" t="n">
-        <v>4.09</v>
+        <v>2.33</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AJ78" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AK78" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AL78" t="n">
-        <v>1.9</v>
+        <v>2.31</v>
       </c>
       <c r="AM78" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AN78" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="AO78" t="n">
-        <v>2.68</v>
+        <v>3.24</v>
       </c>
       <c r="AP78" t="n">
-        <v>2.04</v>
+        <v>2.37</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR78" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AS78" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AT78" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AU78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW78" t="n">
         <v>0</v>
@@ -37581,16 +37581,16 @@
         <v>1</v>
       </c>
       <c r="BA78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB78" t="n">
-        <v>1031</v>
+        <v>4835</v>
       </c>
       <c r="BC78" t="n">
         <v>0</v>
       </c>
       <c r="BD78" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BE78" t="n">
         <v>0</v>
@@ -37605,37 +37605,37 @@
         <v>1</v>
       </c>
       <c r="BI78" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BJ78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM78" t="n">
         <v>5</v>
       </c>
-      <c r="BL78" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM78" t="n">
-        <v>8</v>
-      </c>
       <c r="BN78" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BO78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP78" t="n">
         <v>0</v>
       </c>
       <c r="BQ78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT78" t="n">
         <v>4</v>
@@ -37644,25 +37644,25 @@
         <v>1</v>
       </c>
       <c r="BV78" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="BW78" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="BX78" t="n">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="BY78" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="BZ78" t="n">
-        <v>1.87</v>
+        <v>0.84</v>
       </c>
       <c r="CA78" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="CB78" t="n">
-        <v>2.93</v>
+        <v>2.16</v>
       </c>
       <c r="CC78" t="n">
         <v>0</v>
@@ -37695,7 +37695,7 @@
         <v>0</v>
       </c>
       <c r="CM78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN78" t="n">
         <v>0</v>
@@ -37710,85 +37710,85 @@
         <v>1</v>
       </c>
       <c r="CR78" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="CS78" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU78" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV78" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX78" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY78" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ78" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA78" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB78" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC78" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD78" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DE78" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DF78" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG78" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DH78" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DI78" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ78" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK78" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL78" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DM78" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DN78" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="DO78" t="n">
         <v>16</v>
       </c>
-      <c r="CT78" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU78" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV78" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW78" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX78" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY78" t="n">
-        <v>13</v>
-      </c>
-      <c r="CZ78" t="n">
-        <v>50</v>
-      </c>
-      <c r="DA78" t="n">
-        <v>75</v>
-      </c>
-      <c r="DB78" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC78" t="n">
-        <v>63</v>
-      </c>
-      <c r="DD78" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DE78" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF78" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DG78" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DH78" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="DI78" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ78" t="n">
-        <v>50</v>
-      </c>
-      <c r="DK78" t="n">
-        <v>25</v>
-      </c>
-      <c r="DL78" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="DM78" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="DN78" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="DO78" t="n">
-        <v>17</v>
-      </c>
       <c r="DP78" t="b">
         <v>1</v>
       </c>
       <c r="DQ78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS78" t="b">
         <v>0</v>
@@ -37800,94 +37800,94 @@
         <v>0</v>
       </c>
       <c r="DV78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW78" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="DX78" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="DY78" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="DZ78" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EA78" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="EB78" t="inlineStr"/>
       <c r="EC78" t="inlineStr"/>
       <c r="ED78" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EE78" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EF78" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EG78" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EH78" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EI78" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EJ78" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EK78" t="n">
-        <v>20.84</v>
+        <v>20.83</v>
       </c>
       <c r="EL78" t="n">
-        <v>2.97</v>
+        <v>6.52</v>
       </c>
       <c r="EM78" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="EN78" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="EO78" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EP78" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.66</t>
         </is>
       </c>
     </row>
@@ -38259,7 +38259,7 @@
         <v>2.83</v>
       </c>
       <c r="DO79" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -40271,170 +40271,170 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
         <v>45964.75</v>
       </c>
       <c r="G84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I84" t="n">
+        <v>2</v>
+      </c>
+      <c r="J84" t="n">
+        <v>5</v>
+      </c>
+      <c r="K84" t="n">
         <v>4</v>
       </c>
-      <c r="J84" t="n">
-        <v>4</v>
-      </c>
-      <c r="K84" t="n">
-        <v>7</v>
-      </c>
       <c r="L84" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
         <v>4</v>
       </c>
       <c r="R84" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T84" t="n">
+        <v>9</v>
+      </c>
+      <c r="U84" t="n">
+        <v>11</v>
+      </c>
+      <c r="V84" t="n">
+        <v>16</v>
+      </c>
+      <c r="W84" t="n">
         <v>8</v>
       </c>
-      <c r="U84" t="n">
-        <v>14</v>
-      </c>
-      <c r="V84" t="n">
-        <v>11</v>
-      </c>
-      <c r="W84" t="n">
-        <v>14</v>
-      </c>
       <c r="X84" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y84" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="Z84" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>Estádio da Capital do Móvel</t>
+          <t>Estádio de Ribes</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>Rua do Estádio, Apartado 26, Paços de Ferreira</t>
+          <t>Rua Associação Desportiva Oliveirense 100, Santa Maria de Oliveira</t>
         </is>
       </c>
       <c r="AC84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE84" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AF84" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AG84" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="AH84" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ84" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AK84" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AQ84" t="n">
         <v>1.42</v>
       </c>
-      <c r="AI84" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ84" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AK84" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL84" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM84" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN84" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO84" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AP84" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AQ84" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AR84" t="n">
-        <v>3.16</v>
+        <v>2.55</v>
       </c>
       <c r="AS84" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AT84" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AU84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY84" t="n">
         <v>1</v>
       </c>
       <c r="AZ84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA84" t="n">
         <v>1</v>
       </c>
       <c r="BB84" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="BC84" t="n">
         <v>0</v>
       </c>
       <c r="BD84" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="BE84" t="n">
         <v>0</v>
@@ -40452,73 +40452,73 @@
         <v>0</v>
       </c>
       <c r="BJ84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BK84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BL84" t="n">
         <v>3</v>
       </c>
       <c r="BM84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BN84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BO84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ84" t="n">
         <v>2</v>
       </c>
       <c r="BR84" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT84" t="n">
         <v>3</v>
       </c>
-      <c r="BS84" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT84" t="n">
-        <v>5</v>
-      </c>
       <c r="BU84" t="n">
         <v>1</v>
       </c>
       <c r="BV84" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="BW84" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="BX84" t="n">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="BY84" t="n">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="BZ84" t="n">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
       <c r="CA84" t="n">
-        <v>1.23</v>
+        <v>1.9</v>
       </c>
       <c r="CB84" t="n">
-        <v>2.89</v>
+        <v>3.26</v>
       </c>
       <c r="CC84" t="n">
         <v>0</v>
       </c>
       <c r="CD84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE84" t="n">
         <v>0</v>
       </c>
       <c r="CF84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG84" t="n">
         <v>0</v>
@@ -40554,10 +40554,10 @@
         <v>1</v>
       </c>
       <c r="CR84" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CS84" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="CT84" t="n">
         <v>1</v>
@@ -40566,61 +40566,61 @@
         <v>17</v>
       </c>
       <c r="CV84" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CW84" t="n">
         <v>1</v>
       </c>
       <c r="CX84" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="CY84" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CZ84" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="DA84" t="n">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="DB84" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="DC84" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="DE84" t="n">
-        <v>1</v>
+        <v>2.57</v>
       </c>
       <c r="DF84" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="DG84" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="DH84" t="n">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="DI84" t="n">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="DJ84" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="DK84" t="n">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="DL84" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="DM84" t="n">
-        <v>1.18</v>
+        <v>1.56</v>
       </c>
       <c r="DN84" t="n">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="DO84" t="n">
         <v>16</v>
@@ -40632,10 +40632,10 @@
         <v>1</v>
       </c>
       <c r="DR84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT84" t="b">
         <v>0</v>
@@ -40644,31 +40644,31 @@
         <v>0</v>
       </c>
       <c r="DV84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW84" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="DX84" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="DY84" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="DZ84" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EA84" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EB84" t="inlineStr"/>
@@ -40677,53 +40677,53 @@
       <c r="EE84" t="inlineStr"/>
       <c r="EF84" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EG84" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="EH84" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EI84" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EJ84" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EK84" t="n">
-        <v>17.27</v>
+        <v>11.68</v>
       </c>
       <c r="EL84" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="EM84" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="EN84" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="EO84" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EP84" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.14</t>
         </is>
       </c>
     </row>
@@ -40743,170 +40743,170 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
         <v>45964.75</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K85" t="n">
+        <v>7</v>
+      </c>
+      <c r="L85" t="n">
+        <v>11</v>
+      </c>
+      <c r="M85" t="n">
+        <v>3</v>
+      </c>
+      <c r="N85" t="n">
         <v>4</v>
       </c>
-      <c r="L85" t="n">
-        <v>9</v>
-      </c>
-      <c r="M85" t="n">
-        <v>2</v>
-      </c>
-      <c r="N85" t="n">
-        <v>1</v>
-      </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" t="n">
         <v>4</v>
       </c>
       <c r="R85" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U85" t="n">
+        <v>14</v>
+      </c>
+      <c r="V85" t="n">
         <v>11</v>
       </c>
-      <c r="V85" t="n">
-        <v>16</v>
-      </c>
       <c r="W85" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="X85" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y85" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="Z85" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Estádio de Ribes</t>
+          <t>Estádio da Capital do Móvel</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>Rua Associação Desportiva Oliveirense 100, Santa Maria de Oliveira</t>
+          <t>Rua do Estádio, Apartado 26, Paços de Ferreira</t>
         </is>
       </c>
       <c r="AC85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD85" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE85" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="AF85" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AG85" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AI85" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AP85" t="n">
         <v>2.05</v>
       </c>
-      <c r="AJ85" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AK85" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL85" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM85" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN85" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AO85" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AP85" t="n">
-        <v>2.09</v>
-      </c>
       <c r="AQ85" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AR85" t="n">
-        <v>2.55</v>
+        <v>3.16</v>
       </c>
       <c r="AS85" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="AT85" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AU85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY85" t="n">
         <v>1</v>
       </c>
       <c r="AZ85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA85" t="n">
         <v>1</v>
       </c>
       <c r="BB85" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="BC85" t="n">
         <v>0</v>
       </c>
       <c r="BD85" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="BE85" t="n">
         <v>0</v>
@@ -40924,73 +40924,73 @@
         <v>0</v>
       </c>
       <c r="BJ85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BK85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BL85" t="n">
         <v>3</v>
       </c>
       <c r="BM85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BN85" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BO85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ85" t="n">
         <v>2</v>
       </c>
       <c r="BR85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BT85" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU85" t="n">
         <v>1</v>
       </c>
       <c r="BV85" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="BW85" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="BX85" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="BY85" t="n">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="BZ85" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="CA85" t="n">
-        <v>1.9</v>
+        <v>1.23</v>
       </c>
       <c r="CB85" t="n">
-        <v>3.26</v>
+        <v>2.89</v>
       </c>
       <c r="CC85" t="n">
         <v>0</v>
       </c>
       <c r="CD85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE85" t="n">
         <v>0</v>
       </c>
       <c r="CF85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG85" t="n">
         <v>0</v>
@@ -41026,10 +41026,10 @@
         <v>1</v>
       </c>
       <c r="CR85" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="CS85" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="CT85" t="n">
         <v>1</v>
@@ -41038,64 +41038,64 @@
         <v>17</v>
       </c>
       <c r="CV85" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW85" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX85" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY85" t="n">
         <v>8</v>
       </c>
-      <c r="CW85" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX85" t="n">
+      <c r="CZ85" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA85" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB85" t="n">
         <v>13</v>
       </c>
-      <c r="CY85" t="n">
-        <v>7</v>
-      </c>
-      <c r="CZ85" t="n">
-        <v>20</v>
-      </c>
-      <c r="DA85" t="n">
-        <v>43</v>
-      </c>
-      <c r="DB85" t="n">
-        <v>0</v>
-      </c>
       <c r="DC85" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="DE85" t="n">
-        <v>2.57</v>
+        <v>1</v>
       </c>
       <c r="DF85" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="DG85" t="n">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="DH85" t="n">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="DI85" t="n">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="DJ85" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="DK85" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="DL85" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="DM85" t="n">
-        <v>1.56</v>
+        <v>1.18</v>
       </c>
       <c r="DN85" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="DO85" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41104,10 +41104,10 @@
         <v>1</v>
       </c>
       <c r="DR85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT85" t="b">
         <v>0</v>
@@ -41116,31 +41116,31 @@
         <v>0</v>
       </c>
       <c r="DV85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW85" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="DX85" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="DY85" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="DZ85" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EA85" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="EB85" t="inlineStr"/>
@@ -41149,53 +41149,53 @@
       <c r="EE85" t="inlineStr"/>
       <c r="EF85" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EG85" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>4.15</t>
         </is>
       </c>
       <c r="EH85" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EI85" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EJ85" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EK85" t="n">
-        <v>11.68</v>
+        <v>17.27</v>
       </c>
       <c r="EL85" t="n">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="EM85" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="EN85" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="EO85" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EP85" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.29</t>
         </is>
       </c>
     </row>
@@ -42543,7 +42543,7 @@
         <v>3.15</v>
       </c>
       <c r="DO88" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -44091,52 +44091,52 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
         <v>45969.75</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K92" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L92" t="n">
         <v>17</v>
       </c>
       <c r="M92" t="n">
+        <v>3</v>
+      </c>
+      <c r="N92" t="n">
+        <v>6</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
         <v>5</v>
       </c>
-      <c r="N92" t="n">
-        <v>3</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>3</v>
-      </c>
       <c r="R92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S92" t="n">
         <v>11</v>
@@ -44145,92 +44145,92 @@
         <v>6</v>
       </c>
       <c r="U92" t="n">
+        <v>16</v>
+      </c>
+      <c r="V92" t="n">
+        <v>11</v>
+      </c>
+      <c r="W92" t="n">
         <v>14</v>
       </c>
-      <c r="V92" t="n">
-        <v>9</v>
-      </c>
-      <c r="W92" t="n">
-        <v>16</v>
-      </c>
       <c r="X92" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Y92" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="Z92" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>Estádio Municipal Eng. Manuel Branco Teixeira</t>
+          <t>Caixa Futebol Campus</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>Avenida do Estádio Municipal, Chaves</t>
+          <t>, Seixal</t>
         </is>
       </c>
       <c r="AC92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AD92" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AJ92" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ92" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR92" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AS92" t="n">
         <v>3</v>
       </c>
-      <c r="AE92" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF92" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AG92" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AH92" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI92" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AJ92" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AK92" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL92" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM92" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN92" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO92" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AP92" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ92" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR92" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AS92" t="n">
-        <v>2.73</v>
-      </c>
       <c r="AT92" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AU92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW92" t="n">
         <v>1</v>
@@ -44239,22 +44239,22 @@
         <v>0</v>
       </c>
       <c r="AY92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB92" t="n">
-        <v>1037</v>
+        <v>4841</v>
       </c>
       <c r="BC92" t="n">
         <v>0</v>
       </c>
       <c r="BD92" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="BE92" t="n">
         <v>0</v>
@@ -44272,175 +44272,175 @@
         <v>6</v>
       </c>
       <c r="BJ92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK92" t="n">
         <v>3</v>
       </c>
-      <c r="BK92" t="n">
-        <v>5</v>
-      </c>
       <c r="BL92" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM92" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN92" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR92" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS92" t="n">
         <v>3</v>
       </c>
-      <c r="BM92" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN92" t="n">
+      <c r="BT92" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV92" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW92" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX92" t="n">
+        <v>111</v>
+      </c>
+      <c r="BY92" t="n">
+        <v>81</v>
+      </c>
+      <c r="BZ92" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CA92" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CB92" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="CC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR92" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS92" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU92" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV92" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX92" t="n">
         <v>8</v>
       </c>
-      <c r="BO92" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ92" t="n">
-        <v>4</v>
-      </c>
-      <c r="BR92" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS92" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT92" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU92" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV92" t="n">
-        <v>61</v>
-      </c>
-      <c r="BW92" t="n">
-        <v>31</v>
-      </c>
-      <c r="BX92" t="n">
-        <v>77</v>
-      </c>
-      <c r="BY92" t="n">
-        <v>58</v>
-      </c>
-      <c r="BZ92" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CA92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CB92" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="CC92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN92" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR92" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS92" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU92" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV92" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX92" t="n">
-        <v>3</v>
-      </c>
       <c r="CY92" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ92" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA92" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB92" t="n">
         <v>10</v>
       </c>
-      <c r="CZ92" t="n">
-        <v>25</v>
-      </c>
-      <c r="DA92" t="n">
-        <v>75</v>
-      </c>
-      <c r="DB92" t="n">
-        <v>38</v>
-      </c>
       <c r="DC92" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="DD92" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="DE92" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DF92" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DG92" t="n">
-        <v>0.25</v>
+        <v>1.2</v>
       </c>
       <c r="DH92" t="n">
-        <v>1.44</v>
+        <v>1</v>
       </c>
       <c r="DI92" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="DJ92" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="DK92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="DL92" t="n">
-        <v>1.62</v>
+        <v>2.22</v>
       </c>
       <c r="DM92" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="DN92" t="n">
-        <v>3.05</v>
+        <v>3.69</v>
       </c>
       <c r="DO92" t="n">
         <v>16</v>
@@ -44449,10 +44449,10 @@
         <v>1</v>
       </c>
       <c r="DQ92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS92" t="b">
         <v>0</v>
@@ -44464,94 +44464,86 @@
         <v>0</v>
       </c>
       <c r="DV92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW92" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="DX92" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="DY92" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="DZ92" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EA92" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="EB92" t="inlineStr"/>
       <c r="EC92" t="inlineStr"/>
-      <c r="ED92" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EE92" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
+      <c r="ED92" t="inlineStr"/>
+      <c r="EE92" t="inlineStr"/>
       <c r="EF92" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EG92" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EH92" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="EI92" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EJ92" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EK92" t="n">
-        <v>15.18</v>
+        <v>18.59</v>
       </c>
       <c r="EL92" t="n">
-        <v>3.98</v>
+        <v>3.85</v>
       </c>
       <c r="EM92" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="EN92" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="EO92" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EP92" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.77</t>
         </is>
       </c>
     </row>
@@ -44571,41 +44563,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
         <v>45969.75</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K93" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L93" t="n">
         <v>17</v>
       </c>
       <c r="M93" t="n">
+        <v>5</v>
+      </c>
+      <c r="N93" t="n">
         <v>3</v>
       </c>
-      <c r="N93" t="n">
-        <v>6</v>
-      </c>
       <c r="O93" t="n">
         <v>0</v>
       </c>
@@ -44613,10 +44605,10 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S93" t="n">
         <v>11</v>
@@ -44625,92 +44617,92 @@
         <v>6</v>
       </c>
       <c r="U93" t="n">
+        <v>14</v>
+      </c>
+      <c r="V93" t="n">
+        <v>9</v>
+      </c>
+      <c r="W93" t="n">
         <v>16</v>
       </c>
-      <c r="V93" t="n">
-        <v>11</v>
-      </c>
-      <c r="W93" t="n">
-        <v>14</v>
-      </c>
       <c r="X93" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Y93" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="Z93" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Caixa Futebol Campus</t>
+          <t>Estádio Municipal Eng. Manuel Branco Teixeira</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>, Seixal</t>
+          <t>Avenida do Estádio Municipal, Chaves</t>
         </is>
       </c>
       <c r="AC93" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD93" t="n">
         <v>3</v>
       </c>
-      <c r="AD93" t="n">
-        <v>6</v>
-      </c>
       <c r="AE93" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR93" t="n">
         <v>2.6</v>
       </c>
-      <c r="AF93" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AG93" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH93" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI93" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AJ93" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AK93" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL93" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AM93" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN93" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AO93" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AP93" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AQ93" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR93" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AS93" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AT93" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AU93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW93" t="n">
         <v>1</v>
@@ -44719,22 +44711,22 @@
         <v>0</v>
       </c>
       <c r="AY93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB93" t="n">
-        <v>4841</v>
+        <v>1037</v>
       </c>
       <c r="BC93" t="n">
         <v>0</v>
       </c>
       <c r="BD93" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="BE93" t="n">
         <v>0</v>
@@ -44752,175 +44744,175 @@
         <v>6</v>
       </c>
       <c r="BJ93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK93" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL93" t="n">
         <v>3</v>
       </c>
-      <c r="BL93" t="n">
-        <v>6</v>
-      </c>
       <c r="BM93" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN93" t="n">
         <v>8</v>
       </c>
-      <c r="BN93" t="n">
-        <v>9</v>
-      </c>
       <c r="BO93" t="n">
         <v>1</v>
       </c>
       <c r="BP93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BS93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT93" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV93" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW93" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX93" t="n">
+        <v>77</v>
+      </c>
+      <c r="BY93" t="n">
+        <v>58</v>
+      </c>
+      <c r="BZ93" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CA93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB93" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="CC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN93" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR93" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS93" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU93" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV93" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX93" t="n">
         <v>3</v>
       </c>
-      <c r="BT93" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU93" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV93" t="n">
-        <v>80</v>
-      </c>
-      <c r="BW93" t="n">
-        <v>50</v>
-      </c>
-      <c r="BX93" t="n">
-        <v>111</v>
-      </c>
-      <c r="BY93" t="n">
-        <v>81</v>
-      </c>
-      <c r="BZ93" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CA93" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CB93" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="CC93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR93" t="n">
-        <v>28</v>
-      </c>
-      <c r="CS93" t="n">
-        <v>12</v>
-      </c>
-      <c r="CT93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU93" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV93" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX93" t="n">
-        <v>8</v>
-      </c>
       <c r="CY93" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CZ93" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="DA93" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="DB93" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="DC93" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DE93" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF93" t="n">
         <v>1.5</v>
       </c>
-      <c r="DF93" t="n">
-        <v>1</v>
-      </c>
       <c r="DG93" t="n">
-        <v>1.2</v>
+        <v>0.25</v>
       </c>
       <c r="DH93" t="n">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="DI93" t="n">
-        <v>1.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DJ93" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="DK93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="DL93" t="n">
-        <v>2.22</v>
+        <v>1.62</v>
       </c>
       <c r="DM93" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="DN93" t="n">
-        <v>3.69</v>
+        <v>3.05</v>
       </c>
       <c r="DO93" t="n">
         <v>16</v>
@@ -44929,10 +44921,10 @@
         <v>1</v>
       </c>
       <c r="DQ93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS93" t="b">
         <v>0</v>
@@ -44944,86 +44936,94 @@
         <v>0</v>
       </c>
       <c r="DV93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW93" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="DX93" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="DY93" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="DZ93" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="EA93" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EB93" t="inlineStr"/>
       <c r="EC93" t="inlineStr"/>
-      <c r="ED93" t="inlineStr"/>
-      <c r="EE93" t="inlineStr"/>
+      <c r="ED93" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EE93" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
       <c r="EF93" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EG93" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="EH93" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EI93" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EJ93" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EK93" t="n">
-        <v>18.59</v>
+        <v>15.18</v>
       </c>
       <c r="EL93" t="n">
-        <v>3.85</v>
+        <v>3.98</v>
       </c>
       <c r="EM93" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EN93" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="EO93" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EP93" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -45395,7 +45395,7 @@
         <v>2.92</v>
       </c>
       <c r="DO94" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP94" t="b">
         <v>1</v>
@@ -47879,44 +47879,44 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
         <v>45984.45833333334</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
+        <v>8</v>
+      </c>
+      <c r="K100" t="n">
         <v>3</v>
       </c>
-      <c r="K100" t="n">
-        <v>1</v>
-      </c>
       <c r="L100" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -47925,101 +47925,101 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R100" t="n">
         <v>3</v>
       </c>
       <c r="S100" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U100" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V100" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W100" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="X100" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Y100" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="Z100" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Estádio Municipal Eng. Manuel Branco Teixeira</t>
+          <t>Estádio Dr. Jorge Sampaio</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>Avenida do Estádio Municipal, Chaves</t>
+          <t>Rua da Paradela, Pedroso, Vila Nova de Gaia</t>
         </is>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE100" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AF100" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ100" t="n">
         <v>3.2</v>
       </c>
-      <c r="AG100" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH100" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI100" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ100" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AK100" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AL100" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AM100" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AN100" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AO100" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AR100" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="AS100" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AU100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV100" t="n">
         <v>0</v>
@@ -48028,25 +48028,25 @@
         <v>0</v>
       </c>
       <c r="AX100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY100" t="n">
         <v>0</v>
       </c>
       <c r="AZ100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA100" t="n">
         <v>0</v>
       </c>
       <c r="BB100" t="n">
-        <v>-1</v>
+        <v>1037</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
@@ -48058,187 +48058,187 @@
         <v>2</v>
       </c>
       <c r="BH100" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI100" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK100" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM100" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN100" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS100" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT100" t="n">
         <v>3</v>
       </c>
-      <c r="BL100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM100" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN100" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS100" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT100" t="n">
-        <v>0</v>
-      </c>
       <c r="BU100" t="n">
         <v>1</v>
       </c>
       <c r="BV100" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW100" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX100" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY100" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ100" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CA100" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CB100" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CC100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM100" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP100" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR100" t="n">
+        <v>9</v>
+      </c>
+      <c r="CS100" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU100" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV100" t="n">
+        <v>23</v>
+      </c>
+      <c r="CW100" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX100" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY100" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ100" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA100" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB100" t="n">
         <v>55</v>
       </c>
-      <c r="BW100" t="n">
-        <v>47</v>
-      </c>
-      <c r="BX100" t="n">
-        <v>81</v>
-      </c>
-      <c r="BY100" t="n">
-        <v>83</v>
-      </c>
-      <c r="BZ100" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="CA100" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="CB100" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CC100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM100" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO100" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CP100" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CQ100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR100" t="n">
-        <v>16</v>
-      </c>
-      <c r="CS100" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU100" t="n">
-        <v>12</v>
-      </c>
-      <c r="CV100" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW100" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX100" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY100" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ100" t="n">
-        <v>20</v>
-      </c>
-      <c r="DA100" t="n">
-        <v>60</v>
-      </c>
-      <c r="DB100" t="n">
-        <v>20</v>
-      </c>
       <c r="DC100" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="DD100" t="n">
         <v>1.25</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="DF100" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DG100" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH100" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DI100" t="n">
         <v>1.2</v>
       </c>
-      <c r="DG100" t="n">
-        <v>2</v>
-      </c>
-      <c r="DH100" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="DI100" t="n">
-        <v>2.2</v>
-      </c>
       <c r="DJ100" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="DK100" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="DL100" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.47</v>
+        <v>1.2</v>
       </c>
       <c r="DN100" t="n">
-        <v>3.07</v>
+        <v>2.36</v>
       </c>
       <c r="DO100" t="n">
         <v>16</v>
       </c>
       <c r="DP100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ100" t="b">
         <v>0</v>
@@ -48260,75 +48260,75 @@
       </c>
       <c r="DW100" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="DX100" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="DZ100" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EA100" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EB100" t="inlineStr"/>
       <c r="EC100" t="inlineStr"/>
       <c r="ED100" t="inlineStr">
         <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EE100" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EF100" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EG100" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EH100" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EI100" t="inlineStr">
+        <is>
           <t>1.76</t>
         </is>
       </c>
-      <c r="EE100" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EF100" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EG100" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EH100" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EI100" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
       <c r="EJ100" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EK100" t="n">
-        <v>18.1</v>
+        <v>15.5</v>
       </c>
       <c r="EL100" t="n">
-        <v>9.57</v>
+        <v>1.59</v>
       </c>
       <c r="EM100" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="EN100" t="inlineStr">
@@ -48338,12 +48338,12 @@
       </c>
       <c r="EO100" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EP100" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.86</t>
         </is>
       </c>
     </row>
@@ -48359,44 +48359,44 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
         <v>45984.45833333334</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K101" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L101" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -48405,101 +48405,101 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>3</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T101" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U101" t="n">
+        <v>9</v>
+      </c>
+      <c r="V101" t="n">
+        <v>10</v>
+      </c>
+      <c r="W101" t="n">
+        <v>12</v>
+      </c>
+      <c r="X101" t="n">
         <v>11</v>
       </c>
-      <c r="V101" t="n">
-        <v>11</v>
-      </c>
-      <c r="W101" t="n">
-        <v>23</v>
-      </c>
-      <c r="X101" t="n">
-        <v>15</v>
-      </c>
       <c r="Y101" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="Z101" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>Estádio Dr. Jorge Sampaio</t>
+          <t>Estádio Municipal Eng. Manuel Branco Teixeira</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>Rua da Paradela, Pedroso, Vila Nova de Gaia</t>
+          <t>Avenida do Estádio Municipal, Chaves</t>
         </is>
       </c>
       <c r="AC101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG101" t="n">
         <v>3</v>
       </c>
-      <c r="AE101" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF101" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AG101" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AH101" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI101" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL101" t="n">
         <v>1.85</v>
       </c>
-      <c r="AJ101" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AK101" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL101" t="n">
-        <v>2</v>
-      </c>
       <c r="AM101" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AN101" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AO101" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AR101" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="AS101" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AT101" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV101" t="n">
         <v>0</v>
@@ -48508,25 +48508,25 @@
         <v>0</v>
       </c>
       <c r="AX101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY101" t="n">
         <v>0</v>
       </c>
       <c r="AZ101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA101" t="n">
         <v>0</v>
       </c>
       <c r="BB101" t="n">
-        <v>1037</v>
+        <v>-1</v>
       </c>
       <c r="BC101" t="n">
         <v>0</v>
       </c>
       <c r="BD101" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BE101" t="n">
         <v>0</v>
@@ -48538,67 +48538,67 @@
         <v>2</v>
       </c>
       <c r="BH101" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BI101" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BJ101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM101" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BN101" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BO101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU101" t="n">
         <v>1</v>
       </c>
       <c r="BV101" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BW101" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="BX101" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="BY101" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="BZ101" t="n">
-        <v>1.28</v>
+        <v>0.97</v>
       </c>
       <c r="CA101" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="CB101" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="CC101" t="n">
         <v>0</v>
@@ -48631,94 +48631,94 @@
         <v>0</v>
       </c>
       <c r="CM101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN101" t="n">
         <v>1</v>
       </c>
       <c r="CO101" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP101" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CQ101" t="n">
         <v>1</v>
       </c>
       <c r="CR101" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="CS101" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CT101" t="n">
         <v>1</v>
       </c>
       <c r="CU101" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CV101" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="CW101" t="n">
         <v>1</v>
       </c>
       <c r="CX101" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CY101" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ101" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="DA101" t="n">
+        <v>60</v>
+      </c>
+      <c r="DB101" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC101" t="n">
         <v>80</v>
-      </c>
-      <c r="DB101" t="n">
-        <v>55</v>
-      </c>
-      <c r="DC101" t="n">
-        <v>90</v>
       </c>
       <c r="DD101" t="n">
         <v>1.25</v>
       </c>
       <c r="DE101" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="DF101" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="DG101" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DH101" t="n">
-        <v>0.8</v>
+        <v>1.45</v>
       </c>
       <c r="DI101" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="DJ101" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="DK101" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="DL101" t="n">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="DM101" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="DN101" t="n">
-        <v>2.36</v>
+        <v>3.07</v>
       </c>
       <c r="DO101" t="n">
         <v>16</v>
       </c>
       <c r="DP101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ101" t="b">
         <v>0</v>
@@ -48740,75 +48740,75 @@
       </c>
       <c r="DW101" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="DX101" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="DY101" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="DZ101" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EA101" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EB101" t="inlineStr"/>
       <c r="EC101" t="inlineStr"/>
       <c r="ED101" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EE101" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EF101" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EG101" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EH101" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EI101" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EJ101" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EK101" t="n">
-        <v>15.5</v>
+        <v>18.1</v>
       </c>
       <c r="EL101" t="n">
-        <v>1.59</v>
+        <v>9.57</v>
       </c>
       <c r="EM101" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="EN101" t="inlineStr">
@@ -48818,12 +48818,12 @@
       </c>
       <c r="EO101" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EP101" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -55023,12 +55023,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
@@ -55038,25 +55038,25 @@
         <v>2</v>
       </c>
       <c r="H115" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L115" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M115" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -55065,128 +55065,128 @@
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S115" t="n">
         <v>17</v>
       </c>
       <c r="T115" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="U115" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V115" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="W115" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="X115" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y115" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="Z115" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>Estádio do Mar</t>
+          <t>Caixa Futebol Campus</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>Lugar da Cruz de Pau, Matosinhos</t>
+          <t>, Seixal</t>
         </is>
       </c>
       <c r="AC115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG115" t="n">
         <v>5</v>
       </c>
-      <c r="AD115" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE115" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF115" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG115" t="n">
-        <v>3</v>
-      </c>
       <c r="AH115" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AI115" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AJ115" t="n">
-        <v>3.74</v>
+        <v>3.1</v>
       </c>
       <c r="AK115" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AL115" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AN115" t="n">
-        <v>1.91</v>
+        <v>1.52</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.63</v>
+        <v>3.17</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AR115" t="n">
-        <v>3.23</v>
+        <v>2.55</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AU115" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV115" t="n">
         <v>1</v>
       </c>
       <c r="AW115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX115" t="n">
         <v>1</v>
       </c>
       <c r="AY115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB115" t="n">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="BC115" t="n">
         <v>0</v>
       </c>
       <c r="BD115" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="BE115" t="n">
         <v>0</v>
@@ -55201,76 +55201,76 @@
         <v>1</v>
       </c>
       <c r="BI115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BJ115" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BK115" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BL115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM115" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BN115" t="n">
         <v>6</v>
       </c>
       <c r="BO115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BP115" t="n">
         <v>1</v>
       </c>
       <c r="BQ115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS115" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BT115" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BU115" t="n">
         <v>1</v>
       </c>
       <c r="BV115" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="BW115" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="BX115" t="n">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="BY115" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="BZ115" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="CA115" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="CB115" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="CC115" t="n">
         <v>0</v>
       </c>
       <c r="CD115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE115" t="n">
         <v>0</v>
       </c>
       <c r="CF115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG115" t="n">
         <v>0</v>
@@ -55294,7 +55294,7 @@
         <v>1</v>
       </c>
       <c r="CN115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO115" t="n">
         <v>0</v>
@@ -55306,73 +55306,73 @@
         <v>1</v>
       </c>
       <c r="CR115" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS115" t="n">
         <v>20</v>
       </c>
-      <c r="CS115" t="n">
-        <v>21</v>
-      </c>
       <c r="CT115" t="n">
         <v>1</v>
       </c>
       <c r="CU115" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CV115" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CW115" t="n">
         <v>1</v>
       </c>
       <c r="CX115" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CY115" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CZ115" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="DA115" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="DB115" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="DC115" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="DD115" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="DE115" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DF115" t="n">
-        <v>1.29</v>
+        <v>0.83</v>
       </c>
       <c r="DG115" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="DH115" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DI115" t="n">
-        <v>0.92</v>
+        <v>1.25</v>
       </c>
       <c r="DJ115" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="DK115" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="DL115" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="DM115" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="DN115" t="n">
-        <v>2.81</v>
+        <v>3.4</v>
       </c>
       <c r="DO115" t="n">
         <v>16</v>
@@ -55384,83 +55384,91 @@
         <v>1</v>
       </c>
       <c r="DR115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV115" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW115" t="inlineStr"/>
-      <c r="DX115" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DW115" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="DX115" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
       <c r="DY115" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="DZ115" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="EA115" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="EB115" t="inlineStr"/>
       <c r="EC115" t="inlineStr"/>
       <c r="ED115" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EE115" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EF115" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EG115" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="EH115" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="EI115" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EJ115" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EK115" t="n">
-        <v>15.66</v>
+        <v>18.3</v>
       </c>
       <c r="EL115" t="n">
-        <v>8.699999999999999</v>
+        <v>3.67</v>
       </c>
       <c r="EM115" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="EN115" t="inlineStr">
@@ -55468,8 +55476,16 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="EO115" t="inlineStr"/>
-      <c r="EP115" t="inlineStr"/>
+      <c r="EO115" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EP115" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -55487,12 +55503,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
@@ -55502,25 +55518,25 @@
         <v>2</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J116" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K116" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M116" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -55529,128 +55545,128 @@
         <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S116" t="n">
         <v>17</v>
       </c>
       <c r="T116" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U116" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V116" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W116" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y116" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="Z116" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>Caixa Futebol Campus</t>
+          <t>Estádio do Mar</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>, Seixal</t>
+          <t>Lugar da Cruz de Pau, Matosinhos</t>
         </is>
       </c>
       <c r="AC116" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.63</v>
+        <v>2.04</v>
       </c>
       <c r="AF116" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AG116" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AI116" t="n">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AJ116" t="n">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="AK116" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AL116" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AM116" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AN116" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AO116" t="n">
-        <v>3.17</v>
+        <v>2.63</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AR116" t="n">
-        <v>2.55</v>
+        <v>3.23</v>
       </c>
       <c r="AS116" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="AT116" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AU116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV116" t="n">
         <v>1</v>
       </c>
       <c r="AW116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX116" t="n">
         <v>1</v>
       </c>
       <c r="AY116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB116" t="n">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
       </c>
       <c r="BD116" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="BE116" t="n">
         <v>0</v>
@@ -55665,76 +55681,76 @@
         <v>1</v>
       </c>
       <c r="BI116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BJ116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BK116" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BL116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM116" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="BN116" t="n">
         <v>6</v>
       </c>
       <c r="BO116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BP116" t="n">
         <v>1</v>
       </c>
       <c r="BQ116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS116" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BT116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BU116" t="n">
         <v>1</v>
       </c>
       <c r="BV116" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="BW116" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="BX116" t="n">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="BY116" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="BZ116" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="CA116" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="CB116" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CC116" t="n">
         <v>0</v>
       </c>
       <c r="CD116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE116" t="n">
         <v>0</v>
       </c>
       <c r="CF116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG116" t="n">
         <v>0</v>
@@ -55758,7 +55774,7 @@
         <v>1</v>
       </c>
       <c r="CN116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO116" t="n">
         <v>0</v>
@@ -55770,73 +55786,73 @@
         <v>1</v>
       </c>
       <c r="CR116" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="CS116" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CT116" t="n">
         <v>1</v>
       </c>
       <c r="CU116" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="CV116" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CW116" t="n">
         <v>1</v>
       </c>
       <c r="CX116" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CY116" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CZ116" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="DA116" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="DB116" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="DC116" t="n">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="DD116" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DE116" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DF116" t="n">
-        <v>0.83</v>
+        <v>1.29</v>
       </c>
       <c r="DG116" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="DH116" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI116" t="n">
         <v>0.92</v>
       </c>
-      <c r="DI116" t="n">
-        <v>1.25</v>
-      </c>
       <c r="DJ116" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="DK116" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="DL116" t="n">
-        <v>2.18</v>
+        <v>1.47</v>
       </c>
       <c r="DM116" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="DN116" t="n">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="DO116" t="n">
         <v>16</v>
@@ -55848,91 +55864,83 @@
         <v>1</v>
       </c>
       <c r="DR116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV116" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW116" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="DX116" t="inlineStr">
-        <is>
-          <t>3.08</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="DW116" t="inlineStr"/>
+      <c r="DX116" t="inlineStr"/>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
         <is>
-          <t>5.72</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="EA116" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="EB116" t="inlineStr"/>
       <c r="EC116" t="inlineStr"/>
       <c r="ED116" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EE116" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF116" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EG116" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="EH116" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EI116" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EJ116" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EK116" t="n">
-        <v>18.3</v>
+        <v>15.66</v>
       </c>
       <c r="EL116" t="n">
-        <v>3.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="EM116" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="EN116" t="inlineStr">
@@ -55940,16 +55948,8 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="EO116" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EP116" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
+      <c r="EO116" t="inlineStr"/>
+      <c r="EP116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -60223,31 +60223,31 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F126" s="2" t="n">
         <v>46005.45833333334</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J126" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L126" t="n">
         <v>9</v>
@@ -60256,137 +60256,137 @@
         <v>4</v>
       </c>
       <c r="N126" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P126" t="n">
         <v>1</v>
       </c>
       <c r="Q126" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R126" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S126" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T126" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U126" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V126" t="n">
         <v>10</v>
       </c>
       <c r="W126" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X126" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y126" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="Z126" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>CGD Stadium Aurélio Pereira</t>
+          <t>Estádio Municipal de Portimão</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>, Alcochete</t>
+          <t>Avenida Zeca Afonso Portimão, Portimão</t>
         </is>
       </c>
       <c r="AC126" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD126" t="n">
         <v>4</v>
       </c>
-      <c r="AD126" t="n">
-        <v>8</v>
-      </c>
       <c r="AE126" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="AF126" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AG126" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AH126" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AI126" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AJ126" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AK126" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL126" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AM126" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AN126" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AO126" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AR126" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="AS126" t="n">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="AT126" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AU126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX126" t="n">
         <v>0</v>
       </c>
       <c r="AY126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA126" t="n">
         <v>1</v>
       </c>
       <c r="BB126" t="n">
-        <v>4841</v>
+        <v>1030</v>
       </c>
       <c r="BC126" t="n">
         <v>0</v>
       </c>
       <c r="BD126" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="BE126" t="n">
         <v>0</v>
@@ -60407,10 +60407,10 @@
         <v>1</v>
       </c>
       <c r="BK126" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BM126" t="n">
         <v>5</v>
@@ -60419,160 +60419,160 @@
         <v>4</v>
       </c>
       <c r="BO126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BP126" t="n">
         <v>2</v>
       </c>
       <c r="BQ126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT126" t="n">
         <v>4</v>
       </c>
-      <c r="BR126" t="n">
-        <v>5</v>
-      </c>
-      <c r="BS126" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT126" t="n">
+      <c r="BU126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>32</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>58</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU126" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV126" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX126" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY126" t="n">
         <v>9</v>
       </c>
-      <c r="BU126" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV126" t="n">
-        <v>80</v>
-      </c>
-      <c r="BW126" t="n">
-        <v>40</v>
-      </c>
-      <c r="BX126" t="n">
-        <v>85</v>
-      </c>
-      <c r="BY126" t="n">
-        <v>68</v>
-      </c>
-      <c r="BZ126" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CA126" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CB126" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="CC126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR126" t="n">
-        <v>26</v>
-      </c>
-      <c r="CS126" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU126" t="n">
-        <v>10</v>
-      </c>
-      <c r="CV126" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX126" t="n">
+      <c r="CZ126" t="n">
+        <v>31</v>
+      </c>
+      <c r="DA126" t="n">
+        <v>93</v>
+      </c>
+      <c r="DB126" t="n">
         <v>7</v>
       </c>
-      <c r="CY126" t="n">
-        <v>10</v>
-      </c>
-      <c r="CZ126" t="n">
-        <v>48</v>
-      </c>
-      <c r="DA126" t="n">
-        <v>77</v>
-      </c>
-      <c r="DB126" t="n">
-        <v>32</v>
-      </c>
       <c r="DC126" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="DD126" t="n">
-        <v>1.88</v>
+        <v>0.75</v>
       </c>
       <c r="DE126" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DF126" t="n">
-        <v>2.5</v>
+        <v>0.86</v>
       </c>
       <c r="DG126" t="n">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="DH126" t="n">
-        <v>2.23</v>
+        <v>0.92</v>
       </c>
       <c r="DI126" t="n">
-        <v>1.54</v>
+        <v>0.93</v>
       </c>
       <c r="DJ126" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="DK126" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="DL126" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="DM126" t="n">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="DN126" t="n">
-        <v>3.42</v>
+        <v>2.96</v>
       </c>
       <c r="DO126" t="n">
         <v>16</v>
@@ -60581,10 +60581,10 @@
         <v>1</v>
       </c>
       <c r="DQ126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS126" t="b">
         <v>0</v>
@@ -60596,31 +60596,31 @@
         <v>0</v>
       </c>
       <c r="DV126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW126" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DX126" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="DY126" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="DZ126" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EA126" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="EB126" t="inlineStr"/>
@@ -60629,53 +60629,53 @@
       <c r="EE126" t="inlineStr"/>
       <c r="EF126" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EG126" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EH126" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EI126" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EJ126" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EK126" t="n">
-        <v>14.47</v>
+        <v>16.58</v>
       </c>
       <c r="EL126" t="n">
-        <v>7.14</v>
+        <v>4.73</v>
       </c>
       <c r="EM126" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="EN126" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="EO126" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EP126" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.98</t>
         </is>
       </c>
     </row>
@@ -60695,31 +60695,31 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F127" s="2" t="n">
         <v>46005.45833333334</v>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K127" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L127" t="n">
         <v>9</v>
@@ -60728,137 +60728,137 @@
         <v>4</v>
       </c>
       <c r="N127" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P127" t="n">
         <v>1</v>
       </c>
       <c r="Q127" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R127" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S127" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T127" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U127" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V127" t="n">
         <v>10</v>
       </c>
       <c r="W127" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="X127" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y127" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Z127" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>Estádio Municipal de Portimão</t>
+          <t>CGD Stadium Aurélio Pereira</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>Avenida Zeca Afonso Portimão, Portimão</t>
+          <t>, Alcochete</t>
         </is>
       </c>
       <c r="AC127" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD127" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE127" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="AF127" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AG127" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO127" t="n">
         <v>2.6</v>
       </c>
-      <c r="AH127" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI127" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ127" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK127" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL127" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM127" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN127" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO127" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AP127" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR127" t="n">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="AS127" t="n">
-        <v>2.66</v>
+        <v>2.91</v>
       </c>
       <c r="AT127" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AU127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX127" t="n">
         <v>0</v>
       </c>
       <c r="AY127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA127" t="n">
         <v>1</v>
       </c>
       <c r="BB127" t="n">
-        <v>1030</v>
+        <v>4841</v>
       </c>
       <c r="BC127" t="n">
         <v>0</v>
       </c>
       <c r="BD127" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="BE127" t="n">
         <v>0</v>
@@ -60879,10 +60879,10 @@
         <v>1</v>
       </c>
       <c r="BK127" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL127" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BM127" t="n">
         <v>5</v>
@@ -60891,160 +60891,160 @@
         <v>4</v>
       </c>
       <c r="BO127" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BP127" t="n">
         <v>2</v>
       </c>
       <c r="BQ127" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR127" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BS127" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BT127" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BU127" t="n">
         <v>1</v>
       </c>
       <c r="BV127" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>68</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU127" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV127" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX127" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY127" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ127" t="n">
+        <v>48</v>
+      </c>
+      <c r="DA127" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB127" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC127" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD127" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DE127" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF127" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DG127" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DH127" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DI127" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DJ127" t="n">
         <v>52</v>
       </c>
-      <c r="BW127" t="n">
-        <v>32</v>
-      </c>
-      <c r="BX127" t="n">
-        <v>91</v>
-      </c>
-      <c r="BY127" t="n">
-        <v>58</v>
-      </c>
-      <c r="BZ127" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CA127" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CB127" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="CC127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI127" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ127" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM127" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ127" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR127" t="n">
-        <v>27</v>
-      </c>
-      <c r="CS127" t="n">
-        <v>29</v>
-      </c>
-      <c r="CT127" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU127" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV127" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW127" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX127" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY127" t="n">
-        <v>9</v>
-      </c>
-      <c r="CZ127" t="n">
-        <v>31</v>
-      </c>
-      <c r="DA127" t="n">
-        <v>93</v>
-      </c>
-      <c r="DB127" t="n">
-        <v>7</v>
-      </c>
-      <c r="DC127" t="n">
-        <v>61</v>
-      </c>
-      <c r="DD127" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DE127" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF127" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="DG127" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DH127" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DI127" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="DJ127" t="n">
-        <v>69</v>
-      </c>
       <c r="DK127" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="DL127" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="DM127" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="DN127" t="n">
-        <v>2.96</v>
+        <v>3.42</v>
       </c>
       <c r="DO127" t="n">
         <v>16</v>
@@ -61053,10 +61053,10 @@
         <v>1</v>
       </c>
       <c r="DQ127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS127" t="b">
         <v>0</v>
@@ -61068,31 +61068,31 @@
         <v>0</v>
       </c>
       <c r="DV127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW127" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="DX127" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="DY127" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="DZ127" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EA127" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EB127" t="inlineStr"/>
@@ -61101,53 +61101,53 @@
       <c r="EE127" t="inlineStr"/>
       <c r="EF127" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EG127" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="EH127" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EI127" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EJ127" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EK127" t="n">
-        <v>16.58</v>
+        <v>14.47</v>
       </c>
       <c r="EL127" t="n">
-        <v>4.73</v>
+        <v>7.14</v>
       </c>
       <c r="EM127" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="EN127" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="EO127" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EP127" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.06</t>
         </is>
       </c>
     </row>
@@ -61519,7 +61519,7 @@
         <v>2.79</v>
       </c>
       <c r="DO128" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP128" t="b">
         <v>1</v>
@@ -67691,7 +67691,7 @@
         <v>2.84</v>
       </c>
       <c r="DO141" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP141" t="b">
         <v>1</v>
@@ -67825,22 +67825,22 @@
         <v>1</v>
       </c>
       <c r="Q142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R142" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S142" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T142" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U142" t="n">
+        <v>19</v>
+      </c>
+      <c r="V142" t="n">
         <v>17</v>
-      </c>
-      <c r="V142" t="n">
-        <v>15</v>
       </c>
       <c r="W142" t="n">
         <v>16</v>
@@ -67849,10 +67849,10 @@
         <v>11</v>
       </c>
       <c r="Y142" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Z142" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
@@ -68012,13 +68012,13 @@
         <v>70</v>
       </c>
       <c r="BZ142" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="CA142" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="CB142" t="n">
-        <v>3.62</v>
+        <v>3.86</v>
       </c>
       <c r="CC142" t="n">
         <v>0</v>
@@ -68075,19 +68075,19 @@
         <v>1</v>
       </c>
       <c r="CU142" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV142" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="CW142" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX142" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CY142" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="CZ142" t="n">
         <v>27</v>
@@ -68305,22 +68305,22 @@
         <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R143" t="n">
         <v>3</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T143" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U143" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V143" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W143" t="n">
         <v>13</v>
@@ -68329,10 +68329,10 @@
         <v>5</v>
       </c>
       <c r="Y143" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z143" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
@@ -68492,13 +68492,13 @@
         <v>63</v>
       </c>
       <c r="BZ143" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="CA143" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="CB143" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CC143" t="n">
         <v>0</v>
@@ -68555,19 +68555,19 @@
         <v>1</v>
       </c>
       <c r="CU143" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CV143" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CW143" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX143" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CY143" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CZ143" t="n">
         <v>26</v>
@@ -68772,19 +68772,19 @@
         <v>7</v>
       </c>
       <c r="R144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S144" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="T144" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U144" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="V144" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W144" t="n">
         <v>18</v>
@@ -68793,10 +68793,10 @@
         <v>9</v>
       </c>
       <c r="Y144" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z144" t="n">
         <v>48</v>
-      </c>
-      <c r="Z144" t="n">
-        <v>52</v>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
@@ -68956,13 +68956,13 @@
         <v>80</v>
       </c>
       <c r="BZ144" t="n">
-        <v>2.55</v>
+        <v>2.79</v>
       </c>
       <c r="CA144" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CB144" t="n">
-        <v>3.9</v>
+        <v>4.14</v>
       </c>
       <c r="CC144" t="n">
         <v>0</v>
@@ -69022,16 +69022,16 @@
         <v>9</v>
       </c>
       <c r="CV144" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CW144" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX144" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CY144" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="CZ144" t="n">
         <v>50</v>
@@ -69195,12 +69195,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F145" s="2" t="n">
@@ -69216,43 +69216,43 @@
         <v>3</v>
       </c>
       <c r="J145" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" t="n">
+        <v>6</v>
+      </c>
+      <c r="L145" t="n">
+        <v>7</v>
+      </c>
+      <c r="M145" t="n">
+        <v>5</v>
+      </c>
+      <c r="N145" t="n">
+        <v>2</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>1</v>
+      </c>
+      <c r="R145" t="n">
+        <v>4</v>
+      </c>
+      <c r="S145" t="n">
+        <v>4</v>
+      </c>
+      <c r="T145" t="n">
         <v>9</v>
       </c>
-      <c r="K145" t="n">
-        <v>4</v>
-      </c>
-      <c r="L145" t="n">
+      <c r="U145" t="n">
+        <v>5</v>
+      </c>
+      <c r="V145" t="n">
         <v>13</v>
-      </c>
-      <c r="M145" t="n">
-        <v>0</v>
-      </c>
-      <c r="N145" t="n">
-        <v>1</v>
-      </c>
-      <c r="O145" t="n">
-        <v>0</v>
-      </c>
-      <c r="P145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>7</v>
-      </c>
-      <c r="R145" t="n">
-        <v>5</v>
-      </c>
-      <c r="S145" t="n">
-        <v>5</v>
-      </c>
-      <c r="T145" t="n">
-        <v>7</v>
-      </c>
-      <c r="U145" t="n">
-        <v>12</v>
-      </c>
-      <c r="V145" t="n">
-        <v>12</v>
       </c>
       <c r="W145" t="n">
         <v>19</v>
@@ -69261,74 +69261,74 @@
         <v>14</v>
       </c>
       <c r="Y145" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Z145" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Estádio Municipal 25 de Abril</t>
+          <t>CGD Stadium Aurélio Pereira</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>Rua Futebol Clube de Penafiel, Penafiel</t>
+          <t>, Alcochete</t>
         </is>
       </c>
       <c r="AC145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE145" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AF145" t="n">
         <v>3</v>
       </c>
       <c r="AG145" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH145" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AI145" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AJ145" t="n">
-        <v>3.87</v>
+        <v>3.58</v>
       </c>
       <c r="AK145" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL145" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AM145" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AN145" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AO145" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AP145" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AR145" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AS145" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="AT145" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AU145" t="n">
         <v>3</v>
@@ -69352,203 +69352,203 @@
         <v>2</v>
       </c>
       <c r="BB145" t="n">
-        <v>173</v>
+        <v>1032</v>
       </c>
       <c r="BC145" t="n">
         <v>0</v>
       </c>
       <c r="BD145" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT145" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV145" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW145" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX145" t="n">
+        <v>102</v>
+      </c>
+      <c r="BY145" t="n">
+        <v>113</v>
+      </c>
+      <c r="BZ145" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CA145" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CB145" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR145" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS145" t="n">
         <v>27</v>
       </c>
-      <c r="BE145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF145" t="n">
-        <v>2099</v>
-      </c>
-      <c r="BG145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK145" t="n">
+      <c r="CT145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU145" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV145" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX145" t="n">
         <v>7</v>
       </c>
-      <c r="BL145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM145" t="n">
+      <c r="CY145" t="n">
         <v>4</v>
       </c>
-      <c r="BN145" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV145" t="n">
-        <v>76</v>
-      </c>
-      <c r="BW145" t="n">
-        <v>53</v>
-      </c>
-      <c r="BX145" t="n">
-        <v>98</v>
-      </c>
-      <c r="BY145" t="n">
-        <v>83</v>
-      </c>
-      <c r="BZ145" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CA145" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CB145" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="CC145" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE145" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI145" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ145" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN145" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ145" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR145" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS145" t="n">
-        <v>17</v>
-      </c>
-      <c r="CT145" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU145" t="n">
+      <c r="CZ145" t="n">
+        <v>66</v>
+      </c>
+      <c r="DA145" t="n">
+        <v>66</v>
+      </c>
+      <c r="DB145" t="n">
+        <v>41</v>
+      </c>
+      <c r="DC145" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD145" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DE145" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DF145" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DG145" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH145" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DI145" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DJ145" t="n">
+        <v>34</v>
+      </c>
+      <c r="DK145" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL145" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DM145" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DN145" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="DO145" t="n">
         <v>16</v>
       </c>
-      <c r="CV145" t="n">
-        <v>21</v>
-      </c>
-      <c r="CW145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CX145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CY145" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CZ145" t="n">
-        <v>26</v>
-      </c>
-      <c r="DA145" t="n">
-        <v>60</v>
-      </c>
-      <c r="DB145" t="n">
-        <v>20</v>
-      </c>
-      <c r="DC145" t="n">
-        <v>53</v>
-      </c>
-      <c r="DD145" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DE145" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF145" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DG145" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DH145" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="DI145" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ145" t="n">
-        <v>75</v>
-      </c>
-      <c r="DK145" t="n">
-        <v>41</v>
-      </c>
-      <c r="DL145" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="DM145" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="DN145" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="DO145" t="n">
-        <v>17</v>
-      </c>
       <c r="DP145" t="b">
         <v>1</v>
       </c>
@@ -69572,82 +69572,90 @@
       </c>
       <c r="DW145" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="DX145" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="DY145" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="DZ145" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="EA145" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="EB145" t="inlineStr"/>
       <c r="EC145" t="inlineStr"/>
-      <c r="ED145" t="inlineStr"/>
-      <c r="EE145" t="inlineStr"/>
+      <c r="ED145" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EE145" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
       <c r="EF145" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EG145" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="EH145" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EI145" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EJ145" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EK145" t="n">
-        <v>10.13</v>
+        <v>12.38</v>
       </c>
       <c r="EL145" t="n">
-        <v>4.72</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="EM145" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="EN145" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EO145" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EP145" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.31</t>
         </is>
       </c>
     </row>
@@ -69667,12 +69675,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F146" s="2" t="n">
@@ -69688,43 +69696,43 @@
         <v>3</v>
       </c>
       <c r="J146" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K146" t="n">
+        <v>4</v>
+      </c>
+      <c r="L146" t="n">
+        <v>13</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>8</v>
+      </c>
+      <c r="R146" t="n">
         <v>6</v>
       </c>
-      <c r="L146" t="n">
+      <c r="S146" t="n">
         <v>7</v>
       </c>
-      <c r="M146" t="n">
-        <v>5</v>
-      </c>
-      <c r="N146" t="n">
-        <v>2</v>
-      </c>
-      <c r="O146" t="n">
-        <v>0</v>
-      </c>
-      <c r="P146" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>1</v>
-      </c>
-      <c r="R146" t="n">
-        <v>3</v>
-      </c>
-      <c r="S146" t="n">
-        <v>4</v>
-      </c>
       <c r="T146" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U146" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="V146" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="W146" t="n">
         <v>19</v>
@@ -69733,74 +69741,74 @@
         <v>14</v>
       </c>
       <c r="Y146" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="Z146" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>CGD Stadium Aurélio Pereira</t>
+          <t>Estádio Municipal 25 de Abril</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>, Alcochete</t>
+          <t>Rua Futebol Clube de Penafiel, Penafiel</t>
         </is>
       </c>
       <c r="AC146" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE146" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="AF146" t="n">
         <v>3</v>
       </c>
       <c r="AG146" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="AH146" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AT146" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AI146" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ146" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AK146" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL146" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM146" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN146" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AO146" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AP146" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AQ146" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR146" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AS146" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT146" t="n">
-        <v>1.32</v>
       </c>
       <c r="AU146" t="n">
         <v>3</v>
@@ -69824,19 +69832,19 @@
         <v>2</v>
       </c>
       <c r="BB146" t="n">
-        <v>1032</v>
+        <v>173</v>
       </c>
       <c r="BC146" t="n">
         <v>0</v>
       </c>
       <c r="BD146" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BE146" t="n">
         <v>0</v>
       </c>
       <c r="BF146" t="n">
-        <v>-1</v>
+        <v>2099</v>
       </c>
       <c r="BG146" t="n">
         <v>2</v>
@@ -69845,181 +69853,181 @@
         <v>1</v>
       </c>
       <c r="BI146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK146" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BL146" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM146" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN146" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU146" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV146" t="n">
+        <v>76</v>
+      </c>
+      <c r="BW146" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX146" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY146" t="n">
+        <v>83</v>
+      </c>
+      <c r="BZ146" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CA146" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CB146" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="CC146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP146" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR146" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS146" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU146" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV146" t="n">
+        <v>21</v>
+      </c>
+      <c r="CW146" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX146" t="n">
         <v>5</v>
       </c>
-      <c r="BM146" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN146" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO146" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP146" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ146" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR146" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS146" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT146" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU146" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV146" t="n">
-        <v>39</v>
-      </c>
-      <c r="BW146" t="n">
-        <v>55</v>
-      </c>
-      <c r="BX146" t="n">
-        <v>102</v>
-      </c>
-      <c r="BY146" t="n">
-        <v>113</v>
-      </c>
-      <c r="BZ146" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="CA146" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="CB146" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CC146" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD146" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE146" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF146" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG146" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH146" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI146" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ146" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK146" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL146" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM146" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN146" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO146" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP146" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ146" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR146" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS146" t="n">
-        <v>27</v>
-      </c>
-      <c r="CT146" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU146" t="n">
-        <v>16</v>
-      </c>
-      <c r="CV146" t="n">
-        <v>19</v>
-      </c>
-      <c r="CW146" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CX146" t="n">
-        <v>-1</v>
-      </c>
       <c r="CY146" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CZ146" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="DA146" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="DB146" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC146" t="n">
+        <v>53</v>
+      </c>
+      <c r="DD146" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DE146" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF146" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG146" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH146" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DI146" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ146" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK146" t="n">
         <v>41</v>
       </c>
-      <c r="DC146" t="n">
-        <v>75</v>
-      </c>
-      <c r="DD146" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DE146" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DF146" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DG146" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DH146" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="DI146" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="DJ146" t="n">
-        <v>34</v>
-      </c>
-      <c r="DK146" t="n">
-        <v>34</v>
-      </c>
       <c r="DL146" t="n">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="DM146" t="n">
-        <v>1.56</v>
+        <v>0.96</v>
       </c>
       <c r="DN146" t="n">
-        <v>3.46</v>
+        <v>2.44</v>
       </c>
       <c r="DO146" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -70044,82 +70052,90 @@
       </c>
       <c r="DW146" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="DX146" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="DY146" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="DZ146" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="EA146" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="EB146" t="inlineStr"/>
       <c r="EC146" t="inlineStr"/>
-      <c r="ED146" t="inlineStr"/>
-      <c r="EE146" t="inlineStr"/>
+      <c r="ED146" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EE146" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
       <c r="EF146" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EG146" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="EH146" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EI146" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EJ146" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EK146" t="n">
-        <v>12.38</v>
+        <v>10.13</v>
       </c>
       <c r="EL146" t="n">
-        <v>9.359999999999999</v>
+        <v>4.72</v>
       </c>
       <c r="EM146" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="EN146" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="EO146" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EP146" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>3.15</t>
         </is>
       </c>
     </row>
@@ -70181,22 +70197,22 @@
         <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R147" t="n">
         <v>4</v>
       </c>
       <c r="S147" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T147" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U147" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="V147" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W147" t="n">
         <v>17</v>
@@ -70368,13 +70384,13 @@
         <v>63</v>
       </c>
       <c r="BZ147" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="CA147" t="n">
-        <v>0.9</v>
+        <v>1.21</v>
       </c>
       <c r="CB147" t="n">
-        <v>1.93</v>
+        <v>2.75</v>
       </c>
       <c r="CC147" t="n">
         <v>1</v>
@@ -70437,13 +70453,13 @@
         <v>18</v>
       </c>
       <c r="CW147" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX147" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CY147" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CZ147" t="n">
         <v>47</v>
@@ -70518,48 +70534,56 @@
       <c r="DX147" t="inlineStr"/>
       <c r="DY147" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="DZ147" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="EA147" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="EB147" t="inlineStr"/>
       <c r="EC147" t="inlineStr"/>
       <c r="ED147" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EE147" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EF147" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG147" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EH147" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EI147" t="inlineStr"/>
-      <c r="EJ147" t="inlineStr"/>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EI147" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EJ147" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
       <c r="EK147" t="n">
         <v>9.119999999999999</v>
       </c>
@@ -70640,19 +70664,19 @@
         <v>7</v>
       </c>
       <c r="R148" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S148" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T148" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U148" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V148" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W148" t="n">
         <v>12</v>
@@ -70661,10 +70685,10 @@
         <v>11</v>
       </c>
       <c r="Y148" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="Z148" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="AA148" t="inlineStr"/>
       <c r="AB148" t="inlineStr"/>
@@ -70816,13 +70840,13 @@
         <v>88</v>
       </c>
       <c r="BZ148" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="CA148" t="n">
         <v>1.21</v>
       </c>
       <c r="CB148" t="n">
-        <v>3.01</v>
+        <v>3.13</v>
       </c>
       <c r="CC148" t="n">
         <v>0</v>
@@ -70870,7 +70894,7 @@
         <v>1</v>
       </c>
       <c r="CR148" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CS148" t="n">
         <v>20</v>
@@ -70879,19 +70903,19 @@
         <v>1</v>
       </c>
       <c r="CU148" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV148" t="n">
         <v>14</v>
       </c>
       <c r="CW148" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX148" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CY148" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CZ148" t="n">
         <v>41</v>
@@ -70964,56 +70988,72 @@
       </c>
       <c r="DW148" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="DX148" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="DY148" t="inlineStr">
         <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="DZ148" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="EA148" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="EB148" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EC148" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="ED148" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EE148" t="inlineStr">
+        <is>
           <t>1.89</t>
         </is>
       </c>
-      <c r="DZ148" t="inlineStr">
-        <is>
-          <t>4.05</t>
-        </is>
-      </c>
-      <c r="EA148" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
-      <c r="EB148" t="inlineStr"/>
-      <c r="EC148" t="inlineStr"/>
-      <c r="ED148" t="inlineStr"/>
-      <c r="EE148" t="inlineStr"/>
       <c r="EF148" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EG148" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="EH148" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EI148" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EJ148" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EK148" t="n">
@@ -71039,7 +71079,479 @@
       </c>
       <c r="EP148" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>LigaPro_Portugal_2a_división_2025-2026</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>17</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Lusitania Lourosa</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Leixões</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>46030.84375</v>
+      </c>
+      <c r="G149" t="n">
+        <v>2</v>
+      </c>
+      <c r="H149" t="n">
+        <v>2</v>
+      </c>
+      <c r="I149" t="n">
+        <v>4</v>
+      </c>
+      <c r="J149" t="n">
+        <v>6</v>
+      </c>
+      <c r="K149" t="n">
+        <v>9</v>
+      </c>
+      <c r="L149" t="n">
+        <v>15</v>
+      </c>
+      <c r="M149" t="n">
+        <v>2</v>
+      </c>
+      <c r="N149" t="n">
+        <v>4</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>3</v>
+      </c>
+      <c r="R149" t="n">
+        <v>3</v>
+      </c>
+      <c r="S149" t="n">
+        <v>5</v>
+      </c>
+      <c r="T149" t="n">
+        <v>9</v>
+      </c>
+      <c r="U149" t="n">
+        <v>8</v>
+      </c>
+      <c r="V149" t="n">
+        <v>12</v>
+      </c>
+      <c r="W149" t="n">
+        <v>19</v>
+      </c>
+      <c r="X149" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>Estádio do Lusitânia FC</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>, Lourosa</t>
+        </is>
+      </c>
+      <c r="AC149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>66</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>8</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ149" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR149" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT149" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU149" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV149" t="n">
+        <v>79</v>
+      </c>
+      <c r="BW149" t="n">
+        <v>77</v>
+      </c>
+      <c r="BX149" t="n">
+        <v>122</v>
+      </c>
+      <c r="BY149" t="n">
+        <v>132</v>
+      </c>
+      <c r="BZ149" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CA149" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CB149" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CC149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP149" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR149" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS149" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU149" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV149" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW149" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX149" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY149" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ149" t="n">
+        <v>41</v>
+      </c>
+      <c r="DA149" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB149" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC149" t="n">
+        <v>66</v>
+      </c>
+      <c r="DD149" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE149" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF149" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG149" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH149" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DI149" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ149" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK149" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL149" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DM149" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DN149" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="DO149" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT149" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU149" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV149" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW149" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="DX149" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="DY149" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DZ149" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="EA149" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EB149" t="inlineStr"/>
+      <c r="EC149" t="inlineStr"/>
+      <c r="ED149" t="inlineStr"/>
+      <c r="EE149" t="inlineStr"/>
+      <c r="EF149" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EG149" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="EH149" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EI149" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EJ149" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EK149" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="EL149" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="EM149" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="EN149" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="EO149" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EP149" t="inlineStr">
+        <is>
+          <t>2.98</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -71613,22 +71613,22 @@
         <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R150" t="n">
         <v>5</v>
       </c>
       <c r="S150" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T150" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U150" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V150" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="W150" t="n">
         <v>15</v>
@@ -71637,10 +71637,10 @@
         <v>21</v>
       </c>
       <c r="Y150" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z150" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
@@ -71800,13 +71800,13 @@
         <v>103</v>
       </c>
       <c r="BZ150" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="CA150" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="CB150" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="CC150" t="n">
         <v>0</v>
@@ -71851,31 +71851,31 @@
         <v>0</v>
       </c>
       <c r="CQ150" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR150" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="CS150" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="CT150" t="n">
         <v>1</v>
       </c>
       <c r="CU150" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CV150" t="n">
         <v>16</v>
       </c>
       <c r="CW150" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX150" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CY150" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CZ150" t="n">
         <v>41</v>
@@ -72581,22 +72581,22 @@
         <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R152" t="n">
         <v>2</v>
       </c>
       <c r="S152" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T152" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U152" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V152" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="W152" t="n">
         <v>11</v>
@@ -72605,10 +72605,10 @@
         <v>17</v>
       </c>
       <c r="Y152" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="Z152" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
@@ -72768,13 +72768,13 @@
         <v>73</v>
       </c>
       <c r="BZ152" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="CA152" t="n">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="CB152" t="n">
-        <v>2.68</v>
+        <v>3.06</v>
       </c>
       <c r="CC152" t="n">
         <v>0</v>
@@ -72819,31 +72819,31 @@
         <v>0</v>
       </c>
       <c r="CQ152" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR152" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="CS152" t="n">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="CT152" t="n">
         <v>1</v>
       </c>
       <c r="CU152" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CV152" t="n">
         <v>11</v>
       </c>
       <c r="CW152" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX152" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CY152" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CZ152" t="n">
         <v>32</v>
@@ -73072,19 +73072,19 @@
         <v>5</v>
       </c>
       <c r="R153" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S153" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T153" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U153" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V153" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="W153" t="n">
         <v>12</v>
@@ -73093,10 +73093,10 @@
         <v>17</v>
       </c>
       <c r="Y153" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="Z153" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
@@ -73256,13 +73256,13 @@
         <v>73</v>
       </c>
       <c r="BZ153" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="CA153" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="CB153" t="n">
-        <v>3.12</v>
+        <v>3.62</v>
       </c>
       <c r="CC153" t="n">
         <v>1</v>
@@ -73307,31 +73307,31 @@
         <v>0</v>
       </c>
       <c r="CQ153" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CR153" t="n">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="CS153" t="n">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="CT153" t="n">
         <v>1</v>
       </c>
       <c r="CU153" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CV153" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CW153" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX153" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY153" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CZ153" t="n">
         <v>38</v>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP163" headerRowCount="1">
-  <autoFilter ref="A1:EP163"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP164" headerRowCount="1">
+  <autoFilter ref="A1:EP164"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP163"/>
+  <dimension ref="A1:EP164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE2" t="n">
         <v>1.44</v>
@@ -5133,7 +5133,7 @@
         <v>1.5</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="DP14" t="b">
         <v>0</v>
@@ -11370,7 +11370,7 @@
         <v>100</v>
       </c>
       <c r="DD22" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE22" t="n">
         <v>1.3</v>
@@ -11861,7 +11861,7 @@
         <v>1.25</v>
       </c>
       <c r="DE23" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF23" t="n">
         <v>0</v>
@@ -22749,7 +22749,7 @@
         <v>1.33</v>
       </c>
       <c r="DE46" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF46" t="n">
         <v>2</v>
@@ -26498,7 +26498,7 @@
         <v>75</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE54" t="n">
         <v>0.89</v>
@@ -26957,7 +26957,7 @@
         <v>1.67</v>
       </c>
       <c r="DE55" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF55" t="n">
         <v>1.33</v>
@@ -34418,7 +34418,7 @@
         <v>84</v>
       </c>
       <c r="DD71" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE71" t="n">
         <v>1.67</v>
@@ -38701,7 +38701,7 @@
         <v>1</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF80" t="n">
         <v>1.5</v>
@@ -41062,7 +41062,7 @@
         <v>63</v>
       </c>
       <c r="DD85" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE85" t="n">
         <v>1.22</v>
@@ -45837,7 +45837,7 @@
         <v>1.6</v>
       </c>
       <c r="DE95" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF95" t="n">
         <v>2.25</v>
@@ -47879,44 +47879,44 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
         <v>45984.45833333334</v>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -47925,101 +47925,101 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>3</v>
       </c>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U100" t="n">
+        <v>9</v>
+      </c>
+      <c r="V100" t="n">
+        <v>10</v>
+      </c>
+      <c r="W100" t="n">
+        <v>12</v>
+      </c>
+      <c r="X100" t="n">
         <v>11</v>
       </c>
-      <c r="V100" t="n">
-        <v>11</v>
-      </c>
-      <c r="W100" t="n">
-        <v>23</v>
-      </c>
-      <c r="X100" t="n">
-        <v>15</v>
-      </c>
       <c r="Y100" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="Z100" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Estádio Dr. Jorge Sampaio</t>
+          <t>Estádio Municipal Eng. Manuel Branco Teixeira</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>Rua da Paradela, Pedroso, Vila Nova de Gaia</t>
+          <t>Avenida do Estádio Municipal, Chaves</t>
         </is>
       </c>
       <c r="AC100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG100" t="n">
         <v>3</v>
       </c>
-      <c r="AE100" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF100" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AG100" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AH100" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI100" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL100" t="n">
         <v>1.85</v>
       </c>
-      <c r="AJ100" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AK100" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AL100" t="n">
-        <v>2</v>
-      </c>
       <c r="AM100" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AN100" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AO100" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AR100" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="AS100" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV100" t="n">
         <v>0</v>
@@ -48028,25 +48028,25 @@
         <v>0</v>
       </c>
       <c r="AX100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY100" t="n">
         <v>0</v>
       </c>
       <c r="AZ100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA100" t="n">
         <v>0</v>
       </c>
       <c r="BB100" t="n">
-        <v>1037</v>
+        <v>-1</v>
       </c>
       <c r="BC100" t="n">
         <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BE100" t="n">
         <v>0</v>
@@ -48058,67 +48058,67 @@
         <v>2</v>
       </c>
       <c r="BH100" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BI100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BJ100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM100" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BN100" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BO100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BU100" t="n">
         <v>1</v>
       </c>
       <c r="BV100" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BW100" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="BX100" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="BY100" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="BZ100" t="n">
-        <v>1.28</v>
+        <v>0.97</v>
       </c>
       <c r="CA100" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="CB100" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="CC100" t="n">
         <v>0</v>
@@ -48151,94 +48151,94 @@
         <v>0</v>
       </c>
       <c r="CM100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN100" t="n">
         <v>1</v>
       </c>
       <c r="CO100" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP100" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CQ100" t="n">
         <v>1</v>
       </c>
       <c r="CR100" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="CS100" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="CT100" t="n">
         <v>1</v>
       </c>
       <c r="CU100" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CV100" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="CW100" t="n">
         <v>1</v>
       </c>
       <c r="CX100" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="CY100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ100" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="DA100" t="n">
+        <v>60</v>
+      </c>
+      <c r="DB100" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC100" t="n">
         <v>80</v>
       </c>
-      <c r="DB100" t="n">
-        <v>55</v>
-      </c>
-      <c r="DC100" t="n">
-        <v>90</v>
-      </c>
       <c r="DD100" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="DE100" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="DF100" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="DG100" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DH100" t="n">
-        <v>0.8</v>
+        <v>1.45</v>
       </c>
       <c r="DI100" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="DJ100" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="DK100" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="DL100" t="n">
-        <v>1.16</v>
+        <v>1.6</v>
       </c>
       <c r="DM100" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="DN100" t="n">
-        <v>2.36</v>
+        <v>3.07</v>
       </c>
       <c r="DO100" t="n">
         <v>18</v>
       </c>
       <c r="DP100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ100" t="b">
         <v>0</v>
@@ -48260,75 +48260,75 @@
       </c>
       <c r="DW100" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="DX100" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="DY100" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="DZ100" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EA100" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EB100" t="inlineStr"/>
       <c r="EC100" t="inlineStr"/>
       <c r="ED100" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EE100" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EF100" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EG100" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EH100" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EI100" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EJ100" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EK100" t="n">
-        <v>15.5</v>
+        <v>18.1</v>
       </c>
       <c r="EL100" t="n">
-        <v>1.59</v>
+        <v>9.57</v>
       </c>
       <c r="EM100" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="EN100" t="inlineStr">
@@ -48338,12 +48338,12 @@
       </c>
       <c r="EO100" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EP100" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.04</t>
         </is>
       </c>
     </row>
@@ -48359,44 +48359,44 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
         <v>45984.45833333334</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
+        <v>8</v>
+      </c>
+      <c r="K101" t="n">
         <v>3</v>
       </c>
-      <c r="K101" t="n">
-        <v>1</v>
-      </c>
       <c r="L101" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -48405,101 +48405,101 @@
         <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R101" t="n">
         <v>3</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T101" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U101" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V101" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W101" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="X101" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Y101" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="Z101" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>Estádio Municipal Eng. Manuel Branco Teixeira</t>
+          <t>Estádio Dr. Jorge Sampaio</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>Avenida do Estádio Municipal, Chaves</t>
+          <t>Rua da Paradela, Pedroso, Vila Nova de Gaia</t>
         </is>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE101" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AF101" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ101" t="n">
         <v>3.2</v>
       </c>
-      <c r="AG101" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH101" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI101" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ101" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AK101" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AL101" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AM101" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AN101" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AO101" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AR101" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="AS101" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AT101" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AU101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV101" t="n">
         <v>0</v>
@@ -48508,25 +48508,25 @@
         <v>0</v>
       </c>
       <c r="AX101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY101" t="n">
         <v>0</v>
       </c>
       <c r="AZ101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA101" t="n">
         <v>0</v>
       </c>
       <c r="BB101" t="n">
-        <v>-1</v>
+        <v>1037</v>
       </c>
       <c r="BC101" t="n">
         <v>0</v>
       </c>
       <c r="BD101" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BE101" t="n">
         <v>0</v>
@@ -48538,187 +48538,187 @@
         <v>2</v>
       </c>
       <c r="BH101" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK101" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM101" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN101" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS101" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT101" t="n">
         <v>3</v>
       </c>
-      <c r="BL101" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM101" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN101" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO101" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP101" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ101" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR101" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS101" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT101" t="n">
-        <v>0</v>
-      </c>
       <c r="BU101" t="n">
         <v>1</v>
       </c>
       <c r="BV101" t="n">
+        <v>32</v>
+      </c>
+      <c r="BW101" t="n">
+        <v>34</v>
+      </c>
+      <c r="BX101" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY101" t="n">
+        <v>75</v>
+      </c>
+      <c r="BZ101" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CA101" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CB101" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM101" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP101" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR101" t="n">
+        <v>9</v>
+      </c>
+      <c r="CS101" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU101" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV101" t="n">
+        <v>23</v>
+      </c>
+      <c r="CW101" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX101" t="n">
+        <v>14</v>
+      </c>
+      <c r="CY101" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ101" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA101" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB101" t="n">
         <v>55</v>
       </c>
-      <c r="BW101" t="n">
-        <v>47</v>
-      </c>
-      <c r="BX101" t="n">
-        <v>81</v>
-      </c>
-      <c r="BY101" t="n">
-        <v>83</v>
-      </c>
-      <c r="BZ101" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="CA101" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="CB101" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CC101" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD101" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE101" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF101" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG101" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH101" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI101" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ101" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK101" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL101" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM101" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN101" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO101" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CP101" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CQ101" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR101" t="n">
-        <v>16</v>
-      </c>
-      <c r="CS101" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT101" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU101" t="n">
-        <v>12</v>
-      </c>
-      <c r="CV101" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW101" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX101" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY101" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ101" t="n">
+      <c r="DC101" t="n">
+        <v>90</v>
+      </c>
+      <c r="DD101" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DE101" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DF101" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DG101" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH101" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DI101" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DJ101" t="n">
+        <v>30</v>
+      </c>
+      <c r="DK101" t="n">
         <v>20</v>
       </c>
-      <c r="DA101" t="n">
-        <v>60</v>
-      </c>
-      <c r="DB101" t="n">
-        <v>20</v>
-      </c>
-      <c r="DC101" t="n">
-        <v>80</v>
-      </c>
-      <c r="DD101" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="DE101" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="DF101" t="n">
+      <c r="DL101" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="DM101" t="n">
         <v>1.2</v>
       </c>
-      <c r="DG101" t="n">
-        <v>2</v>
-      </c>
-      <c r="DH101" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="DI101" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DJ101" t="n">
-        <v>80</v>
-      </c>
-      <c r="DK101" t="n">
-        <v>40</v>
-      </c>
-      <c r="DL101" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DM101" t="n">
-        <v>1.47</v>
-      </c>
       <c r="DN101" t="n">
-        <v>3.07</v>
+        <v>2.36</v>
       </c>
       <c r="DO101" t="n">
         <v>18</v>
       </c>
       <c r="DP101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DQ101" t="b">
         <v>0</v>
@@ -48740,75 +48740,75 @@
       </c>
       <c r="DW101" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="DX101" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="DY101" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="DZ101" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EA101" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EB101" t="inlineStr"/>
       <c r="EC101" t="inlineStr"/>
       <c r="ED101" t="inlineStr">
         <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EE101" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EF101" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EG101" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="EH101" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EI101" t="inlineStr">
+        <is>
           <t>1.76</t>
         </is>
       </c>
-      <c r="EE101" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EF101" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EG101" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="EH101" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EI101" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
       <c r="EJ101" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EK101" t="n">
-        <v>18.1</v>
+        <v>15.5</v>
       </c>
       <c r="EL101" t="n">
-        <v>9.57</v>
+        <v>1.59</v>
       </c>
       <c r="EM101" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="EN101" t="inlineStr">
@@ -48818,12 +48818,12 @@
       </c>
       <c r="EO101" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EP101" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.86</t>
         </is>
       </c>
     </row>
@@ -50263,170 +50263,170 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
         <v>45991.45833333334</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
         <v>2</v>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J105" t="n">
+        <v>2</v>
+      </c>
+      <c r="K105" t="n">
+        <v>2</v>
+      </c>
+      <c r="L105" t="n">
         <v>4</v>
       </c>
-      <c r="K105" t="n">
-        <v>6</v>
-      </c>
-      <c r="L105" t="n">
-        <v>10</v>
-      </c>
       <c r="M105" t="n">
         <v>1</v>
       </c>
       <c r="N105" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R105" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S105" t="n">
         <v>4</v>
       </c>
       <c r="T105" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V105" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="W105" t="n">
+        <v>14</v>
+      </c>
+      <c r="X105" t="n">
         <v>11</v>
       </c>
-      <c r="X105" t="n">
-        <v>17</v>
-      </c>
       <c r="Y105" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="Z105" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Campo Manuel Marques</t>
+          <t>Estádio Dr. Jorge Sampaio</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>Rua Cândido dos Reis, Torres Vedras</t>
+          <t>Rua da Paradela, Pedroso, Vila Nova de Gaia</t>
         </is>
       </c>
       <c r="AC105" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AD105" t="n">
         <v>6</v>
       </c>
       <c r="AE105" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="AF105" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AG105" t="n">
-        <v>2.98</v>
+        <v>2.67</v>
       </c>
       <c r="AH105" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AI105" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AJ105" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AK105" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AL105" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AM105" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AN105" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AO105" t="n">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="AP105" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AR105" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AS105" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AT105" t="n">
         <v>1.33</v>
       </c>
       <c r="AU105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV105" t="n">
         <v>0</v>
       </c>
       <c r="AW105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB105" t="n">
-        <v>165</v>
+        <v>4894</v>
       </c>
       <c r="BC105" t="n">
         <v>0</v>
       </c>
       <c r="BD105" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="BE105" t="n">
         <v>0</v>
@@ -50441,178 +50441,178 @@
         <v>1</v>
       </c>
       <c r="BI105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ105" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BK105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR105" t="n">
+        <v>5</v>
+      </c>
+      <c r="BS105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT105" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV105" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW105" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX105" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY105" t="n">
+        <v>101</v>
+      </c>
+      <c r="BZ105" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="CA105" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CB105" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR105" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS105" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU105" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV105" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX105" t="n">
         <v>6</v>
-      </c>
-      <c r="BN105" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO105" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP105" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ105" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR105" t="n">
-        <v>4</v>
-      </c>
-      <c r="BS105" t="n">
-        <v>5</v>
-      </c>
-      <c r="BT105" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU105" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV105" t="n">
-        <v>41</v>
-      </c>
-      <c r="BW105" t="n">
-        <v>68</v>
-      </c>
-      <c r="BX105" t="n">
-        <v>67</v>
-      </c>
-      <c r="BY105" t="n">
-        <v>92</v>
-      </c>
-      <c r="BZ105" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="CA105" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="CB105" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="CC105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN105" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR105" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS105" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU105" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV105" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX105" t="n">
-        <v>10</v>
       </c>
       <c r="CY105" t="n">
         <v>7</v>
       </c>
       <c r="CZ105" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="DA105" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="DB105" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="DC105" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE105" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="DF105" t="n">
-        <v>2</v>
+        <v>1.17</v>
       </c>
       <c r="DG105" t="n">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="DH105" t="n">
-        <v>1.82</v>
+        <v>1</v>
       </c>
       <c r="DI105" t="n">
-        <v>1.42</v>
+        <v>1</v>
       </c>
       <c r="DJ105" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="DK105" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="DL105" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="DM105" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DN105" t="n">
-        <v>2.95</v>
+        <v>2.52</v>
       </c>
       <c r="DO105" t="n">
         <v>18</v>
@@ -50624,7 +50624,7 @@
         <v>1</v>
       </c>
       <c r="DR105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS105" t="b">
         <v>0</v>
@@ -50636,11 +50636,11 @@
         <v>0</v>
       </c>
       <c r="DV105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW105" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="DX105" t="inlineStr">
@@ -50650,17 +50650,17 @@
       </c>
       <c r="DY105" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="DZ105" t="inlineStr">
         <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EA105" t="inlineStr">
+        <is>
           <t>3.22</t>
-        </is>
-      </c>
-      <c r="EA105" t="inlineStr">
-        <is>
-          <t>3.29</t>
         </is>
       </c>
       <c r="EB105" t="inlineStr"/>
@@ -50669,12 +50669,12 @@
       <c r="EE105" t="inlineStr"/>
       <c r="EF105" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EG105" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="EH105" t="inlineStr">
@@ -50684,28 +50684,28 @@
       </c>
       <c r="EI105" t="inlineStr">
         <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EJ105" t="inlineStr">
+        <is>
           <t>1.92</t>
         </is>
       </c>
-      <c r="EJ105" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
       <c r="EK105" t="n">
-        <v>13.94</v>
+        <v>11.53</v>
       </c>
       <c r="EL105" t="n">
-        <v>9.039999999999999</v>
+        <v>6.05</v>
       </c>
       <c r="EM105" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="EN105" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="EO105" t="inlineStr">
@@ -50715,7 +50715,7 @@
       </c>
       <c r="EP105" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.24</t>
         </is>
       </c>
     </row>
@@ -50735,170 +50735,170 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
         <v>45991.45833333334</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
         <v>2</v>
       </c>
       <c r="I106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L106" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M106" t="n">
         <v>1</v>
       </c>
       <c r="N106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R106" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S106" t="n">
         <v>4</v>
       </c>
       <c r="T106" t="n">
+        <v>10</v>
+      </c>
+      <c r="U106" t="n">
         <v>6</v>
       </c>
-      <c r="U106" t="n">
-        <v>7</v>
-      </c>
       <c r="V106" t="n">
+        <v>17</v>
+      </c>
+      <c r="W106" t="n">
         <v>11</v>
       </c>
-      <c r="W106" t="n">
-        <v>14</v>
-      </c>
       <c r="X106" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Y106" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="Z106" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>Estádio Dr. Jorge Sampaio</t>
+          <t>Campo Manuel Marques</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>Rua da Paradela, Pedroso, Vila Nova de Gaia</t>
+          <t>Rua Cândido dos Reis, Torres Vedras</t>
         </is>
       </c>
       <c r="AC106" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD106" t="n">
         <v>6</v>
       </c>
       <c r="AE106" t="n">
-        <v>2.43</v>
+        <v>2.23</v>
       </c>
       <c r="AF106" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AG106" t="n">
-        <v>2.67</v>
+        <v>2.98</v>
       </c>
       <c r="AH106" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AI106" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AJ106" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AK106" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AL106" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AM106" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AN106" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AO106" t="n">
-        <v>2.92</v>
+        <v>2.69</v>
       </c>
       <c r="AP106" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AR106" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AS106" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AT106" t="n">
         <v>1.33</v>
       </c>
       <c r="AU106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV106" t="n">
         <v>0</v>
       </c>
       <c r="AW106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ106" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB106" t="n">
-        <v>4894</v>
+        <v>165</v>
       </c>
       <c r="BC106" t="n">
         <v>0</v>
       </c>
       <c r="BD106" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="BE106" t="n">
         <v>0</v>
@@ -50913,76 +50913,76 @@
         <v>1</v>
       </c>
       <c r="BI106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ106" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BK106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BN106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BO106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BP106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR106" t="n">
+        <v>4</v>
+      </c>
+      <c r="BS106" t="n">
         <v>5</v>
       </c>
-      <c r="BS106" t="n">
-        <v>1</v>
-      </c>
       <c r="BT106" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BU106" t="n">
         <v>1</v>
       </c>
       <c r="BV106" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="BW106" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="BX106" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="BY106" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="BZ106" t="n">
-        <v>1.02</v>
+        <v>0.82</v>
       </c>
       <c r="CA106" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="CB106" t="n">
-        <v>2.46</v>
+        <v>2.87</v>
       </c>
       <c r="CC106" t="n">
         <v>0</v>
       </c>
       <c r="CD106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE106" t="n">
         <v>0</v>
       </c>
       <c r="CF106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG106" t="n">
         <v>0</v>
@@ -51003,88 +51003,88 @@
         <v>0</v>
       </c>
       <c r="CM106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO106" t="n">
         <v>0</v>
       </c>
       <c r="CP106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ106" t="n">
         <v>1</v>
       </c>
       <c r="CR106" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CS106" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="CT106" t="n">
         <v>1</v>
       </c>
       <c r="CU106" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV106" t="n">
         <v>11</v>
       </c>
-      <c r="CV106" t="n">
-        <v>15</v>
-      </c>
       <c r="CW106" t="n">
         <v>1</v>
       </c>
       <c r="CX106" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CY106" t="n">
         <v>7</v>
       </c>
       <c r="CZ106" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="DA106" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="DB106" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="DC106" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="DD106" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="DE106" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DF106" t="n">
-        <v>1.17</v>
+        <v>2</v>
       </c>
       <c r="DG106" t="n">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="DH106" t="n">
-        <v>1</v>
+        <v>1.82</v>
       </c>
       <c r="DI106" t="n">
-        <v>1</v>
+        <v>1.42</v>
       </c>
       <c r="DJ106" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="DK106" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="DL106" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="DM106" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DN106" t="n">
-        <v>2.52</v>
+        <v>2.95</v>
       </c>
       <c r="DO106" t="n">
         <v>18</v>
@@ -51096,7 +51096,7 @@
         <v>1</v>
       </c>
       <c r="DR106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS106" t="b">
         <v>0</v>
@@ -51108,11 +51108,11 @@
         <v>0</v>
       </c>
       <c r="DV106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW106" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="DX106" t="inlineStr">
@@ -51122,17 +51122,17 @@
       </c>
       <c r="DY106" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="DZ106" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EA106" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="EB106" t="inlineStr"/>
@@ -51141,12 +51141,12 @@
       <c r="EE106" t="inlineStr"/>
       <c r="EF106" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EG106" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="EH106" t="inlineStr">
@@ -51156,7 +51156,7 @@
       </c>
       <c r="EI106" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EJ106" t="inlineStr">
@@ -51165,19 +51165,19 @@
         </is>
       </c>
       <c r="EK106" t="n">
-        <v>11.53</v>
+        <v>13.94</v>
       </c>
       <c r="EL106" t="n">
-        <v>6.05</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="EM106" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="EN106" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="EO106" t="inlineStr">
@@ -51187,7 +51187,7 @@
       </c>
       <c r="EP106" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>3.23</t>
         </is>
       </c>
     </row>
@@ -52974,7 +52974,7 @@
         <v>70</v>
       </c>
       <c r="DD110" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE110" t="n">
         <v>0.88</v>
@@ -56769,7 +56769,7 @@
         <v>1.33</v>
       </c>
       <c r="DE118" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF118" t="n">
         <v>1.4</v>
@@ -57851,170 +57851,170 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F121" s="2" t="n">
         <v>46003.75</v>
       </c>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>6</v>
       </c>
       <c r="K121" t="n">
+        <v>6</v>
+      </c>
+      <c r="L121" t="n">
+        <v>12</v>
+      </c>
+      <c r="M121" t="n">
+        <v>4</v>
+      </c>
+      <c r="N121" t="n">
+        <v>2</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>4</v>
+      </c>
+      <c r="R121" t="n">
+        <v>1</v>
+      </c>
+      <c r="S121" t="n">
         <v>5</v>
       </c>
-      <c r="L121" t="n">
-        <v>11</v>
-      </c>
-      <c r="M121" t="n">
+      <c r="T121" t="n">
+        <v>12</v>
+      </c>
+      <c r="U121" t="n">
+        <v>9</v>
+      </c>
+      <c r="V121" t="n">
+        <v>13</v>
+      </c>
+      <c r="W121" t="n">
+        <v>13</v>
+      </c>
+      <c r="X121" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>Estádio Dr. Jorge Sampaio</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>Rua da Paradela, Pedroso, Vila Nova de Gaia</t>
+        </is>
+      </c>
+      <c r="AC121" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR121" t="n">
         <v>3</v>
       </c>
-      <c r="N121" t="n">
-        <v>4</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>5</v>
-      </c>
-      <c r="R121" t="n">
-        <v>8</v>
-      </c>
-      <c r="S121" t="n">
-        <v>9</v>
-      </c>
-      <c r="T121" t="n">
-        <v>3</v>
-      </c>
-      <c r="U121" t="n">
-        <v>14</v>
-      </c>
-      <c r="V121" t="n">
-        <v>11</v>
-      </c>
-      <c r="W121" t="n">
-        <v>14</v>
-      </c>
-      <c r="X121" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y121" t="n">
-        <v>51</v>
-      </c>
-      <c r="Z121" t="n">
-        <v>49</v>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>Estádio de Ribes</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>Rua Associação Desportiva Oliveirense 100, Santa Maria de Oliveira</t>
-        </is>
-      </c>
-      <c r="AC121" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD121" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE121" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF121" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AG121" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH121" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI121" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ121" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AK121" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL121" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM121" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AN121" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AO121" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AP121" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AQ121" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR121" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AS121" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="AT121" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AU121" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV121" t="n">
         <v>1</v>
       </c>
       <c r="AW121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB121" t="n">
-        <v>165</v>
+        <v>1037</v>
       </c>
       <c r="BC121" t="n">
         <v>0</v>
       </c>
       <c r="BD121" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="BE121" t="n">
         <v>0</v>
@@ -58029,13 +58029,13 @@
         <v>1</v>
       </c>
       <c r="BI121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BK121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL121" t="n">
         <v>2</v>
@@ -58044,61 +58044,61 @@
         <v>6</v>
       </c>
       <c r="BN121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ121" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BU121" t="n">
         <v>1</v>
       </c>
       <c r="BV121" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="BW121" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="BX121" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="BY121" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="BZ121" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="CA121" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="CB121" t="n">
-        <v>3.24</v>
+        <v>2.64</v>
       </c>
       <c r="CC121" t="n">
         <v>0</v>
       </c>
       <c r="CD121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE121" t="n">
         <v>0</v>
       </c>
       <c r="CF121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG121" t="n">
         <v>0</v>
@@ -58113,13 +58113,13 @@
         <v>1</v>
       </c>
       <c r="CK121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL121" t="n">
         <v>0</v>
       </c>
       <c r="CM121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN121" t="n">
         <v>0</v>
@@ -58134,16 +58134,16 @@
         <v>1</v>
       </c>
       <c r="CR121" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="CS121" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="CT121" t="n">
         <v>1</v>
       </c>
       <c r="CU121" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="CV121" t="n">
         <v>14</v>
@@ -58152,55 +58152,55 @@
         <v>1</v>
       </c>
       <c r="CX121" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY121" t="n">
         <v>3</v>
       </c>
-      <c r="CY121" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ121" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="DA121" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="DB121" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="DC121" t="n">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="DD121" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="DE121" t="n">
-        <v>1.78</v>
+        <v>0.89</v>
       </c>
       <c r="DF121" t="n">
-        <v>1.71</v>
+        <v>1</v>
       </c>
       <c r="DG121" t="n">
-        <v>1.86</v>
+        <v>1</v>
       </c>
       <c r="DH121" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DI121" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DJ121" t="n">
+        <v>54</v>
+      </c>
+      <c r="DK121" t="n">
+        <v>34</v>
+      </c>
+      <c r="DL121" t="n">
         <v>1.15</v>
       </c>
-      <c r="DI121" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="DJ121" t="n">
-        <v>71</v>
-      </c>
-      <c r="DK121" t="n">
-        <v>29</v>
-      </c>
-      <c r="DL121" t="n">
-        <v>1.29</v>
-      </c>
       <c r="DM121" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="DN121" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="DO121" t="n">
         <v>18</v>
@@ -58209,91 +58209,99 @@
         <v>1</v>
       </c>
       <c r="DQ121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU121" t="b">
         <v>0</v>
       </c>
       <c r="DV121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW121" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="DX121" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="DY121" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="DZ121" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EA121" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="EB121" t="inlineStr"/>
       <c r="EC121" t="inlineStr"/>
-      <c r="ED121" t="inlineStr"/>
-      <c r="EE121" t="inlineStr"/>
+      <c r="ED121" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EE121" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
       <c r="EF121" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EG121" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="EH121" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EI121" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EJ121" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EK121" t="n">
-        <v>9.609999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="EL121" t="n">
-        <v>1.16</v>
+        <v>6.67</v>
       </c>
       <c r="EM121" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="EN121" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EO121" t="inlineStr">
@@ -58303,7 +58311,7 @@
       </c>
       <c r="EP121" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
@@ -58323,41 +58331,41 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F122" s="2" t="n">
         <v>46003.75</v>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J122" t="n">
         <v>6</v>
       </c>
       <c r="K122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L122" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M122" t="n">
+        <v>3</v>
+      </c>
+      <c r="N122" t="n">
         <v>4</v>
       </c>
-      <c r="N122" t="n">
-        <v>2</v>
-      </c>
       <c r="O122" t="n">
         <v>0</v>
       </c>
@@ -58365,128 +58373,128 @@
         <v>0</v>
       </c>
       <c r="Q122" t="n">
+        <v>5</v>
+      </c>
+      <c r="R122" t="n">
+        <v>8</v>
+      </c>
+      <c r="S122" t="n">
+        <v>9</v>
+      </c>
+      <c r="T122" t="n">
+        <v>3</v>
+      </c>
+      <c r="U122" t="n">
+        <v>14</v>
+      </c>
+      <c r="V122" t="n">
+        <v>11</v>
+      </c>
+      <c r="W122" t="n">
+        <v>14</v>
+      </c>
+      <c r="X122" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>Estádio de Ribes</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>Rua Associação Desportiva Oliveirense 100, Santa Maria de Oliveira</t>
+        </is>
+      </c>
+      <c r="AC122" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD122" t="n">
         <v>4</v>
       </c>
-      <c r="R122" t="n">
-        <v>1</v>
-      </c>
-      <c r="S122" t="n">
+      <c r="AE122" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU122" t="n">
         <v>5</v>
       </c>
-      <c r="T122" t="n">
-        <v>12</v>
-      </c>
-      <c r="U122" t="n">
-        <v>9</v>
-      </c>
-      <c r="V122" t="n">
-        <v>13</v>
-      </c>
-      <c r="W122" t="n">
-        <v>13</v>
-      </c>
-      <c r="X122" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>44</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>Estádio Dr. Jorge Sampaio</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>Rua da Paradela, Pedroso, Vila Nova de Gaia</t>
-        </is>
-      </c>
-      <c r="AC122" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD122" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE122" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF122" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG122" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="AH122" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI122" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ122" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AK122" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL122" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM122" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN122" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AO122" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AP122" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AQ122" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR122" t="n">
+      <c r="AV122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ122" t="n">
         <v>3</v>
       </c>
-      <c r="AS122" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AT122" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AU122" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV122" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ122" t="n">
-        <v>0</v>
-      </c>
       <c r="BA122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB122" t="n">
-        <v>1037</v>
+        <v>165</v>
       </c>
       <c r="BC122" t="n">
         <v>0</v>
       </c>
       <c r="BD122" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="BE122" t="n">
         <v>0</v>
@@ -58501,13 +58509,13 @@
         <v>1</v>
       </c>
       <c r="BI122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BK122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL122" t="n">
         <v>2</v>
@@ -58516,61 +58524,61 @@
         <v>6</v>
       </c>
       <c r="BN122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BO122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BR122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BU122" t="n">
         <v>1</v>
       </c>
       <c r="BV122" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="BW122" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="BX122" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="BY122" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="BZ122" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="CA122" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="CB122" t="n">
-        <v>2.64</v>
+        <v>3.24</v>
       </c>
       <c r="CC122" t="n">
         <v>0</v>
       </c>
       <c r="CD122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE122" t="n">
         <v>0</v>
       </c>
       <c r="CF122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG122" t="n">
         <v>0</v>
@@ -58585,13 +58593,13 @@
         <v>1</v>
       </c>
       <c r="CK122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL122" t="n">
         <v>0</v>
       </c>
       <c r="CM122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN122" t="n">
         <v>0</v>
@@ -58606,16 +58614,16 @@
         <v>1</v>
       </c>
       <c r="CR122" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="CS122" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="CT122" t="n">
         <v>1</v>
       </c>
       <c r="CU122" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="CV122" t="n">
         <v>14</v>
@@ -58624,55 +58632,55 @@
         <v>1</v>
       </c>
       <c r="CX122" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="CY122" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CZ122" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="DA122" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="DB122" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="DC122" t="n">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="DD122" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="DE122" t="n">
-        <v>0.89</v>
+        <v>1.78</v>
       </c>
       <c r="DF122" t="n">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="DG122" t="n">
-        <v>1</v>
+        <v>1.86</v>
       </c>
       <c r="DH122" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="DI122" t="n">
-        <v>1.14</v>
+        <v>1.64</v>
       </c>
       <c r="DJ122" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="DK122" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="DL122" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="DM122" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="DN122" t="n">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="DO122" t="n">
         <v>18</v>
@@ -58681,99 +58689,91 @@
         <v>1</v>
       </c>
       <c r="DQ122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU122" t="b">
         <v>0</v>
       </c>
       <c r="DV122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW122" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="DX122" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="DY122" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="DZ122" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EA122" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EB122" t="inlineStr"/>
       <c r="EC122" t="inlineStr"/>
-      <c r="ED122" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EE122" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
+      <c r="ED122" t="inlineStr"/>
+      <c r="EE122" t="inlineStr"/>
       <c r="EF122" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EG122" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="EH122" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EI122" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EJ122" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EK122" t="n">
-        <v>9.9</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="EL122" t="n">
-        <v>6.67</v>
+        <v>1.16</v>
       </c>
       <c r="EM122" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="EN122" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="EO122" t="inlineStr">
@@ -58783,7 +58783,7 @@
       </c>
       <c r="EP122" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.22</t>
         </is>
       </c>
     </row>
@@ -60223,31 +60223,31 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F126" s="2" t="n">
         <v>46005.45833333334</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J126" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L126" t="n">
         <v>9</v>
@@ -60256,137 +60256,137 @@
         <v>4</v>
       </c>
       <c r="N126" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P126" t="n">
         <v>1</v>
       </c>
       <c r="Q126" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R126" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S126" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T126" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U126" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V126" t="n">
         <v>10</v>
       </c>
       <c r="W126" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="X126" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y126" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="Z126" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>CGD Stadium Aurélio Pereira</t>
+          <t>Estádio Municipal de Portimão</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>, Alcochete</t>
+          <t>Avenida Zeca Afonso Portimão, Portimão</t>
         </is>
       </c>
       <c r="AC126" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD126" t="n">
         <v>4</v>
       </c>
-      <c r="AD126" t="n">
-        <v>8</v>
-      </c>
       <c r="AE126" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="AF126" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AG126" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AH126" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AI126" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AJ126" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AK126" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL126" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AM126" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AN126" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AO126" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AR126" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="AS126" t="n">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="AT126" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AU126" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX126" t="n">
         <v>0</v>
       </c>
       <c r="AY126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA126" t="n">
         <v>1</v>
       </c>
       <c r="BB126" t="n">
-        <v>4841</v>
+        <v>1030</v>
       </c>
       <c r="BC126" t="n">
         <v>0</v>
       </c>
       <c r="BD126" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="BE126" t="n">
         <v>0</v>
@@ -60407,10 +60407,10 @@
         <v>1</v>
       </c>
       <c r="BK126" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BM126" t="n">
         <v>5</v>
@@ -60419,160 +60419,160 @@
         <v>4</v>
       </c>
       <c r="BO126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BP126" t="n">
         <v>2</v>
       </c>
       <c r="BQ126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT126" t="n">
         <v>4</v>
       </c>
-      <c r="BR126" t="n">
-        <v>5</v>
-      </c>
-      <c r="BS126" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT126" t="n">
+      <c r="BU126" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>32</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>58</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>27</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU126" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV126" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW126" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX126" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY126" t="n">
         <v>9</v>
       </c>
-      <c r="BU126" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV126" t="n">
-        <v>80</v>
-      </c>
-      <c r="BW126" t="n">
-        <v>40</v>
-      </c>
-      <c r="BX126" t="n">
-        <v>85</v>
-      </c>
-      <c r="BY126" t="n">
-        <v>68</v>
-      </c>
-      <c r="BZ126" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CA126" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CB126" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="CC126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP126" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR126" t="n">
-        <v>26</v>
-      </c>
-      <c r="CS126" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU126" t="n">
-        <v>10</v>
-      </c>
-      <c r="CV126" t="n">
-        <v>17</v>
-      </c>
-      <c r="CW126" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX126" t="n">
+      <c r="CZ126" t="n">
+        <v>31</v>
+      </c>
+      <c r="DA126" t="n">
+        <v>93</v>
+      </c>
+      <c r="DB126" t="n">
         <v>7</v>
       </c>
-      <c r="CY126" t="n">
-        <v>10</v>
-      </c>
-      <c r="CZ126" t="n">
-        <v>48</v>
-      </c>
-      <c r="DA126" t="n">
-        <v>77</v>
-      </c>
-      <c r="DB126" t="n">
-        <v>32</v>
-      </c>
       <c r="DC126" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="DD126" t="n">
-        <v>1.67</v>
+        <v>0.78</v>
       </c>
       <c r="DE126" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="DF126" t="n">
-        <v>2.5</v>
+        <v>0.86</v>
       </c>
       <c r="DG126" t="n">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="DH126" t="n">
-        <v>2.23</v>
+        <v>0.92</v>
       </c>
       <c r="DI126" t="n">
-        <v>1.54</v>
+        <v>0.93</v>
       </c>
       <c r="DJ126" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="DK126" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="DL126" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="DM126" t="n">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="DN126" t="n">
-        <v>3.42</v>
+        <v>2.96</v>
       </c>
       <c r="DO126" t="n">
         <v>18</v>
@@ -60581,10 +60581,10 @@
         <v>1</v>
       </c>
       <c r="DQ126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS126" t="b">
         <v>0</v>
@@ -60596,31 +60596,31 @@
         <v>0</v>
       </c>
       <c r="DV126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW126" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="DX126" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="DY126" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="DZ126" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="EA126" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="EB126" t="inlineStr"/>
@@ -60629,53 +60629,53 @@
       <c r="EE126" t="inlineStr"/>
       <c r="EF126" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EG126" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="EH126" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EI126" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EJ126" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EK126" t="n">
-        <v>14.47</v>
+        <v>16.58</v>
       </c>
       <c r="EL126" t="n">
-        <v>7.14</v>
+        <v>4.73</v>
       </c>
       <c r="EM126" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="EN126" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="EO126" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EP126" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.98</t>
         </is>
       </c>
     </row>
@@ -60695,31 +60695,31 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F127" s="2" t="n">
         <v>46005.45833333334</v>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K127" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L127" t="n">
         <v>9</v>
@@ -60728,137 +60728,137 @@
         <v>4</v>
       </c>
       <c r="N127" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P127" t="n">
         <v>1</v>
       </c>
       <c r="Q127" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R127" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S127" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T127" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U127" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="V127" t="n">
         <v>10</v>
       </c>
       <c r="W127" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="X127" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y127" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Z127" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>Estádio Municipal de Portimão</t>
+          <t>CGD Stadium Aurélio Pereira</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>Avenida Zeca Afonso Portimão, Portimão</t>
+          <t>, Alcochete</t>
         </is>
       </c>
       <c r="AC127" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD127" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE127" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="AF127" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AG127" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AO127" t="n">
         <v>2.6</v>
       </c>
-      <c r="AH127" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI127" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ127" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AK127" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL127" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM127" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN127" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO127" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AP127" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AR127" t="n">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="AS127" t="n">
-        <v>2.66</v>
+        <v>2.91</v>
       </c>
       <c r="AT127" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AU127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX127" t="n">
         <v>0</v>
       </c>
       <c r="AY127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA127" t="n">
         <v>1</v>
       </c>
       <c r="BB127" t="n">
-        <v>1030</v>
+        <v>4841</v>
       </c>
       <c r="BC127" t="n">
         <v>0</v>
       </c>
       <c r="BD127" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="BE127" t="n">
         <v>0</v>
@@ -60879,10 +60879,10 @@
         <v>1</v>
       </c>
       <c r="BK127" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL127" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BM127" t="n">
         <v>5</v>
@@ -60891,160 +60891,160 @@
         <v>4</v>
       </c>
       <c r="BO127" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BP127" t="n">
         <v>2</v>
       </c>
       <c r="BQ127" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BR127" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BS127" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BT127" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BU127" t="n">
         <v>1</v>
       </c>
       <c r="BV127" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>40</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>68</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>26</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU127" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV127" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX127" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY127" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ127" t="n">
+        <v>48</v>
+      </c>
+      <c r="DA127" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB127" t="n">
+        <v>32</v>
+      </c>
+      <c r="DC127" t="n">
+        <v>85</v>
+      </c>
+      <c r="DD127" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE127" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DF127" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DG127" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DH127" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DI127" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DJ127" t="n">
         <v>52</v>
       </c>
-      <c r="BW127" t="n">
-        <v>32</v>
-      </c>
-      <c r="BX127" t="n">
-        <v>91</v>
-      </c>
-      <c r="BY127" t="n">
-        <v>58</v>
-      </c>
-      <c r="BZ127" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CA127" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CB127" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="CC127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI127" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ127" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM127" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP127" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ127" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR127" t="n">
-        <v>27</v>
-      </c>
-      <c r="CS127" t="n">
-        <v>29</v>
-      </c>
-      <c r="CT127" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU127" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV127" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW127" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX127" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY127" t="n">
-        <v>9</v>
-      </c>
-      <c r="CZ127" t="n">
-        <v>31</v>
-      </c>
-      <c r="DA127" t="n">
-        <v>93</v>
-      </c>
-      <c r="DB127" t="n">
-        <v>7</v>
-      </c>
-      <c r="DC127" t="n">
-        <v>61</v>
-      </c>
-      <c r="DD127" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="DE127" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="DF127" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="DG127" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DH127" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DI127" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="DJ127" t="n">
-        <v>69</v>
-      </c>
       <c r="DK127" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="DL127" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="DM127" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="DN127" t="n">
-        <v>2.96</v>
+        <v>3.42</v>
       </c>
       <c r="DO127" t="n">
         <v>18</v>
@@ -61053,10 +61053,10 @@
         <v>1</v>
       </c>
       <c r="DQ127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS127" t="b">
         <v>0</v>
@@ -61068,31 +61068,31 @@
         <v>0</v>
       </c>
       <c r="DV127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW127" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="DX127" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="DY127" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="DZ127" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EA127" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EB127" t="inlineStr"/>
@@ -61101,53 +61101,53 @@
       <c r="EE127" t="inlineStr"/>
       <c r="EF127" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EG127" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="EH127" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EI127" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EJ127" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EK127" t="n">
-        <v>16.58</v>
+        <v>14.47</v>
       </c>
       <c r="EL127" t="n">
-        <v>4.73</v>
+        <v>7.14</v>
       </c>
       <c r="EM127" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="EN127" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="EO127" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EP127" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.06</t>
         </is>
       </c>
     </row>
@@ -61486,7 +61486,7 @@
         <v>75</v>
       </c>
       <c r="DD128" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE128" t="n">
         <v>1.88</v>
@@ -63401,7 +63401,7 @@
         <v>1.67</v>
       </c>
       <c r="DE132" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="DF132" t="n">
         <v>1.83</v>
@@ -67170,7 +67170,7 @@
         <v>75</v>
       </c>
       <c r="DD140" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="DE140" t="n">
         <v>1.44</v>
@@ -69195,12 +69195,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F145" s="2" t="n">
@@ -69216,43 +69216,43 @@
         <v>3</v>
       </c>
       <c r="J145" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" t="n">
+        <v>6</v>
+      </c>
+      <c r="L145" t="n">
+        <v>7</v>
+      </c>
+      <c r="M145" t="n">
+        <v>5</v>
+      </c>
+      <c r="N145" t="n">
+        <v>2</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>1</v>
+      </c>
+      <c r="R145" t="n">
+        <v>4</v>
+      </c>
+      <c r="S145" t="n">
+        <v>4</v>
+      </c>
+      <c r="T145" t="n">
         <v>9</v>
       </c>
-      <c r="K145" t="n">
-        <v>4</v>
-      </c>
-      <c r="L145" t="n">
+      <c r="U145" t="n">
+        <v>5</v>
+      </c>
+      <c r="V145" t="n">
         <v>13</v>
-      </c>
-      <c r="M145" t="n">
-        <v>0</v>
-      </c>
-      <c r="N145" t="n">
-        <v>1</v>
-      </c>
-      <c r="O145" t="n">
-        <v>0</v>
-      </c>
-      <c r="P145" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>8</v>
-      </c>
-      <c r="R145" t="n">
-        <v>6</v>
-      </c>
-      <c r="S145" t="n">
-        <v>7</v>
-      </c>
-      <c r="T145" t="n">
-        <v>8</v>
-      </c>
-      <c r="U145" t="n">
-        <v>15</v>
-      </c>
-      <c r="V145" t="n">
-        <v>14</v>
       </c>
       <c r="W145" t="n">
         <v>19</v>
@@ -69261,74 +69261,74 @@
         <v>14</v>
       </c>
       <c r="Y145" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z145" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Estádio Municipal 25 de Abril</t>
+          <t>CGD Stadium Aurélio Pereira</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>Rua Futebol Clube de Penafiel, Penafiel</t>
+          <t>, Alcochete</t>
         </is>
       </c>
       <c r="AC145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE145" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AF145" t="n">
         <v>3</v>
       </c>
       <c r="AG145" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH145" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AI145" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AJ145" t="n">
-        <v>3.87</v>
+        <v>3.58</v>
       </c>
       <c r="AK145" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL145" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AM145" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AN145" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="AO145" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AP145" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AR145" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AS145" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="AT145" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AU145" t="n">
         <v>3</v>
@@ -69352,136 +69352,136 @@
         <v>2</v>
       </c>
       <c r="BB145" t="n">
-        <v>173</v>
+        <v>1032</v>
       </c>
       <c r="BC145" t="n">
         <v>0</v>
       </c>
       <c r="BD145" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO145" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT145" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU145" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV145" t="n">
+        <v>39</v>
+      </c>
+      <c r="BW145" t="n">
+        <v>55</v>
+      </c>
+      <c r="BX145" t="n">
+        <v>102</v>
+      </c>
+      <c r="BY145" t="n">
+        <v>113</v>
+      </c>
+      <c r="BZ145" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="CA145" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CB145" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP145" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ145" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR145" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS145" t="n">
         <v>27</v>
-      </c>
-      <c r="BE145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF145" t="n">
-        <v>2099</v>
-      </c>
-      <c r="BG145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK145" t="n">
-        <v>7</v>
-      </c>
-      <c r="BL145" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM145" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN145" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT145" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU145" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV145" t="n">
-        <v>76</v>
-      </c>
-      <c r="BW145" t="n">
-        <v>53</v>
-      </c>
-      <c r="BX145" t="n">
-        <v>98</v>
-      </c>
-      <c r="BY145" t="n">
-        <v>83</v>
-      </c>
-      <c r="BZ145" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="CA145" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CB145" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="CC145" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE145" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI145" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ145" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN145" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP145" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ145" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR145" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS145" t="n">
-        <v>17</v>
       </c>
       <c r="CT145" t="n">
         <v>1</v>
@@ -69490,61 +69490,61 @@
         <v>14</v>
       </c>
       <c r="CV145" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="CW145" t="n">
         <v>1</v>
       </c>
       <c r="CX145" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CY145" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="CZ145" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="DA145" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="DB145" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="DC145" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="DD145" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="DE145" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="DF145" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="DG145" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="DH145" t="n">
-        <v>1.19</v>
+        <v>1.93</v>
       </c>
       <c r="DI145" t="n">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="DJ145" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="DK145" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="DL145" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="DM145" t="n">
-        <v>0.96</v>
+        <v>1.56</v>
       </c>
       <c r="DN145" t="n">
-        <v>2.44</v>
+        <v>3.46</v>
       </c>
       <c r="DO145" t="n">
         <v>18</v>
@@ -69572,90 +69572,90 @@
       </c>
       <c r="DW145" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="DX145" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="DY145" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="DZ145" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="EA145" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="EB145" t="inlineStr"/>
       <c r="EC145" t="inlineStr"/>
       <c r="ED145" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EE145" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EF145" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EG145" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="EH145" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EI145" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EJ145" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EK145" t="n">
-        <v>10.13</v>
+        <v>12.38</v>
       </c>
       <c r="EL145" t="n">
-        <v>4.72</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="EM145" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="EN145" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EO145" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EP145" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.31</t>
         </is>
       </c>
     </row>
@@ -69675,12 +69675,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F146" s="2" t="n">
@@ -69696,43 +69696,43 @@
         <v>3</v>
       </c>
       <c r="J146" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K146" t="n">
+        <v>4</v>
+      </c>
+      <c r="L146" t="n">
+        <v>13</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>8</v>
+      </c>
+      <c r="R146" t="n">
         <v>6</v>
       </c>
-      <c r="L146" t="n">
+      <c r="S146" t="n">
         <v>7</v>
       </c>
-      <c r="M146" t="n">
-        <v>5</v>
-      </c>
-      <c r="N146" t="n">
-        <v>2</v>
-      </c>
-      <c r="O146" t="n">
-        <v>0</v>
-      </c>
-      <c r="P146" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>1</v>
-      </c>
-      <c r="R146" t="n">
-        <v>4</v>
-      </c>
-      <c r="S146" t="n">
-        <v>4</v>
-      </c>
       <c r="T146" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U146" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="V146" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W146" t="n">
         <v>19</v>
@@ -69741,74 +69741,74 @@
         <v>14</v>
       </c>
       <c r="Y146" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Z146" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>CGD Stadium Aurélio Pereira</t>
+          <t>Estádio Municipal 25 de Abril</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>, Alcochete</t>
+          <t>Rua Futebol Clube de Penafiel, Penafiel</t>
         </is>
       </c>
       <c r="AC146" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE146" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="AF146" t="n">
         <v>3</v>
       </c>
       <c r="AG146" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="AH146" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AT146" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AI146" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ146" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AK146" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL146" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM146" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN146" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AO146" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AP146" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AQ146" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR146" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AS146" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT146" t="n">
-        <v>1.32</v>
       </c>
       <c r="AU146" t="n">
         <v>3</v>
@@ -69832,19 +69832,19 @@
         <v>2</v>
       </c>
       <c r="BB146" t="n">
-        <v>1032</v>
+        <v>173</v>
       </c>
       <c r="BC146" t="n">
         <v>0</v>
       </c>
       <c r="BD146" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="BE146" t="n">
         <v>0</v>
       </c>
       <c r="BF146" t="n">
-        <v>-1</v>
+        <v>2099</v>
       </c>
       <c r="BG146" t="n">
         <v>2</v>
@@ -69853,73 +69853,73 @@
         <v>1</v>
       </c>
       <c r="BI146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK146" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BL146" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BM146" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BN146" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BO146" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP146" t="n">
         <v>1</v>
       </c>
       <c r="BQ146" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BR146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT146" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BU146" t="n">
         <v>1</v>
       </c>
       <c r="BV146" t="n">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="BW146" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="BX146" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="BY146" t="n">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="BZ146" t="n">
-        <v>0.68</v>
+        <v>2.05</v>
       </c>
       <c r="CA146" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="CB146" t="n">
-        <v>2.19</v>
+        <v>3.74</v>
       </c>
       <c r="CC146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD146" t="n">
         <v>0</v>
       </c>
       <c r="CE146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF146" t="n">
         <v>0</v>
@@ -69937,7 +69937,7 @@
         <v>1</v>
       </c>
       <c r="CK146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL146" t="n">
         <v>0</v>
@@ -69946,7 +69946,7 @@
         <v>0</v>
       </c>
       <c r="CN146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO146" t="n">
         <v>0</v>
@@ -69958,10 +69958,10 @@
         <v>1</v>
       </c>
       <c r="CR146" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="CS146" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="CT146" t="n">
         <v>1</v>
@@ -69970,61 +69970,61 @@
         <v>14</v>
       </c>
       <c r="CV146" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="CW146" t="n">
         <v>1</v>
       </c>
       <c r="CX146" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="CY146" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CZ146" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="DA146" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="DB146" t="n">
+        <v>20</v>
+      </c>
+      <c r="DC146" t="n">
+        <v>53</v>
+      </c>
+      <c r="DD146" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DE146" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="DF146" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG146" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH146" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="DI146" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ146" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK146" t="n">
         <v>41</v>
       </c>
-      <c r="DC146" t="n">
-        <v>75</v>
-      </c>
-      <c r="DD146" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DE146" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DF146" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DG146" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DH146" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="DI146" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="DJ146" t="n">
-        <v>34</v>
-      </c>
-      <c r="DK146" t="n">
-        <v>34</v>
-      </c>
       <c r="DL146" t="n">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="DM146" t="n">
-        <v>1.56</v>
+        <v>0.96</v>
       </c>
       <c r="DN146" t="n">
-        <v>3.46</v>
+        <v>2.44</v>
       </c>
       <c r="DO146" t="n">
         <v>18</v>
@@ -70052,90 +70052,90 @@
       </c>
       <c r="DW146" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="DX146" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="DY146" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="DZ146" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="EA146" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="EB146" t="inlineStr"/>
       <c r="EC146" t="inlineStr"/>
       <c r="ED146" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EE146" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EF146" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EG146" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="EH146" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EI146" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EJ146" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EK146" t="n">
-        <v>12.38</v>
+        <v>10.13</v>
       </c>
       <c r="EL146" t="n">
-        <v>9.359999999999999</v>
+        <v>4.72</v>
       </c>
       <c r="EM146" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="EN146" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="EO146" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EP146" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.15</t>
         </is>
       </c>
     </row>
@@ -76880,16 +76880,16 @@
         <v>3</v>
       </c>
       <c r="R161" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S161" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T161" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U161" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="V161" t="n">
         <v>8</v>
@@ -76901,10 +76901,10 @@
         <v>7</v>
       </c>
       <c r="Y161" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z161" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
@@ -77064,13 +77064,13 @@
         <v>96</v>
       </c>
       <c r="BZ161" t="n">
-        <v>0.92</v>
+        <v>1.54</v>
       </c>
       <c r="CA161" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="CB161" t="n">
-        <v>2.23</v>
+        <v>2.78</v>
       </c>
       <c r="CC161" t="n">
         <v>0</v>
@@ -77127,19 +77127,19 @@
         <v>1</v>
       </c>
       <c r="CU161" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CV161" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CW161" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX161" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CY161" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CZ161" t="n">
         <v>38</v>
@@ -77315,10 +77315,10 @@
         <v>4</v>
       </c>
       <c r="K162" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L162" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M162" t="n">
         <v>1</v>
@@ -77342,13 +77342,13 @@
         <v>3</v>
       </c>
       <c r="T162" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U162" t="n">
         <v>4</v>
       </c>
       <c r="V162" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W162" t="n">
         <v>8</v>
@@ -77357,10 +77357,10 @@
         <v>11</v>
       </c>
       <c r="Y162" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="Z162" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
@@ -77523,10 +77523,10 @@
         <v>0.53</v>
       </c>
       <c r="CA162" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="CB162" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="CC162" t="n">
         <v>0</v>
@@ -77577,25 +77577,25 @@
         <v>14</v>
       </c>
       <c r="CS162" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CT162" t="n">
         <v>1</v>
       </c>
       <c r="CU162" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CV162" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CW162" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX162" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CY162" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CZ162" t="n">
         <v>48</v>
@@ -77809,7 +77809,7 @@
         <v>10</v>
       </c>
       <c r="M163" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N163" t="n">
         <v>1</v>
@@ -77824,19 +77824,19 @@
         <v>5</v>
       </c>
       <c r="R163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S163" t="n">
         <v>4</v>
       </c>
       <c r="T163" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U163" t="n">
         <v>9</v>
       </c>
       <c r="V163" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="W163" t="n">
         <v>21</v>
@@ -77861,7 +77861,7 @@
         </is>
       </c>
       <c r="AC163" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD163" t="n">
         <v>1</v>
@@ -77981,7 +77981,7 @@
         <v>0</v>
       </c>
       <c r="BQ163" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BR163" t="n">
         <v>1</v>
@@ -77990,7 +77990,7 @@
         <v>0</v>
       </c>
       <c r="BT163" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BU163" t="n">
         <v>1</v>
@@ -78011,10 +78011,10 @@
         <v>1.23</v>
       </c>
       <c r="CA163" t="n">
-        <v>1.59</v>
+        <v>1.03</v>
       </c>
       <c r="CB163" t="n">
-        <v>2.82</v>
+        <v>2.26</v>
       </c>
       <c r="CC163" t="n">
         <v>0</v>
@@ -78232,6 +78232,478 @@
       <c r="EP163" t="inlineStr">
         <is>
           <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>LigaPro_Portugal_2a_división_2025-2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>19</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Paços de Ferreira</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Academico Viseu</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>46045.75</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2</v>
+      </c>
+      <c r="H164" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" t="n">
+        <v>3</v>
+      </c>
+      <c r="J164" t="n">
+        <v>8</v>
+      </c>
+      <c r="K164" t="n">
+        <v>2</v>
+      </c>
+      <c r="L164" t="n">
+        <v>10</v>
+      </c>
+      <c r="M164" t="n">
+        <v>8</v>
+      </c>
+      <c r="N164" t="n">
+        <v>2</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>7</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6</v>
+      </c>
+      <c r="S164" t="n">
+        <v>13</v>
+      </c>
+      <c r="T164" t="n">
+        <v>3</v>
+      </c>
+      <c r="U164" t="n">
+        <v>20</v>
+      </c>
+      <c r="V164" t="n">
+        <v>9</v>
+      </c>
+      <c r="W164" t="n">
+        <v>12</v>
+      </c>
+      <c r="X164" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>Estádio da Capital do Móvel</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>Rua do Estádio, Apartado 26, Paços de Ferreira</t>
+        </is>
+      </c>
+      <c r="AC164" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>173</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>77</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ164" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR164" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS164" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT164" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU164" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV164" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW164" t="n">
+        <v>37</v>
+      </c>
+      <c r="BX164" t="n">
+        <v>93</v>
+      </c>
+      <c r="BY164" t="n">
+        <v>58</v>
+      </c>
+      <c r="BZ164" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CA164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CB164" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="CC164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP164" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR164" t="n">
+        <v>29</v>
+      </c>
+      <c r="CS164" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT164" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU164" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV164" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CX164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CY164" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CZ164" t="n">
+        <v>71</v>
+      </c>
+      <c r="DA164" t="n">
+        <v>77</v>
+      </c>
+      <c r="DB164" t="n">
+        <v>35</v>
+      </c>
+      <c r="DC164" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD164" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DE164" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DF164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG164" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DH164" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="DI164" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DJ164" t="n">
+        <v>30</v>
+      </c>
+      <c r="DK164" t="n">
+        <v>24</v>
+      </c>
+      <c r="DL164" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DM164" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DN164" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="DO164" t="n">
+        <v>19</v>
+      </c>
+      <c r="DP164" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ164" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR164" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU164" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV164" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW164" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="DX164" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="DY164" t="inlineStr">
+        <is>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="DZ164" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EA164" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="EB164" t="inlineStr"/>
+      <c r="EC164" t="inlineStr"/>
+      <c r="ED164" t="inlineStr"/>
+      <c r="EE164" t="inlineStr"/>
+      <c r="EF164" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EG164" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="EH164" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EI164" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EJ164" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EK164" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="EL164" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="EM164" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="EN164" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EO164" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EP164" t="inlineStr">
+        <is>
+          <t>3.01</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -80537,22 +80537,22 @@
         <v>0</v>
       </c>
       <c r="Q174" t="n">
+        <v>2</v>
+      </c>
+      <c r="R174" t="n">
+        <v>3</v>
+      </c>
+      <c r="S174" t="n">
+        <v>10</v>
+      </c>
+      <c r="T174" t="n">
         <v>4</v>
       </c>
-      <c r="R174" t="n">
-        <v>3</v>
-      </c>
-      <c r="S174" t="n">
-        <v>4</v>
-      </c>
-      <c r="T174" t="n">
-        <v>3</v>
-      </c>
       <c r="U174" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="V174" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W174" t="n">
         <v>18</v>
@@ -80724,13 +80724,13 @@
         <v>130</v>
       </c>
       <c r="BZ174" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="CA174" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="CB174" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="CC174" t="n">
         <v>0</v>
@@ -80778,7 +80778,7 @@
         <v>1</v>
       </c>
       <c r="CR174" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CS174" t="n">
         <v>20</v>
@@ -80787,19 +80787,19 @@
         <v>1</v>
       </c>
       <c r="CU174" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CV174" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CW174" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX174" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CY174" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CZ174" t="n">
         <v>33</v>
@@ -83278,7 +83278,7 @@
         <v>0</v>
       </c>
       <c r="P180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q180" t="n">
         <v>4</v>
@@ -83324,7 +83324,7 @@
         <v>3</v>
       </c>
       <c r="AD180" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE180" t="n">
         <v>3.4</v>
@@ -83444,13 +83444,13 @@
         <v>2</v>
       </c>
       <c r="BR180" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BS180" t="n">
         <v>3</v>
       </c>
       <c r="BT180" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BU180" t="n">
         <v>1</v>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -81921,22 +81921,22 @@
         <v>0</v>
       </c>
       <c r="Q177" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R177" t="n">
         <v>4</v>
       </c>
       <c r="S177" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T177" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U177" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V177" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W177" t="n">
         <v>19</v>
@@ -81945,10 +81945,10 @@
         <v>14</v>
       </c>
       <c r="Y177" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="Z177" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
@@ -82108,13 +82108,13 @@
         <v>86</v>
       </c>
       <c r="BZ177" t="n">
-        <v>1.75</v>
+        <v>2.19</v>
       </c>
       <c r="CA177" t="n">
-        <v>0.9</v>
+        <v>1.21</v>
       </c>
       <c r="CB177" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="CC177" t="n">
         <v>0</v>
@@ -82171,19 +82171,19 @@
         <v>1</v>
       </c>
       <c r="CU177" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CV177" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="CW177" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX177" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CY177" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="CZ177" t="n">
         <v>33</v>
@@ -82383,16 +82383,16 @@
         <v>5</v>
       </c>
       <c r="S178" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="T178" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U178" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="V178" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W178" t="n">
         <v>11</v>
@@ -82401,10 +82401,10 @@
         <v>14</v>
       </c>
       <c r="Y178" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Z178" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="inlineStr"/>
@@ -82556,13 +82556,13 @@
         <v>55</v>
       </c>
       <c r="BZ178" t="n">
-        <v>1.05</v>
+        <v>1.61</v>
       </c>
       <c r="CA178" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="CB178" t="n">
-        <v>2.27</v>
+        <v>2.95</v>
       </c>
       <c r="CC178" t="n">
         <v>0</v>
@@ -82613,25 +82613,25 @@
         <v>27</v>
       </c>
       <c r="CS178" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CT178" t="n">
         <v>1</v>
       </c>
       <c r="CU178" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="CV178" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CW178" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX178" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CY178" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CZ178" t="n">
         <v>50</v>
@@ -82826,13 +82826,13 @@
         <v>4</v>
       </c>
       <c r="T179" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U179" t="n">
         <v>9</v>
       </c>
       <c r="V179" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W179" t="n">
         <v>9</v>
@@ -82841,10 +82841,10 @@
         <v>11</v>
       </c>
       <c r="Y179" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="Z179" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
@@ -83007,10 +83007,10 @@
         <v>1.29</v>
       </c>
       <c r="CA179" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="CB179" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="CC179" t="n">
         <v>0</v>
@@ -83067,19 +83067,19 @@
         <v>1</v>
       </c>
       <c r="CU179" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CV179" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CW179" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX179" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY179" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CZ179" t="n">
         <v>39</v>
@@ -83287,16 +83287,16 @@
         <v>6</v>
       </c>
       <c r="S180" t="n">
+        <v>9</v>
+      </c>
+      <c r="T180" t="n">
         <v>8</v>
       </c>
-      <c r="T180" t="n">
-        <v>5</v>
-      </c>
       <c r="U180" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V180" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="W180" t="n">
         <v>13</v>
@@ -83305,10 +83305,10 @@
         <v>21</v>
       </c>
       <c r="Y180" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="Z180" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
@@ -83468,13 +83468,13 @@
         <v>87</v>
       </c>
       <c r="BZ180" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="CA180" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="CB180" t="n">
-        <v>2.93</v>
+        <v>3.17</v>
       </c>
       <c r="CC180" t="n">
         <v>0</v>
@@ -83534,16 +83534,16 @@
         <v>21</v>
       </c>
       <c r="CV180" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="CW180" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX180" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CY180" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CZ180" t="n">
         <v>39</v>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -87929,19 +87929,19 @@
         <v>0</v>
       </c>
       <c r="Q190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S190" t="n">
         <v>2</v>
       </c>
       <c r="T190" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U190" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V190" t="n">
         <v>6</v>
@@ -87953,10 +87953,10 @@
         <v>14</v>
       </c>
       <c r="Y190" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Z190" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
@@ -88116,13 +88116,13 @@
         <v>86</v>
       </c>
       <c r="BZ190" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="CA190" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="CB190" t="n">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="CC190" t="n">
         <v>0</v>
@@ -88173,25 +88173,25 @@
         <v>24</v>
       </c>
       <c r="CS190" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT190" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU190" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV190" t="n">
         <v>22</v>
       </c>
-      <c r="CT190" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU190" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV190" t="n">
-        <v>24</v>
-      </c>
       <c r="CW190" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX190" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="CY190" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="CZ190" t="n">
         <v>35</v>
@@ -88393,22 +88393,22 @@
         <v>0</v>
       </c>
       <c r="Q191" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S191" t="n">
+        <v>10</v>
+      </c>
+      <c r="T191" t="n">
         <v>5</v>
       </c>
-      <c r="T191" t="n">
-        <v>0</v>
-      </c>
       <c r="U191" t="n">
+        <v>20</v>
+      </c>
+      <c r="V191" t="n">
         <v>8</v>
-      </c>
-      <c r="V191" t="n">
-        <v>2</v>
       </c>
       <c r="W191" t="n">
         <v>7</v>
@@ -88417,10 +88417,10 @@
         <v>5</v>
       </c>
       <c r="Y191" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Z191" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
@@ -88580,13 +88580,13 @@
         <v>97</v>
       </c>
       <c r="BZ191" t="n">
-        <v>1.15</v>
+        <v>2.38</v>
       </c>
       <c r="CA191" t="n">
-        <v>0.64</v>
+        <v>1.08</v>
       </c>
       <c r="CB191" t="n">
-        <v>1.78</v>
+        <v>3.46</v>
       </c>
       <c r="CC191" t="n">
         <v>0</v>
@@ -88643,19 +88643,19 @@
         <v>1</v>
       </c>
       <c r="CU191" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CV191" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="CW191" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX191" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CY191" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CZ191" t="n">
         <v>25</v>
@@ -88860,19 +88860,19 @@
         <v>4</v>
       </c>
       <c r="R192" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S192" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T192" t="n">
         <v>15</v>
       </c>
       <c r="U192" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V192" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W192" t="n">
         <v>18</v>
@@ -88881,10 +88881,10 @@
         <v>12</v>
       </c>
       <c r="Y192" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Z192" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
@@ -89044,13 +89044,13 @@
         <v>68</v>
       </c>
       <c r="BZ192" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="CA192" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="CB192" t="n">
-        <v>2.84</v>
+        <v>3.03</v>
       </c>
       <c r="CC192" t="n">
         <v>0</v>
@@ -89110,16 +89110,16 @@
         <v>12</v>
       </c>
       <c r="CV192" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CW192" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX192" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="CY192" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="CZ192" t="n">
         <v>35</v>
@@ -89793,22 +89793,22 @@
         <v>0</v>
       </c>
       <c r="Q194" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R194" t="n">
+        <v>9</v>
+      </c>
+      <c r="S194" t="n">
         <v>8</v>
       </c>
-      <c r="S194" t="n">
-        <v>7</v>
-      </c>
       <c r="T194" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U194" t="n">
         <v>14</v>
       </c>
       <c r="V194" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="W194" t="n">
         <v>14</v>
@@ -89817,10 +89817,10 @@
         <v>7</v>
       </c>
       <c r="Y194" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Z194" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
@@ -89980,13 +89980,13 @@
         <v>71</v>
       </c>
       <c r="BZ194" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="CA194" t="n">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="CB194" t="n">
-        <v>3.39</v>
+        <v>3.7</v>
       </c>
       <c r="CC194" t="n">
         <v>0</v>
@@ -90034,10 +90034,10 @@
         <v>1</v>
       </c>
       <c r="CR194" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="CS194" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CT194" t="n">
         <v>1</v>
@@ -90046,16 +90046,16 @@
         <v>7</v>
       </c>
       <c r="CV194" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CW194" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX194" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CY194" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CZ194" t="n">
         <v>55</v>
@@ -90255,16 +90255,16 @@
         <v>5</v>
       </c>
       <c r="S195" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T195" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U195" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V195" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W195" t="n">
         <v>13</v>
@@ -90273,10 +90273,10 @@
         <v>15</v>
       </c>
       <c r="Y195" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Z195" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA195" t="inlineStr"/>
       <c r="AB195" t="inlineStr"/>
@@ -90428,13 +90428,13 @@
         <v>88</v>
       </c>
       <c r="BZ195" t="n">
-        <v>0.85</v>
+        <v>0.97</v>
       </c>
       <c r="CA195" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="CB195" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="CC195" t="n">
         <v>0</v>
@@ -90482,7 +90482,7 @@
         <v>1</v>
       </c>
       <c r="CR195" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CS195" t="n">
         <v>35</v>
@@ -90491,19 +90491,19 @@
         <v>1</v>
       </c>
       <c r="CU195" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="CV195" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CW195" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX195" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="CY195" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CZ195" t="n">
         <v>35</v>
@@ -91188,19 +91188,19 @@
         <v>5</v>
       </c>
       <c r="R197" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S197" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T197" t="n">
         <v>5</v>
       </c>
       <c r="U197" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V197" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W197" t="n">
         <v>18</v>
@@ -91209,10 +91209,10 @@
         <v>11</v>
       </c>
       <c r="Y197" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Z197" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
@@ -91372,13 +91372,13 @@
         <v>67</v>
       </c>
       <c r="BZ197" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="CA197" t="n">
-        <v>0.99</v>
+        <v>1.12</v>
       </c>
       <c r="CB197" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="CC197" t="n">
         <v>0</v>
@@ -91429,25 +91429,25 @@
         <v>16</v>
       </c>
       <c r="CS197" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CT197" t="n">
         <v>1</v>
       </c>
       <c r="CU197" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CV197" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="CW197" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX197" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CY197" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CZ197" t="n">
         <v>64</v>
@@ -91641,19 +91641,19 @@
         <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R198" t="n">
+        <v>4</v>
+      </c>
+      <c r="S198" t="n">
+        <v>2</v>
+      </c>
+      <c r="T198" t="n">
         <v>5</v>
       </c>
-      <c r="S198" t="n">
-        <v>3</v>
-      </c>
-      <c r="T198" t="n">
-        <v>4</v>
-      </c>
       <c r="U198" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V198" t="n">
         <v>9</v>
@@ -91665,10 +91665,10 @@
         <v>18</v>
       </c>
       <c r="Y198" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Z198" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
@@ -91828,13 +91828,13 @@
         <v>92</v>
       </c>
       <c r="BZ198" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="CA198" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="CB198" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="CC198" t="n">
         <v>0</v>
@@ -91882,28 +91882,28 @@
         <v>1</v>
       </c>
       <c r="CR198" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CS198" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="CT198" t="n">
         <v>1</v>
       </c>
       <c r="CU198" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CV198" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CW198" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX198" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="CY198" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="CZ198" t="n">
         <v>50</v>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -93487,40 +93487,40 @@
         <v>4</v>
       </c>
       <c r="K202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L202" t="n">
+        <v>7</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="n">
+        <v>2</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>3</v>
+      </c>
+      <c r="R202" t="n">
         <v>6</v>
       </c>
-      <c r="M202" t="n">
-        <v>0</v>
-      </c>
-      <c r="N202" t="n">
-        <v>2</v>
-      </c>
-      <c r="O202" t="n">
-        <v>0</v>
-      </c>
-      <c r="P202" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q202" t="n">
-        <v>4</v>
-      </c>
-      <c r="R202" t="n">
-        <v>3</v>
-      </c>
       <c r="S202" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T202" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U202" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V202" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="W202" t="n">
         <v>5</v>
@@ -93529,10 +93529,10 @@
         <v>14</v>
       </c>
       <c r="Y202" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="Z202" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
@@ -93692,13 +93692,13 @@
         <v>54</v>
       </c>
       <c r="BZ202" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="CA202" t="n">
-        <v>1.09</v>
+        <v>1.61</v>
       </c>
       <c r="CB202" t="n">
-        <v>2.18</v>
+        <v>2.75</v>
       </c>
       <c r="CC202" t="n">
         <v>0</v>
@@ -93746,7 +93746,7 @@
         <v>1</v>
       </c>
       <c r="CR202" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CS202" t="n">
         <v>24</v>
@@ -93755,19 +93755,19 @@
         <v>1</v>
       </c>
       <c r="CU202" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="CV202" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW202" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX202" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY202" t="n">
         <v>8</v>
-      </c>
-      <c r="CW202" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CX202" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CY202" t="n">
-        <v>-1</v>
       </c>
       <c r="CZ202" t="n">
         <v>46</v>
@@ -95329,13 +95329,13 @@
         <v>1</v>
       </c>
       <c r="Q206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
         <v>2</v>
       </c>
       <c r="S206" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T206" t="n">
         <v>8</v>
@@ -95353,10 +95353,10 @@
         <v>17</v>
       </c>
       <c r="Y206" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z206" t="n">
         <v>52</v>
-      </c>
-      <c r="Z206" t="n">
-        <v>48</v>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
@@ -95516,13 +95516,13 @@
         <v>66</v>
       </c>
       <c r="BZ206" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="CA206" t="n">
         <v>1.05</v>
       </c>
       <c r="CB206" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="CC206" t="n">
         <v>0</v>
@@ -95579,19 +95579,19 @@
         <v>1</v>
       </c>
       <c r="CU206" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="CV206" t="n">
         <v>11</v>
       </c>
       <c r="CW206" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX206" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CY206" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="CZ206" t="n">
         <v>50</v>
@@ -95756,13 +95756,13 @@
         <v>1</v>
       </c>
       <c r="J207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K207" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L207" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M207" t="n">
         <v>0</v>
@@ -95780,19 +95780,19 @@
         <v>4</v>
       </c>
       <c r="R207" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S207" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T207" t="n">
+        <v>17</v>
+      </c>
+      <c r="U207" t="n">
         <v>14</v>
       </c>
-      <c r="U207" t="n">
-        <v>12</v>
-      </c>
       <c r="V207" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="W207" t="n">
         <v>14</v>
@@ -95801,10 +95801,10 @@
         <v>19</v>
       </c>
       <c r="Y207" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z207" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
@@ -95964,13 +95964,13 @@
         <v>102</v>
       </c>
       <c r="BZ207" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="CA207" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="CB207" t="n">
-        <v>3.18</v>
+        <v>3.62</v>
       </c>
       <c r="CC207" t="n">
         <v>0</v>
@@ -96030,16 +96030,16 @@
         <v>20</v>
       </c>
       <c r="CV207" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CW207" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX207" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="CY207" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CZ207" t="n">
         <v>48</v>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -97641,19 +97641,19 @@
         <v>0</v>
       </c>
       <c r="Q211" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R211" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S211" t="n">
         <v>4</v>
       </c>
       <c r="T211" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U211" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V211" t="n">
         <v>8</v>
@@ -97665,10 +97665,10 @@
         <v>9</v>
       </c>
       <c r="Y211" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Z211" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AA211" t="inlineStr"/>
       <c r="AB211" t="inlineStr"/>
@@ -97820,13 +97820,13 @@
         <v>100</v>
       </c>
       <c r="BZ211" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="CA211" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="CB211" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="CC211" t="n">
         <v>0</v>
@@ -97886,16 +97886,16 @@
         <v>9</v>
       </c>
       <c r="CV211" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="CW211" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX211" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="CY211" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CZ211" t="n">
         <v>68</v>
@@ -99484,19 +99484,19 @@
         <v>4</v>
       </c>
       <c r="R215" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S215" t="n">
+        <v>11</v>
+      </c>
+      <c r="T215" t="n">
+        <v>4</v>
+      </c>
+      <c r="U215" t="n">
+        <v>15</v>
+      </c>
+      <c r="V215" t="n">
         <v>8</v>
-      </c>
-      <c r="T215" t="n">
-        <v>3</v>
-      </c>
-      <c r="U215" t="n">
-        <v>12</v>
-      </c>
-      <c r="V215" t="n">
-        <v>6</v>
       </c>
       <c r="W215" t="n">
         <v>12</v>
@@ -99505,10 +99505,10 @@
         <v>9</v>
       </c>
       <c r="Y215" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="Z215" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
@@ -99668,13 +99668,13 @@
         <v>77</v>
       </c>
       <c r="BZ215" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="CA215" t="n">
-        <v>0.96</v>
+        <v>1.15</v>
       </c>
       <c r="CB215" t="n">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="CC215" t="n">
         <v>0</v>
@@ -99722,7 +99722,7 @@
         <v>1</v>
       </c>
       <c r="CR215" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CS215" t="n">
         <v>20</v>
@@ -99734,16 +99734,16 @@
         <v>10</v>
       </c>
       <c r="CV215" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW215" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="CX215" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="CY215" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="CZ215" t="n">
         <v>27</v>

--- a/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
+++ b/data/matches/leagues/LigaPro_Portugal_2a_división_2025-2026.xlsx
@@ -104086,7 +104086,7 @@
         <v>0</v>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q225" t="n">
         <v>2</v>
@@ -104132,7 +104132,7 @@
         <v>3</v>
       </c>
       <c r="AD225" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE225" t="n">
         <v>1.98</v>
@@ -104252,13 +104252,13 @@
         <v>2</v>
       </c>
       <c r="BR225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS225" t="n">
         <v>3</v>
       </c>
       <c r="BT225" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU225" t="n">
         <v>1</v>
@@ -104424,74 +104424,82 @@
       </c>
       <c r="DW225" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="DX225" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="DY225" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="DZ225" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="EA225" t="inlineStr">
         <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="EB225" t="inlineStr"/>
-      <c r="EC225" t="inlineStr"/>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EB225" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EC225" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
       <c r="ED225" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EE225" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EF225" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EG225" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="EH225" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EI225" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EJ225" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EK225" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EL225" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.07</t>
         </is>
       </c>
     </row>
